--- a/compare/output/dscale_CO2_downscaled_SSP460.xlsx
+++ b/compare/output/dscale_CO2_downscaled_SSP460.xlsx
@@ -535,7 +535,7 @@
         <v>0.241678</v>
       </c>
       <c r="H2" t="n">
-        <v>0.271519</v>
+        <v>0.27152</v>
       </c>
       <c r="I2" t="n">
         <v>0.293247</v>
@@ -760,7 +760,7 @@
         <v>0.333281</v>
       </c>
       <c r="G5" t="n">
-        <v>0.478325</v>
+        <v>0.478326</v>
       </c>
       <c r="H5" t="n">
         <v>0.641835</v>
@@ -836,13 +836,13 @@
         <v>6.586869</v>
       </c>
       <c r="G6" t="n">
-        <v>6.899435</v>
+        <v>6.899436</v>
       </c>
       <c r="H6" t="n">
-        <v>7.25055</v>
+        <v>7.250552</v>
       </c>
       <c r="I6" t="n">
-        <v>7.632468</v>
+        <v>7.632472</v>
       </c>
       <c r="J6" t="n">
         <v>12.480582</v>
@@ -909,16 +909,16 @@
         <v>5.7596</v>
       </c>
       <c r="F7" t="n">
-        <v>8.926752</v>
+        <v>8.926750999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>10.811509</v>
+        <v>10.811508</v>
       </c>
       <c r="H7" t="n">
-        <v>13.023802</v>
+        <v>13.0238</v>
       </c>
       <c r="I7" t="n">
-        <v>15.239087</v>
+        <v>15.23908</v>
       </c>
       <c r="J7" t="n">
         <v>9.654696</v>
@@ -988,13 +988,13 @@
         <v>1.701139</v>
       </c>
       <c r="G8" t="n">
-        <v>2.012675</v>
+        <v>2.012676</v>
       </c>
       <c r="H8" t="n">
         <v>2.366648</v>
       </c>
       <c r="I8" t="n">
-        <v>2.70134</v>
+        <v>2.701341</v>
       </c>
       <c r="J8" t="n">
         <v>3.856727</v>
@@ -1061,13 +1061,13 @@
         <v>1.299174</v>
       </c>
       <c r="F9" t="n">
-        <v>1.52672</v>
+        <v>1.526719</v>
       </c>
       <c r="G9" t="n">
         <v>1.335611</v>
       </c>
       <c r="H9" t="n">
-        <v>1.207858</v>
+        <v>1.207857</v>
       </c>
       <c r="I9" t="n">
         <v>1.116186</v>
@@ -1140,13 +1140,13 @@
         <v>0.483944</v>
       </c>
       <c r="G10" t="n">
-        <v>0.480384</v>
+        <v>0.480385</v>
       </c>
       <c r="H10" t="n">
         <v>0.496848</v>
       </c>
       <c r="I10" t="n">
-        <v>0.518078</v>
+        <v>0.518079</v>
       </c>
       <c r="J10" t="n">
         <v>1.749278</v>
@@ -1216,13 +1216,13 @@
         <v>10.138872</v>
       </c>
       <c r="G11" t="n">
-        <v>11.180577</v>
+        <v>11.180576</v>
       </c>
       <c r="H11" t="n">
-        <v>12.471667</v>
+        <v>12.471665</v>
       </c>
       <c r="I11" t="n">
-        <v>13.591516</v>
+        <v>13.591513</v>
       </c>
       <c r="J11" t="n">
         <v>11.237282</v>
@@ -1371,10 +1371,10 @@
         <v>2.787266</v>
       </c>
       <c r="H13" t="n">
-        <v>3.125593</v>
+        <v>3.125595</v>
       </c>
       <c r="I13" t="n">
-        <v>3.511403</v>
+        <v>3.511406</v>
       </c>
       <c r="J13" t="n">
         <v>8.062433</v>
@@ -1438,58 +1438,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>44.334894</v>
+        <v>44.334895</v>
       </c>
       <c r="F14" t="n">
-        <v>52.162678</v>
+        <v>52.16268</v>
       </c>
       <c r="G14" t="n">
-        <v>57.386579</v>
+        <v>57.386583</v>
       </c>
       <c r="H14" t="n">
-        <v>63.819041</v>
+        <v>63.819047</v>
       </c>
       <c r="I14" t="n">
-        <v>70.19728499999999</v>
+        <v>70.197292</v>
       </c>
       <c r="J14" t="n">
-        <v>75.855555</v>
+        <v>75.855565</v>
       </c>
       <c r="K14" t="n">
-        <v>80.95252600000001</v>
+        <v>80.952538</v>
       </c>
       <c r="L14" t="n">
-        <v>84.792027</v>
+        <v>84.792041</v>
       </c>
       <c r="M14" t="n">
-        <v>88.244996</v>
+        <v>88.245012</v>
       </c>
       <c r="N14" t="n">
-        <v>91.08234299999999</v>
+        <v>91.08236100000001</v>
       </c>
       <c r="O14" t="n">
-        <v>91.901912</v>
+        <v>91.901933</v>
       </c>
       <c r="P14" t="n">
-        <v>92.58988600000001</v>
+        <v>92.58990900000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>91.99858399999999</v>
+        <v>91.998609</v>
       </c>
       <c r="R14" t="n">
-        <v>90.311511</v>
+        <v>90.311537</v>
       </c>
       <c r="S14" t="n">
-        <v>88.883892</v>
+        <v>88.88392</v>
       </c>
       <c r="T14" t="n">
-        <v>87.97293999999999</v>
+        <v>87.97297</v>
       </c>
       <c r="U14" t="n">
-        <v>86.903555</v>
+        <v>86.903587</v>
       </c>
       <c r="V14" t="n">
-        <v>85.995605</v>
+        <v>85.995639</v>
       </c>
     </row>
     <row r="15">
@@ -1514,58 +1514,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>64.37771499999999</v>
+        <v>64.377714</v>
       </c>
       <c r="F15" t="n">
-        <v>83.659538</v>
+        <v>83.659537</v>
       </c>
       <c r="G15" t="n">
-        <v>96.56450700000001</v>
+        <v>96.564505</v>
       </c>
       <c r="H15" t="n">
-        <v>109.532246</v>
+        <v>109.532244</v>
       </c>
       <c r="I15" t="n">
-        <v>120.884261</v>
+        <v>120.884259</v>
       </c>
       <c r="J15" t="n">
-        <v>130.047892</v>
+        <v>130.047888</v>
       </c>
       <c r="K15" t="n">
-        <v>138.128504</v>
+        <v>138.128499</v>
       </c>
       <c r="L15" t="n">
-        <v>144.692713</v>
+        <v>144.692708</v>
       </c>
       <c r="M15" t="n">
-        <v>151.314545</v>
+        <v>151.314539</v>
       </c>
       <c r="N15" t="n">
-        <v>157.287357</v>
+        <v>157.287349</v>
       </c>
       <c r="O15" t="n">
-        <v>159.834045</v>
+        <v>159.834036</v>
       </c>
       <c r="P15" t="n">
-        <v>161.999974</v>
+        <v>161.999964</v>
       </c>
       <c r="Q15" t="n">
-        <v>161.66182</v>
+        <v>161.661809</v>
       </c>
       <c r="R15" t="n">
-        <v>159.078547</v>
+        <v>159.078535</v>
       </c>
       <c r="S15" t="n">
-        <v>156.621063</v>
+        <v>156.621051</v>
       </c>
       <c r="T15" t="n">
-        <v>154.719443</v>
+        <v>154.71943</v>
       </c>
       <c r="U15" t="n">
-        <v>152.17691</v>
+        <v>152.176896</v>
       </c>
       <c r="V15" t="n">
-        <v>149.621522</v>
+        <v>149.621507</v>
       </c>
     </row>
     <row r="16">
@@ -1593,55 +1593,55 @@
         <v>14.707479</v>
       </c>
       <c r="F16" t="n">
-        <v>15.243764</v>
+        <v>15.243765</v>
       </c>
       <c r="G16" t="n">
-        <v>14.306075</v>
+        <v>14.306076</v>
       </c>
       <c r="H16" t="n">
-        <v>14.04979</v>
+        <v>14.049791</v>
       </c>
       <c r="I16" t="n">
-        <v>14.178345</v>
+        <v>14.178346</v>
       </c>
       <c r="J16" t="n">
-        <v>14.502996</v>
+        <v>14.502997</v>
       </c>
       <c r="K16" t="n">
-        <v>14.982208</v>
+        <v>14.982209</v>
       </c>
       <c r="L16" t="n">
-        <v>15.43039</v>
+        <v>15.430391</v>
       </c>
       <c r="M16" t="n">
-        <v>15.947765</v>
+        <v>15.947767</v>
       </c>
       <c r="N16" t="n">
-        <v>16.416819</v>
+        <v>16.41682</v>
       </c>
       <c r="O16" t="n">
-        <v>16.520545</v>
+        <v>16.520546</v>
       </c>
       <c r="P16" t="n">
-        <v>16.572831</v>
+        <v>16.572832</v>
       </c>
       <c r="Q16" t="n">
-        <v>16.371588</v>
+        <v>16.371589</v>
       </c>
       <c r="R16" t="n">
-        <v>15.967934</v>
+        <v>15.967935</v>
       </c>
       <c r="S16" t="n">
-        <v>15.617798</v>
+        <v>15.617799</v>
       </c>
       <c r="T16" t="n">
-        <v>15.369195</v>
+        <v>15.369196</v>
       </c>
       <c r="U16" t="n">
-        <v>15.105361</v>
+        <v>15.105362</v>
       </c>
       <c r="V16" t="n">
-        <v>14.874827</v>
+        <v>14.874828</v>
       </c>
     </row>
     <row r="17">
@@ -1666,58 +1666,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>16.439384</v>
+        <v>16.439383</v>
       </c>
       <c r="F17" t="n">
-        <v>19.234521</v>
+        <v>19.234519</v>
       </c>
       <c r="G17" t="n">
-        <v>20.343063</v>
+        <v>20.343061</v>
       </c>
       <c r="H17" t="n">
-        <v>21.475992</v>
+        <v>21.475988</v>
       </c>
       <c r="I17" t="n">
-        <v>22.260847</v>
+        <v>22.260842</v>
       </c>
       <c r="J17" t="n">
-        <v>22.475349</v>
+        <v>22.475342</v>
       </c>
       <c r="K17" t="n">
-        <v>22.43882</v>
+        <v>22.438812</v>
       </c>
       <c r="L17" t="n">
-        <v>22.257611</v>
+        <v>22.257602</v>
       </c>
       <c r="M17" t="n">
-        <v>22.327633</v>
+        <v>22.327622</v>
       </c>
       <c r="N17" t="n">
-        <v>22.542529</v>
+        <v>22.542517</v>
       </c>
       <c r="O17" t="n">
-        <v>22.473708</v>
+        <v>22.473695</v>
       </c>
       <c r="P17" t="n">
-        <v>22.489038</v>
+        <v>22.489024</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.241244</v>
+        <v>22.241229</v>
       </c>
       <c r="R17" t="n">
-        <v>21.7781</v>
+        <v>21.778085</v>
       </c>
       <c r="S17" t="n">
-        <v>21.4501</v>
+        <v>21.450084</v>
       </c>
       <c r="T17" t="n">
-        <v>21.347196</v>
+        <v>21.347179</v>
       </c>
       <c r="U17" t="n">
-        <v>21.325758</v>
+        <v>21.32574</v>
       </c>
       <c r="V17" t="n">
-        <v>21.436623</v>
+        <v>21.436605</v>
       </c>
     </row>
     <row r="18">
@@ -1754,16 +1754,16 @@
         <v>12.436918</v>
       </c>
       <c r="I18" t="n">
-        <v>13.468073</v>
+        <v>13.468072</v>
       </c>
       <c r="J18" t="n">
-        <v>14.664939</v>
+        <v>14.664938</v>
       </c>
       <c r="K18" t="n">
-        <v>15.996624</v>
+        <v>15.996623</v>
       </c>
       <c r="L18" t="n">
-        <v>17.279106</v>
+        <v>17.279105</v>
       </c>
       <c r="M18" t="n">
         <v>18.427865</v>
@@ -1781,10 +1781,10 @@
         <v>18.148198</v>
       </c>
       <c r="R18" t="n">
-        <v>17.222382</v>
+        <v>17.222381</v>
       </c>
       <c r="S18" t="n">
-        <v>16.399018</v>
+        <v>16.399017</v>
       </c>
       <c r="T18" t="n">
         <v>15.741089</v>
@@ -1793,7 +1793,7 @@
         <v>15.121458</v>
       </c>
       <c r="V18" t="n">
-        <v>14.580967</v>
+        <v>14.580966</v>
       </c>
     </row>
     <row r="19">
@@ -1827,7 +1827,7 @@
         <v>14.673292</v>
       </c>
       <c r="H19" t="n">
-        <v>16.271805</v>
+        <v>16.271804</v>
       </c>
       <c r="I19" t="n">
         <v>17.914294</v>
@@ -2058,7 +2058,7 @@
         <v>3.198387</v>
       </c>
       <c r="I22" t="n">
-        <v>3.481071</v>
+        <v>3.481072</v>
       </c>
       <c r="J22" t="n">
         <v>5.380083</v>
@@ -2204,7 +2204,7 @@
         <v>1.518716</v>
       </c>
       <c r="G24" t="n">
-        <v>1.681206</v>
+        <v>1.681205</v>
       </c>
       <c r="H24" t="n">
         <v>1.814574</v>
@@ -2356,13 +2356,13 @@
         <v>4.957188</v>
       </c>
       <c r="G26" t="n">
-        <v>5.333527</v>
+        <v>5.333528</v>
       </c>
       <c r="H26" t="n">
-        <v>5.689253</v>
+        <v>5.689254</v>
       </c>
       <c r="I26" t="n">
-        <v>6.105135</v>
+        <v>6.105137</v>
       </c>
       <c r="J26" t="n">
         <v>13.144654</v>
@@ -2438,7 +2438,7 @@
         <v>2.430023</v>
       </c>
       <c r="I27" t="n">
-        <v>2.664332</v>
+        <v>2.664334</v>
       </c>
       <c r="J27" t="n">
         <v>6.473291</v>
@@ -2508,13 +2508,13 @@
         <v>4.387437</v>
       </c>
       <c r="G28" t="n">
-        <v>5.143028</v>
+        <v>5.143027</v>
       </c>
       <c r="H28" t="n">
-        <v>6.193975</v>
+        <v>6.193974</v>
       </c>
       <c r="I28" t="n">
-        <v>7.575323</v>
+        <v>7.575319</v>
       </c>
       <c r="J28" t="n">
         <v>0.56876</v>
@@ -2961,16 +2961,16 @@
         <v>0.838858</v>
       </c>
       <c r="F34" t="n">
-        <v>1.932427</v>
+        <v>1.932426</v>
       </c>
       <c r="G34" t="n">
-        <v>3.746908</v>
+        <v>3.746907</v>
       </c>
       <c r="H34" t="n">
-        <v>6.10539</v>
+        <v>6.105388</v>
       </c>
       <c r="I34" t="n">
-        <v>8.415851999999999</v>
+        <v>8.415849</v>
       </c>
       <c r="J34" t="n">
         <v>23.454572</v>
@@ -3037,7 +3037,7 @@
         <v>1.381694</v>
       </c>
       <c r="F35" t="n">
-        <v>2.249056</v>
+        <v>2.249057</v>
       </c>
       <c r="G35" t="n">
         <v>3.141299</v>
@@ -3046,7 +3046,7 @@
         <v>3.999476</v>
       </c>
       <c r="I35" t="n">
-        <v>4.592177</v>
+        <v>4.592178</v>
       </c>
       <c r="J35" t="n">
         <v>2.122288</v>
@@ -3195,7 +3195,7 @@
         <v>1.804025</v>
       </c>
       <c r="H37" t="n">
-        <v>1.839741</v>
+        <v>1.839742</v>
       </c>
       <c r="I37" t="n">
         <v>1.851331</v>
@@ -3268,13 +3268,13 @@
         <v>5.182872</v>
       </c>
       <c r="G38" t="n">
-        <v>5.91829</v>
+        <v>5.918291</v>
       </c>
       <c r="H38" t="n">
         <v>6.693076</v>
       </c>
       <c r="I38" t="n">
-        <v>7.405721</v>
+        <v>7.405722</v>
       </c>
       <c r="J38" t="n">
         <v>5.718107</v>
@@ -3797,7 +3797,7 @@
         <v>0.657623</v>
       </c>
       <c r="F45" t="n">
-        <v>0.942604</v>
+        <v>0.942605</v>
       </c>
       <c r="G45" t="n">
         <v>1.127411</v>
@@ -3876,13 +3876,13 @@
         <v>0.7284</v>
       </c>
       <c r="G46" t="n">
-        <v>0.906423</v>
+        <v>0.9064219999999999</v>
       </c>
       <c r="H46" t="n">
         <v>1.140105</v>
       </c>
       <c r="I46" t="n">
-        <v>1.449754</v>
+        <v>1.449753</v>
       </c>
       <c r="J46" t="n">
         <v>3.149057</v>
@@ -3955,10 +3955,10 @@
         <v>54.989578</v>
       </c>
       <c r="H47" t="n">
-        <v>65.90714199999999</v>
+        <v>65.907143</v>
       </c>
       <c r="I47" t="n">
-        <v>76.069463</v>
+        <v>76.06946499999999</v>
       </c>
       <c r="J47" t="n">
         <v>79.83144299999999</v>
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>112.261664</v>
+        <v>112.261678</v>
       </c>
       <c r="F54" t="n">
-        <v>133.935774</v>
+        <v>133.935806</v>
       </c>
       <c r="G54" t="n">
-        <v>141.877177</v>
+        <v>141.877224</v>
       </c>
       <c r="H54" t="n">
-        <v>146.023804</v>
+        <v>146.023865</v>
       </c>
       <c r="I54" t="n">
-        <v>148.161479</v>
+        <v>148.161554</v>
       </c>
       <c r="J54" t="n">
-        <v>147.409714</v>
+        <v>147.409801</v>
       </c>
       <c r="K54" t="n">
-        <v>146.978865</v>
+        <v>146.978965</v>
       </c>
       <c r="L54" t="n">
-        <v>144.584934</v>
+        <v>144.585045</v>
       </c>
       <c r="M54" t="n">
-        <v>144.297104</v>
+        <v>144.297228</v>
       </c>
       <c r="N54" t="n">
-        <v>147.128217</v>
+        <v>147.128359</v>
       </c>
       <c r="O54" t="n">
-        <v>150.888664</v>
+        <v>150.888827</v>
       </c>
       <c r="P54" t="n">
-        <v>155.584477</v>
+        <v>155.584666</v>
       </c>
       <c r="Q54" t="n">
-        <v>158.501148</v>
+        <v>158.501365</v>
       </c>
       <c r="R54" t="n">
-        <v>159.720166</v>
+        <v>159.720416</v>
       </c>
       <c r="S54" t="n">
-        <v>159.726642</v>
+        <v>159.726931</v>
       </c>
       <c r="T54" t="n">
-        <v>158.865514</v>
+        <v>158.865853</v>
       </c>
       <c r="U54" t="n">
-        <v>157.422178</v>
+        <v>157.422585</v>
       </c>
       <c r="V54" t="n">
-        <v>155.439975</v>
+        <v>155.440482</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>9.898759999999999</v>
+        <v>9.898745999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>10.974632</v>
+        <v>10.9746</v>
       </c>
       <c r="G55" t="n">
-        <v>10.96558</v>
+        <v>10.965533</v>
       </c>
       <c r="H55" t="n">
-        <v>10.790734</v>
+        <v>10.790673</v>
       </c>
       <c r="I55" t="n">
-        <v>10.581149</v>
+        <v>10.581075</v>
       </c>
       <c r="J55" t="n">
-        <v>10.256767</v>
+        <v>10.256681</v>
       </c>
       <c r="K55" t="n">
-        <v>10.02309</v>
+        <v>10.022991</v>
       </c>
       <c r="L55" t="n">
-        <v>9.703082999999999</v>
+        <v>9.702973</v>
       </c>
       <c r="M55" t="n">
-        <v>9.556195000000001</v>
+        <v>9.55607</v>
       </c>
       <c r="N55" t="n">
-        <v>9.640060999999999</v>
+        <v>9.639919000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>9.813364</v>
+        <v>9.813202</v>
       </c>
       <c r="P55" t="n">
-        <v>10.081499</v>
+        <v>10.081311</v>
       </c>
       <c r="Q55" t="n">
-        <v>10.272114</v>
+        <v>10.271896</v>
       </c>
       <c r="R55" t="n">
-        <v>10.391886</v>
+        <v>10.391636</v>
       </c>
       <c r="S55" t="n">
-        <v>10.467486</v>
+        <v>10.467197</v>
       </c>
       <c r="T55" t="n">
-        <v>10.52044</v>
+        <v>10.520102</v>
       </c>
       <c r="U55" t="n">
-        <v>10.566666</v>
+        <v>10.566259</v>
       </c>
       <c r="V55" t="n">
-        <v>10.598015</v>
+        <v>10.597508</v>
       </c>
     </row>
     <row r="56">
@@ -4782,58 +4782,58 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.393495</v>
+        <v>0.393496</v>
       </c>
       <c r="F58" t="n">
-        <v>0.423725</v>
+        <v>0.423726</v>
       </c>
       <c r="G58" t="n">
-        <v>0.47101</v>
+        <v>0.471013</v>
       </c>
       <c r="H58" t="n">
-        <v>0.509162</v>
+        <v>0.509165</v>
       </c>
       <c r="I58" t="n">
-        <v>0.533062</v>
+        <v>0.533066</v>
       </c>
       <c r="J58" t="n">
-        <v>0.537166</v>
+        <v>0.537172</v>
       </c>
       <c r="K58" t="n">
-        <v>0.525499</v>
+        <v>0.525506</v>
       </c>
       <c r="L58" t="n">
-        <v>0.505729</v>
+        <v>0.505737</v>
       </c>
       <c r="M58" t="n">
-        <v>0.493586</v>
+        <v>0.493595</v>
       </c>
       <c r="N58" t="n">
-        <v>0.487594</v>
+        <v>0.487604</v>
       </c>
       <c r="O58" t="n">
-        <v>0.482024</v>
+        <v>0.482036</v>
       </c>
       <c r="P58" t="n">
-        <v>0.483757</v>
+        <v>0.483771</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.482557</v>
+        <v>0.482573</v>
       </c>
       <c r="R58" t="n">
-        <v>0.475555</v>
+        <v>0.475573</v>
       </c>
       <c r="S58" t="n">
-        <v>0.464622</v>
+        <v>0.464642</v>
       </c>
       <c r="T58" t="n">
-        <v>0.450053</v>
+        <v>0.450076</v>
       </c>
       <c r="U58" t="n">
-        <v>0.432449</v>
+        <v>0.432476</v>
       </c>
       <c r="V58" t="n">
-        <v>0.413135</v>
+        <v>0.413167</v>
       </c>
     </row>
     <row r="59">
@@ -4861,55 +4861,55 @@
         <v>0.086434</v>
       </c>
       <c r="F59" t="n">
-        <v>0.096884</v>
+        <v>0.096883</v>
       </c>
       <c r="G59" t="n">
-        <v>0.111599</v>
+        <v>0.111597</v>
       </c>
       <c r="H59" t="n">
-        <v>0.122295</v>
+        <v>0.122294</v>
       </c>
       <c r="I59" t="n">
-        <v>0.128686</v>
+        <v>0.128684</v>
       </c>
       <c r="J59" t="n">
-        <v>0.130588</v>
+        <v>0.130586</v>
       </c>
       <c r="K59" t="n">
-        <v>0.129428</v>
+        <v>0.129425</v>
       </c>
       <c r="L59" t="n">
-        <v>0.127344</v>
+        <v>0.127341</v>
       </c>
       <c r="M59" t="n">
-        <v>0.128589</v>
+        <v>0.128586</v>
       </c>
       <c r="N59" t="n">
-        <v>0.133107</v>
+        <v>0.133103</v>
       </c>
       <c r="O59" t="n">
-        <v>0.139423</v>
+        <v>0.139418</v>
       </c>
       <c r="P59" t="n">
-        <v>0.149298</v>
+        <v>0.149292</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.159583</v>
+        <v>0.159576</v>
       </c>
       <c r="R59" t="n">
-        <v>0.169177</v>
+        <v>0.16917</v>
       </c>
       <c r="S59" t="n">
-        <v>0.178594</v>
+        <v>0.178586</v>
       </c>
       <c r="T59" t="n">
-        <v>0.188013</v>
+        <v>0.188002</v>
       </c>
       <c r="U59" t="n">
-        <v>0.197533</v>
+        <v>0.197519</v>
       </c>
       <c r="V59" t="n">
-        <v>0.207589</v>
+        <v>0.207572</v>
       </c>
     </row>
     <row r="60">
@@ -4949,43 +4949,43 @@
         <v>0.18192</v>
       </c>
       <c r="J60" t="n">
-        <v>0.172288</v>
+        <v>0.172289</v>
       </c>
       <c r="K60" t="n">
-        <v>0.160159</v>
+        <v>0.16016</v>
       </c>
       <c r="L60" t="n">
-        <v>0.146884</v>
+        <v>0.146885</v>
       </c>
       <c r="M60" t="n">
-        <v>0.135997</v>
+        <v>0.135998</v>
       </c>
       <c r="N60" t="n">
-        <v>0.127328</v>
+        <v>0.127329</v>
       </c>
       <c r="O60" t="n">
-        <v>0.11963</v>
+        <v>0.119631</v>
       </c>
       <c r="P60" t="n">
-        <v>0.115133</v>
+        <v>0.115134</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.110665</v>
+        <v>0.110667</v>
       </c>
       <c r="R60" t="n">
-        <v>0.105495</v>
+        <v>0.105496</v>
       </c>
       <c r="S60" t="n">
-        <v>0.09986</v>
+        <v>0.09986200000000001</v>
       </c>
       <c r="T60" t="n">
-        <v>0.093875</v>
+        <v>0.093876</v>
       </c>
       <c r="U60" t="n">
-        <v>0.087773</v>
+        <v>0.087774</v>
       </c>
       <c r="V60" t="n">
-        <v>0.081835</v>
+        <v>0.08183699999999999</v>
       </c>
     </row>
     <row r="61">
@@ -5013,55 +5013,55 @@
         <v>2.729493</v>
       </c>
       <c r="F61" t="n">
-        <v>2.930936</v>
+        <v>2.930935</v>
       </c>
       <c r="G61" t="n">
-        <v>3.093603</v>
+        <v>3.093602</v>
       </c>
       <c r="H61" t="n">
-        <v>3.155784</v>
+        <v>3.155782</v>
       </c>
       <c r="I61" t="n">
-        <v>3.137796</v>
+        <v>3.137793</v>
       </c>
       <c r="J61" t="n">
-        <v>3.051084</v>
+        <v>3.051079</v>
       </c>
       <c r="K61" t="n">
-        <v>2.913326</v>
+        <v>2.913319</v>
       </c>
       <c r="L61" t="n">
-        <v>2.752127</v>
+        <v>2.752119</v>
       </c>
       <c r="M61" t="n">
-        <v>2.645054</v>
+        <v>2.645044</v>
       </c>
       <c r="N61" t="n">
-        <v>2.591483</v>
+        <v>2.591471</v>
       </c>
       <c r="O61" t="n">
-        <v>2.557189</v>
+        <v>2.557176</v>
       </c>
       <c r="P61" t="n">
-        <v>2.568019</v>
+        <v>2.568004</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.561325</v>
+        <v>2.561308</v>
       </c>
       <c r="R61" t="n">
-        <v>2.519283</v>
+        <v>2.519263</v>
       </c>
       <c r="S61" t="n">
-        <v>2.44927</v>
+        <v>2.449247</v>
       </c>
       <c r="T61" t="n">
-        <v>2.357147</v>
+        <v>2.35712</v>
       </c>
       <c r="U61" t="n">
-        <v>2.250822</v>
+        <v>2.250788</v>
       </c>
       <c r="V61" t="n">
-        <v>2.138589</v>
+        <v>2.138546</v>
       </c>
     </row>
     <row r="62">
@@ -5086,58 +5086,58 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10.352147</v>
+        <v>10.352157</v>
       </c>
       <c r="F62" t="n">
-        <v>11.874874</v>
+        <v>11.874903</v>
       </c>
       <c r="G62" t="n">
-        <v>13.005846</v>
+        <v>13.005901</v>
       </c>
       <c r="H62" t="n">
-        <v>13.31099</v>
+        <v>13.311073</v>
       </c>
       <c r="I62" t="n">
-        <v>12.941902</v>
+        <v>12.942008</v>
       </c>
       <c r="J62" t="n">
-        <v>12.066117</v>
+        <v>12.066239</v>
       </c>
       <c r="K62" t="n">
-        <v>10.902911</v>
+        <v>10.903042</v>
       </c>
       <c r="L62" t="n">
-        <v>9.718018000000001</v>
+        <v>9.718154999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>8.802616</v>
+        <v>8.802761</v>
       </c>
       <c r="N62" t="n">
-        <v>8.073338</v>
+        <v>8.073492</v>
       </c>
       <c r="O62" t="n">
-        <v>7.419132</v>
+        <v>7.419294</v>
       </c>
       <c r="P62" t="n">
-        <v>6.939989</v>
+        <v>6.940164</v>
       </c>
       <c r="Q62" t="n">
-        <v>6.486953</v>
+        <v>6.48714</v>
       </c>
       <c r="R62" t="n">
-        <v>6.029333</v>
+        <v>6.029533</v>
       </c>
       <c r="S62" t="n">
-        <v>5.603288</v>
+        <v>5.603504</v>
       </c>
       <c r="T62" t="n">
-        <v>5.198703</v>
+        <v>5.198941</v>
       </c>
       <c r="U62" t="n">
-        <v>4.802396</v>
+        <v>4.802662</v>
       </c>
       <c r="V62" t="n">
-        <v>4.425868</v>
+        <v>4.426176</v>
       </c>
     </row>
     <row r="63">
@@ -5162,58 +5162,58 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>8.384328</v>
+        <v>8.384334000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>9.342665999999999</v>
+        <v>9.342681000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>9.877961000000001</v>
+        <v>9.877986</v>
       </c>
       <c r="H63" t="n">
-        <v>10.050395</v>
+        <v>10.05043</v>
       </c>
       <c r="I63" t="n">
-        <v>10.029757</v>
+        <v>10.029803</v>
       </c>
       <c r="J63" t="n">
-        <v>9.875843</v>
+        <v>9.8759</v>
       </c>
       <c r="K63" t="n">
-        <v>9.620239</v>
+        <v>9.620309000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>9.271985000000001</v>
+        <v>9.272068000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>9.034643000000001</v>
+        <v>9.034739999999999</v>
       </c>
       <c r="N63" t="n">
-        <v>8.865246000000001</v>
+        <v>8.865359</v>
       </c>
       <c r="O63" t="n">
-        <v>8.687256</v>
+        <v>8.687384</v>
       </c>
       <c r="P63" t="n">
-        <v>8.634567000000001</v>
+        <v>8.634713</v>
       </c>
       <c r="Q63" t="n">
-        <v>8.53504</v>
+        <v>8.535206000000001</v>
       </c>
       <c r="R63" t="n">
-        <v>8.360709</v>
+        <v>8.360896</v>
       </c>
       <c r="S63" t="n">
-        <v>8.137589999999999</v>
+        <v>8.137801</v>
       </c>
       <c r="T63" t="n">
-        <v>7.863101</v>
+        <v>7.863341</v>
       </c>
       <c r="U63" t="n">
-        <v>7.541027</v>
+        <v>7.541305</v>
       </c>
       <c r="V63" t="n">
-        <v>7.187034</v>
+        <v>7.187363</v>
       </c>
     </row>
     <row r="64">
@@ -5259,7 +5259,7 @@
         <v>0.035926</v>
       </c>
       <c r="L64" t="n">
-        <v>0.033299</v>
+        <v>0.033298</v>
       </c>
       <c r="M64" t="n">
         <v>0.031374</v>
@@ -5277,19 +5277,19 @@
         <v>0.028562</v>
       </c>
       <c r="R64" t="n">
-        <v>0.027875</v>
+        <v>0.027874</v>
       </c>
       <c r="S64" t="n">
         <v>0.027057</v>
       </c>
       <c r="T64" t="n">
-        <v>0.026177</v>
+        <v>0.026176</v>
       </c>
       <c r="U64" t="n">
-        <v>0.025278</v>
+        <v>0.025277</v>
       </c>
       <c r="V64" t="n">
-        <v>0.024389</v>
+        <v>0.024388</v>
       </c>
     </row>
     <row r="65">
@@ -5314,58 +5314,58 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5.96332</v>
+        <v>5.963309</v>
       </c>
       <c r="F65" t="n">
-        <v>6.949765</v>
+        <v>6.94974</v>
       </c>
       <c r="G65" t="n">
-        <v>8.097398</v>
+        <v>8.097356</v>
       </c>
       <c r="H65" t="n">
-        <v>9.126466000000001</v>
+        <v>9.126407</v>
       </c>
       <c r="I65" t="n">
-        <v>9.980433</v>
+        <v>9.980356</v>
       </c>
       <c r="J65" t="n">
-        <v>10.584838</v>
+        <v>10.584743</v>
       </c>
       <c r="K65" t="n">
-        <v>10.983167</v>
+        <v>10.983056</v>
       </c>
       <c r="L65" t="n">
-        <v>11.299955</v>
+        <v>11.299826</v>
       </c>
       <c r="M65" t="n">
-        <v>11.876477</v>
+        <v>11.87633</v>
       </c>
       <c r="N65" t="n">
-        <v>12.703374</v>
+        <v>12.703205</v>
       </c>
       <c r="O65" t="n">
-        <v>13.659032</v>
+        <v>13.65884</v>
       </c>
       <c r="P65" t="n">
-        <v>14.957554</v>
+        <v>14.957333</v>
       </c>
       <c r="Q65" t="n">
-        <v>16.324177</v>
+        <v>16.323921</v>
       </c>
       <c r="R65" t="n">
-        <v>17.648031</v>
+        <v>17.647738</v>
       </c>
       <c r="S65" t="n">
-        <v>18.952542</v>
+        <v>18.952203</v>
       </c>
       <c r="T65" t="n">
-        <v>20.226314</v>
+        <v>20.225917</v>
       </c>
       <c r="U65" t="n">
-        <v>21.450813</v>
+        <v>21.45034</v>
       </c>
       <c r="V65" t="n">
-        <v>22.664305</v>
+        <v>22.663721</v>
       </c>
     </row>
     <row r="66">
@@ -5390,58 +5390,58 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3.697833</v>
+        <v>3.697827</v>
       </c>
       <c r="F66" t="n">
-        <v>4.205154</v>
+        <v>4.20514</v>
       </c>
       <c r="G66" t="n">
-        <v>4.785234</v>
+        <v>4.785211</v>
       </c>
       <c r="H66" t="n">
-        <v>5.269134</v>
+        <v>5.269103</v>
       </c>
       <c r="I66" t="n">
-        <v>5.633856</v>
+        <v>5.633817</v>
       </c>
       <c r="J66" t="n">
-        <v>5.843414</v>
+        <v>5.843367</v>
       </c>
       <c r="K66" t="n">
-        <v>5.923965</v>
+        <v>5.92391</v>
       </c>
       <c r="L66" t="n">
-        <v>5.956122</v>
+        <v>5.95606</v>
       </c>
       <c r="M66" t="n">
-        <v>6.136437</v>
+        <v>6.136367</v>
       </c>
       <c r="N66" t="n">
-        <v>6.46786</v>
+        <v>6.467783</v>
       </c>
       <c r="O66" t="n">
-        <v>6.888598</v>
+        <v>6.888516</v>
       </c>
       <c r="P66" t="n">
-        <v>7.502679</v>
+        <v>7.502591</v>
       </c>
       <c r="Q66" t="n">
-        <v>8.163887000000001</v>
+        <v>8.163795</v>
       </c>
       <c r="R66" t="n">
-        <v>8.807207</v>
+        <v>8.807112999999999</v>
       </c>
       <c r="S66" t="n">
-        <v>9.441803</v>
+        <v>9.441708</v>
       </c>
       <c r="T66" t="n">
-        <v>10.067886</v>
+        <v>10.067791</v>
       </c>
       <c r="U66" t="n">
-        <v>10.685474</v>
+        <v>10.685382</v>
       </c>
       <c r="V66" t="n">
-        <v>11.316325</v>
+        <v>11.316239</v>
       </c>
     </row>
     <row r="67">
@@ -5466,58 +5466,58 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1.228039</v>
+        <v>1.228017</v>
       </c>
       <c r="F67" t="n">
-        <v>1.429052</v>
+        <v>1.429007</v>
       </c>
       <c r="G67" t="n">
-        <v>1.702845</v>
+        <v>1.702773</v>
       </c>
       <c r="H67" t="n">
-        <v>1.960661</v>
+        <v>1.960563</v>
       </c>
       <c r="I67" t="n">
-        <v>2.178116</v>
+        <v>2.177995</v>
       </c>
       <c r="J67" t="n">
-        <v>2.336517</v>
+        <v>2.336376</v>
       </c>
       <c r="K67" t="n">
-        <v>2.429881</v>
+        <v>2.429725</v>
       </c>
       <c r="L67" t="n">
-        <v>2.486174</v>
+        <v>2.486003</v>
       </c>
       <c r="M67" t="n">
-        <v>2.588288</v>
+        <v>2.588101</v>
       </c>
       <c r="N67" t="n">
-        <v>2.742783</v>
+        <v>2.742575</v>
       </c>
       <c r="O67" t="n">
-        <v>2.925366</v>
+        <v>2.925137</v>
       </c>
       <c r="P67" t="n">
-        <v>3.18529</v>
+        <v>3.185033</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.463985</v>
+        <v>3.463698</v>
       </c>
       <c r="R67" t="n">
-        <v>3.738924</v>
+        <v>3.738605</v>
       </c>
       <c r="S67" t="n">
-        <v>4.017507</v>
+        <v>4.01715</v>
       </c>
       <c r="T67" t="n">
-        <v>4.298429</v>
+        <v>4.298026</v>
       </c>
       <c r="U67" t="n">
-        <v>4.578026</v>
+        <v>4.577563</v>
       </c>
       <c r="V67" t="n">
-        <v>4.865491</v>
+        <v>4.864943</v>
       </c>
     </row>
     <row r="68">
@@ -5542,58 +5542,58 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.484302</v>
+        <v>2.484304</v>
       </c>
       <c r="F68" t="n">
-        <v>2.935769</v>
+        <v>2.935775</v>
       </c>
       <c r="G68" t="n">
-        <v>3.602331</v>
+        <v>3.602346</v>
       </c>
       <c r="H68" t="n">
-        <v>4.118836</v>
+        <v>4.118863</v>
       </c>
       <c r="I68" t="n">
-        <v>4.359499</v>
+        <v>4.359538</v>
       </c>
       <c r="J68" t="n">
-        <v>4.304253</v>
+        <v>4.304302</v>
       </c>
       <c r="K68" t="n">
-        <v>4.056946</v>
+        <v>4.057002</v>
       </c>
       <c r="L68" t="n">
-        <v>3.744335</v>
+        <v>3.744396</v>
       </c>
       <c r="M68" t="n">
-        <v>3.507736</v>
+        <v>3.507803</v>
       </c>
       <c r="N68" t="n">
-        <v>3.333199</v>
+        <v>3.333272</v>
       </c>
       <c r="O68" t="n">
-        <v>3.185607</v>
+        <v>3.185688</v>
       </c>
       <c r="P68" t="n">
-        <v>3.111047</v>
+        <v>3.111138</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.03996</v>
+        <v>3.040062</v>
       </c>
       <c r="R68" t="n">
-        <v>2.950274</v>
+        <v>2.950388</v>
       </c>
       <c r="S68" t="n">
-        <v>2.848692</v>
+        <v>2.84882</v>
       </c>
       <c r="T68" t="n">
-        <v>2.740217</v>
+        <v>2.740363</v>
       </c>
       <c r="U68" t="n">
-        <v>2.628128</v>
+        <v>2.628297</v>
       </c>
       <c r="V68" t="n">
-        <v>2.518513</v>
+        <v>2.518717</v>
       </c>
     </row>
     <row r="69">
@@ -5624,19 +5624,19 @@
         <v>0.068176</v>
       </c>
       <c r="G69" t="n">
-        <v>0.07252599999999999</v>
+        <v>0.07252500000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>0.07432</v>
+        <v>0.074319</v>
       </c>
       <c r="I69" t="n">
         <v>0.074243</v>
       </c>
       <c r="J69" t="n">
-        <v>0.072972</v>
+        <v>0.07297099999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>0.07061199999999999</v>
+        <v>0.07061099999999999</v>
       </c>
       <c r="L69" t="n">
         <v>0.06743</v>
@@ -5645,31 +5645,31 @@
         <v>0.06492000000000001</v>
       </c>
       <c r="N69" t="n">
-        <v>0.06293</v>
+        <v>0.062929</v>
       </c>
       <c r="O69" t="n">
-        <v>0.060902</v>
+        <v>0.060901</v>
       </c>
       <c r="P69" t="n">
-        <v>0.059797</v>
+        <v>0.059796</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.058191</v>
+        <v>0.05819</v>
       </c>
       <c r="R69" t="n">
-        <v>0.055878</v>
+        <v>0.055877</v>
       </c>
       <c r="S69" t="n">
-        <v>0.053185</v>
+        <v>0.053184</v>
       </c>
       <c r="T69" t="n">
-        <v>0.05029</v>
+        <v>0.050288</v>
       </c>
       <c r="U69" t="n">
-        <v>0.047332</v>
+        <v>0.047331</v>
       </c>
       <c r="V69" t="n">
-        <v>0.044431</v>
+        <v>0.04443</v>
       </c>
     </row>
     <row r="70">
@@ -5694,58 +5694,58 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.92832</v>
+        <v>1.928312</v>
       </c>
       <c r="F70" t="n">
-        <v>2.112942</v>
+        <v>2.112925</v>
       </c>
       <c r="G70" t="n">
-        <v>2.322293</v>
+        <v>2.322268</v>
       </c>
       <c r="H70" t="n">
-        <v>2.454045</v>
+        <v>2.454012</v>
       </c>
       <c r="I70" t="n">
-        <v>2.51623</v>
+        <v>2.51619</v>
       </c>
       <c r="J70" t="n">
-        <v>2.506867</v>
+        <v>2.506822</v>
       </c>
       <c r="K70" t="n">
-        <v>2.444708</v>
+        <v>2.444661</v>
       </c>
       <c r="L70" t="n">
-        <v>2.368016</v>
+        <v>2.367968</v>
       </c>
       <c r="M70" t="n">
-        <v>2.343663</v>
+        <v>2.343615</v>
       </c>
       <c r="N70" t="n">
-        <v>2.353658</v>
+        <v>2.353609</v>
       </c>
       <c r="O70" t="n">
-        <v>2.372146</v>
+        <v>2.372096</v>
       </c>
       <c r="P70" t="n">
-        <v>2.437843</v>
+        <v>2.437792</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.502428</v>
+        <v>2.502377</v>
       </c>
       <c r="R70" t="n">
-        <v>2.550428</v>
+        <v>2.550378</v>
       </c>
       <c r="S70" t="n">
-        <v>2.586065</v>
+        <v>2.586016</v>
       </c>
       <c r="T70" t="n">
-        <v>2.608306</v>
+        <v>2.60826</v>
       </c>
       <c r="U70" t="n">
-        <v>2.6176</v>
+        <v>2.617559</v>
       </c>
       <c r="V70" t="n">
-        <v>2.616425</v>
+        <v>2.616388</v>
       </c>
     </row>
     <row r="71">
@@ -5770,58 +5770,58 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.733523</v>
+        <v>3.733527</v>
       </c>
       <c r="F71" t="n">
-        <v>4.492457</v>
+        <v>4.492468</v>
       </c>
       <c r="G71" t="n">
-        <v>4.977163</v>
+        <v>4.977183</v>
       </c>
       <c r="H71" t="n">
-        <v>5.141346</v>
+        <v>5.141374</v>
       </c>
       <c r="I71" t="n">
-        <v>5.096293</v>
+        <v>5.096329</v>
       </c>
       <c r="J71" t="n">
-        <v>4.933573</v>
+        <v>4.933614</v>
       </c>
       <c r="K71" t="n">
-        <v>4.726147</v>
+        <v>4.726194</v>
       </c>
       <c r="L71" t="n">
-        <v>4.548318</v>
+        <v>4.548373</v>
       </c>
       <c r="M71" t="n">
-        <v>4.472178</v>
+        <v>4.472242</v>
       </c>
       <c r="N71" t="n">
-        <v>4.444584</v>
+        <v>4.444658</v>
       </c>
       <c r="O71" t="n">
-        <v>4.388138</v>
+        <v>4.388222</v>
       </c>
       <c r="P71" t="n">
-        <v>4.366871</v>
+        <v>4.366967</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.298348</v>
+        <v>4.298455</v>
       </c>
       <c r="R71" t="n">
-        <v>4.180833</v>
+        <v>4.180951</v>
       </c>
       <c r="S71" t="n">
-        <v>4.03498</v>
+        <v>4.035111</v>
       </c>
       <c r="T71" t="n">
-        <v>3.862434</v>
+        <v>3.86258</v>
       </c>
       <c r="U71" t="n">
-        <v>3.666503</v>
+        <v>3.666667</v>
       </c>
       <c r="V71" t="n">
-        <v>3.457378</v>
+        <v>3.457569</v>
       </c>
     </row>
     <row r="72">
@@ -5846,58 +5846,58 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2.551492</v>
+        <v>2.551488</v>
       </c>
       <c r="F72" t="n">
-        <v>2.582999</v>
+        <v>2.58299</v>
       </c>
       <c r="G72" t="n">
-        <v>2.642842</v>
+        <v>2.642829</v>
       </c>
       <c r="H72" t="n">
-        <v>2.642132</v>
+        <v>2.642117</v>
       </c>
       <c r="I72" t="n">
-        <v>2.606939</v>
+        <v>2.606921</v>
       </c>
       <c r="J72" t="n">
-        <v>2.528841</v>
+        <v>2.528823</v>
       </c>
       <c r="K72" t="n">
-        <v>2.414224</v>
+        <v>2.414206</v>
       </c>
       <c r="L72" t="n">
-        <v>2.287952</v>
+        <v>2.287936</v>
       </c>
       <c r="M72" t="n">
-        <v>2.207502</v>
+        <v>2.207488</v>
       </c>
       <c r="N72" t="n">
-        <v>2.150614</v>
+        <v>2.150601</v>
       </c>
       <c r="O72" t="n">
-        <v>2.095153</v>
+        <v>2.095142</v>
       </c>
       <c r="P72" t="n">
-        <v>2.085516</v>
+        <v>2.085505</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.080648</v>
+        <v>2.080639</v>
       </c>
       <c r="R72" t="n">
-        <v>2.064523</v>
+        <v>2.064516</v>
       </c>
       <c r="S72" t="n">
-        <v>2.03723</v>
+        <v>2.037226</v>
       </c>
       <c r="T72" t="n">
         <v>1.998735</v>
       </c>
       <c r="U72" t="n">
-        <v>1.951685</v>
+        <v>1.951689</v>
       </c>
       <c r="V72" t="n">
-        <v>1.89931</v>
+        <v>1.899319</v>
       </c>
     </row>
     <row r="73">
@@ -5922,58 +5922,58 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>12.892398</v>
+        <v>12.892427</v>
       </c>
       <c r="F73" t="n">
-        <v>10.830671</v>
+        <v>10.83072</v>
       </c>
       <c r="G73" t="n">
-        <v>8.410893</v>
+        <v>8.410951000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>6.738893</v>
+        <v>6.738956</v>
       </c>
       <c r="I73" t="n">
-        <v>5.844246</v>
+        <v>5.844315</v>
       </c>
       <c r="J73" t="n">
-        <v>5.33021</v>
+        <v>5.330286</v>
       </c>
       <c r="K73" t="n">
-        <v>4.933021</v>
+        <v>4.933106</v>
       </c>
       <c r="L73" t="n">
-        <v>4.534971</v>
+        <v>4.535063</v>
       </c>
       <c r="M73" t="n">
-        <v>4.214906</v>
+        <v>4.215005</v>
       </c>
       <c r="N73" t="n">
-        <v>3.954051</v>
+        <v>3.954158</v>
       </c>
       <c r="O73" t="n">
-        <v>3.719685</v>
+        <v>3.719801</v>
       </c>
       <c r="P73" t="n">
-        <v>3.568281</v>
+        <v>3.568409</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.414064</v>
+        <v>3.414205</v>
       </c>
       <c r="R73" t="n">
-        <v>3.233817</v>
+        <v>3.23397</v>
       </c>
       <c r="S73" t="n">
-        <v>3.04299</v>
+        <v>3.043158</v>
       </c>
       <c r="T73" t="n">
-        <v>2.84758</v>
+        <v>2.847765</v>
       </c>
       <c r="U73" t="n">
-        <v>2.653583</v>
+        <v>2.653792</v>
       </c>
       <c r="V73" t="n">
-        <v>2.469543</v>
+        <v>2.469786</v>
       </c>
     </row>
     <row r="74">
@@ -6004,7 +6004,7 @@
         <v>0.040493</v>
       </c>
       <c r="G74" t="n">
-        <v>0.04448</v>
+        <v>0.044479</v>
       </c>
       <c r="H74" t="n">
         <v>0.044893</v>
@@ -6013,7 +6013,7 @@
         <v>0.043476</v>
       </c>
       <c r="J74" t="n">
-        <v>0.041154</v>
+        <v>0.041153</v>
       </c>
       <c r="K74" t="n">
         <v>0.038308</v>
@@ -6022,7 +6022,7 @@
         <v>0.035316</v>
       </c>
       <c r="M74" t="n">
-        <v>0.033127</v>
+        <v>0.033126</v>
       </c>
       <c r="N74" t="n">
         <v>0.031508</v>
@@ -6049,7 +6049,7 @@
         <v>0.023137</v>
       </c>
       <c r="V74" t="n">
-        <v>0.021877</v>
+        <v>0.021876</v>
       </c>
     </row>
     <row r="75">
@@ -6074,58 +6074,58 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.794182</v>
+        <v>1.79418</v>
       </c>
       <c r="F75" t="n">
-        <v>1.932394</v>
+        <v>1.932391</v>
       </c>
       <c r="G75" t="n">
-        <v>2.154221</v>
+        <v>2.154217</v>
       </c>
       <c r="H75" t="n">
-        <v>2.171939</v>
+        <v>2.171934</v>
       </c>
       <c r="I75" t="n">
-        <v>2.130399</v>
+        <v>2.130393</v>
       </c>
       <c r="J75" t="n">
-        <v>2.055282</v>
+        <v>2.055275</v>
       </c>
       <c r="K75" t="n">
-        <v>1.950666</v>
+        <v>1.950659</v>
       </c>
       <c r="L75" t="n">
-        <v>1.827032</v>
+        <v>1.827024</v>
       </c>
       <c r="M75" t="n">
-        <v>1.719351</v>
+        <v>1.719342</v>
       </c>
       <c r="N75" t="n">
-        <v>1.634625</v>
+        <v>1.634616</v>
       </c>
       <c r="O75" t="n">
-        <v>1.535254</v>
+        <v>1.535245</v>
       </c>
       <c r="P75" t="n">
-        <v>1.466479</v>
+        <v>1.46647</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.381533</v>
+        <v>1.381523</v>
       </c>
       <c r="R75" t="n">
-        <v>1.273585</v>
+        <v>1.273576</v>
       </c>
       <c r="S75" t="n">
-        <v>1.174905</v>
+        <v>1.174896</v>
       </c>
       <c r="T75" t="n">
-        <v>1.087311</v>
+        <v>1.087302</v>
       </c>
       <c r="U75" t="n">
-        <v>1.016182</v>
+        <v>1.016173</v>
       </c>
       <c r="V75" t="n">
-        <v>0.957126</v>
+        <v>0.957117</v>
       </c>
     </row>
     <row r="76">
@@ -6150,58 +6150,58 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11.027737</v>
+        <v>11.027733</v>
       </c>
       <c r="F76" t="n">
-        <v>12.231787</v>
+        <v>12.231779</v>
       </c>
       <c r="G76" t="n">
-        <v>11.119323</v>
+        <v>11.119311</v>
       </c>
       <c r="H76" t="n">
-        <v>9.505307999999999</v>
+        <v>9.505291</v>
       </c>
       <c r="I76" t="n">
-        <v>8.556706999999999</v>
+        <v>8.556685999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>8.141337999999999</v>
+        <v>8.141313</v>
       </c>
       <c r="K76" t="n">
-        <v>7.913433</v>
+        <v>7.913404</v>
       </c>
       <c r="L76" t="n">
-        <v>7.720622</v>
+        <v>7.720589</v>
       </c>
       <c r="M76" t="n">
-        <v>7.504614</v>
+        <v>7.504577</v>
       </c>
       <c r="N76" t="n">
-        <v>7.315173</v>
+        <v>7.315132</v>
       </c>
       <c r="O76" t="n">
-        <v>6.900394</v>
+        <v>6.90035</v>
       </c>
       <c r="P76" t="n">
-        <v>6.516069</v>
+        <v>6.516022</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.987424</v>
+        <v>5.987374</v>
       </c>
       <c r="R76" t="n">
-        <v>5.339827</v>
+        <v>5.339777</v>
       </c>
       <c r="S76" t="n">
-        <v>4.778361</v>
+        <v>4.77831</v>
       </c>
       <c r="T76" t="n">
-        <v>4.327986</v>
+        <v>4.327935</v>
       </c>
       <c r="U76" t="n">
-        <v>3.99503</v>
+        <v>3.994978</v>
       </c>
       <c r="V76" t="n">
-        <v>3.729803</v>
+        <v>3.72975</v>
       </c>
     </row>
     <row r="77">
@@ -6226,58 +6226,58 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3.40059</v>
+        <v>3.400588</v>
       </c>
       <c r="F77" t="n">
-        <v>4.159162</v>
+        <v>4.159159</v>
       </c>
       <c r="G77" t="n">
-        <v>4.867765</v>
+        <v>4.867762</v>
       </c>
       <c r="H77" t="n">
-        <v>4.773809</v>
+        <v>4.773805</v>
       </c>
       <c r="I77" t="n">
-        <v>4.347311</v>
+        <v>4.347306</v>
       </c>
       <c r="J77" t="n">
-        <v>3.865399</v>
+        <v>3.865393</v>
       </c>
       <c r="K77" t="n">
-        <v>3.448818</v>
+        <v>3.44881</v>
       </c>
       <c r="L77" t="n">
-        <v>3.130792</v>
+        <v>3.130784</v>
       </c>
       <c r="M77" t="n">
-        <v>2.921755</v>
+        <v>2.921746</v>
       </c>
       <c r="N77" t="n">
-        <v>2.78056</v>
+        <v>2.780551</v>
       </c>
       <c r="O77" t="n">
-        <v>2.608226</v>
+        <v>2.608217</v>
       </c>
       <c r="P77" t="n">
-        <v>2.48082</v>
+        <v>2.48081</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.32931</v>
+        <v>2.329301</v>
       </c>
       <c r="R77" t="n">
-        <v>2.148504</v>
+        <v>2.148495</v>
       </c>
       <c r="S77" t="n">
-        <v>1.991444</v>
+        <v>1.991434</v>
       </c>
       <c r="T77" t="n">
-        <v>1.85654</v>
+        <v>1.856531</v>
       </c>
       <c r="U77" t="n">
-        <v>1.748821</v>
+        <v>1.748812</v>
       </c>
       <c r="V77" t="n">
-        <v>1.657922</v>
+        <v>1.657913</v>
       </c>
     </row>
     <row r="78">
@@ -6302,58 +6302,58 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>65.607697</v>
+        <v>65.60771699999999</v>
       </c>
       <c r="F78" t="n">
-        <v>61.380712</v>
+        <v>61.380735</v>
       </c>
       <c r="G78" t="n">
-        <v>58.043771</v>
+        <v>58.04379</v>
       </c>
       <c r="H78" t="n">
-        <v>52.939615</v>
+        <v>52.939629</v>
       </c>
       <c r="I78" t="n">
-        <v>50.050095</v>
+        <v>50.050105</v>
       </c>
       <c r="J78" t="n">
-        <v>48.620112</v>
+        <v>48.620121</v>
       </c>
       <c r="K78" t="n">
-        <v>47.687092</v>
+        <v>47.687101</v>
       </c>
       <c r="L78" t="n">
-        <v>46.660089</v>
+        <v>46.660098</v>
       </c>
       <c r="M78" t="n">
-        <v>46.022018</v>
+        <v>46.022029</v>
       </c>
       <c r="N78" t="n">
-        <v>45.771761</v>
+        <v>45.771773</v>
       </c>
       <c r="O78" t="n">
-        <v>44.717826</v>
+        <v>44.71784</v>
       </c>
       <c r="P78" t="n">
-        <v>44.168582</v>
+        <v>44.168597</v>
       </c>
       <c r="Q78" t="n">
-        <v>42.873025</v>
+        <v>42.87304</v>
       </c>
       <c r="R78" t="n">
-        <v>40.650598</v>
+        <v>40.650613</v>
       </c>
       <c r="S78" t="n">
-        <v>38.517228</v>
+        <v>38.517245</v>
       </c>
       <c r="T78" t="n">
-        <v>36.509649</v>
+        <v>36.509667</v>
       </c>
       <c r="U78" t="n">
-        <v>34.781215</v>
+        <v>34.781234</v>
       </c>
       <c r="V78" t="n">
-        <v>33.171228</v>
+        <v>33.171249</v>
       </c>
     </row>
     <row r="79">
@@ -6378,58 +6378,58 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3.295237</v>
+        <v>3.295233</v>
       </c>
       <c r="F79" t="n">
-        <v>4.643638</v>
+        <v>4.643633</v>
       </c>
       <c r="G79" t="n">
-        <v>6.76771</v>
+        <v>6.767705</v>
       </c>
       <c r="H79" t="n">
-        <v>8.39662</v>
+        <v>8.396615000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>9.507705</v>
+        <v>9.5077</v>
       </c>
       <c r="J79" t="n">
-        <v>10.057701</v>
+        <v>10.057695</v>
       </c>
       <c r="K79" t="n">
-        <v>10.146932</v>
+        <v>10.146925</v>
       </c>
       <c r="L79" t="n">
-        <v>9.929907999999999</v>
+        <v>9.929900999999999</v>
       </c>
       <c r="M79" t="n">
-        <v>9.679952</v>
+        <v>9.679945</v>
       </c>
       <c r="N79" t="n">
-        <v>9.488288000000001</v>
+        <v>9.48828</v>
       </c>
       <c r="O79" t="n">
-        <v>9.164209</v>
+        <v>9.164199999999999</v>
       </c>
       <c r="P79" t="n">
-        <v>8.997681999999999</v>
+        <v>8.997672</v>
       </c>
       <c r="Q79" t="n">
-        <v>8.715657</v>
+        <v>8.715647000000001</v>
       </c>
       <c r="R79" t="n">
-        <v>8.259014000000001</v>
+        <v>8.259003999999999</v>
       </c>
       <c r="S79" t="n">
-        <v>7.82002</v>
+        <v>7.820011</v>
       </c>
       <c r="T79" t="n">
-        <v>7.404717</v>
+        <v>7.404708</v>
       </c>
       <c r="U79" t="n">
-        <v>7.049981</v>
+        <v>7.049972</v>
       </c>
       <c r="V79" t="n">
-        <v>6.728826</v>
+        <v>6.728817</v>
       </c>
     </row>
     <row r="80">
@@ -6454,58 +6454,58 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5.757384</v>
+        <v>5.757385</v>
       </c>
       <c r="F80" t="n">
-        <v>5.287513</v>
+        <v>5.287512</v>
       </c>
       <c r="G80" t="n">
-        <v>5.09992</v>
+        <v>5.099919</v>
       </c>
       <c r="H80" t="n">
-        <v>4.874996</v>
+        <v>4.874994</v>
       </c>
       <c r="I80" t="n">
-        <v>4.861585</v>
+        <v>4.861582</v>
       </c>
       <c r="J80" t="n">
-        <v>4.968514</v>
+        <v>4.968511</v>
       </c>
       <c r="K80" t="n">
-        <v>5.108599</v>
+        <v>5.108596</v>
       </c>
       <c r="L80" t="n">
-        <v>5.215944</v>
+        <v>5.21594</v>
       </c>
       <c r="M80" t="n">
-        <v>5.339657</v>
+        <v>5.339653</v>
       </c>
       <c r="N80" t="n">
-        <v>5.488828</v>
+        <v>5.488824</v>
       </c>
       <c r="O80" t="n">
-        <v>5.539077</v>
+        <v>5.539074</v>
       </c>
       <c r="P80" t="n">
-        <v>5.665529</v>
+        <v>5.665525</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.700047</v>
+        <v>5.700044</v>
       </c>
       <c r="R80" t="n">
-        <v>5.58971</v>
+        <v>5.589708</v>
       </c>
       <c r="S80" t="n">
-        <v>5.453183</v>
+        <v>5.453181</v>
       </c>
       <c r="T80" t="n">
-        <v>5.297024</v>
+        <v>5.297022</v>
       </c>
       <c r="U80" t="n">
-        <v>5.151257</v>
+        <v>5.151256</v>
       </c>
       <c r="V80" t="n">
-        <v>4.999295</v>
+        <v>4.999294</v>
       </c>
     </row>
     <row r="81">
@@ -6530,58 +6530,58 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.626493</v>
+        <v>1.626487</v>
       </c>
       <c r="F81" t="n">
-        <v>2.379923</v>
+        <v>2.379913</v>
       </c>
       <c r="G81" t="n">
-        <v>3.547947</v>
+        <v>3.547934</v>
       </c>
       <c r="H81" t="n">
-        <v>4.515859</v>
+        <v>4.515843</v>
       </c>
       <c r="I81" t="n">
-        <v>5.276908</v>
+        <v>5.276889</v>
       </c>
       <c r="J81" t="n">
-        <v>5.780535</v>
+        <v>5.780513</v>
       </c>
       <c r="K81" t="n">
-        <v>6.050756</v>
+        <v>6.05073</v>
       </c>
       <c r="L81" t="n">
-        <v>6.172617</v>
+        <v>6.172587</v>
       </c>
       <c r="M81" t="n">
-        <v>6.29307</v>
+        <v>6.293035</v>
       </c>
       <c r="N81" t="n">
-        <v>6.457184</v>
+        <v>6.457144</v>
       </c>
       <c r="O81" t="n">
-        <v>6.599798</v>
+        <v>6.599754</v>
       </c>
       <c r="P81" t="n">
-        <v>6.903844</v>
+        <v>6.903795</v>
       </c>
       <c r="Q81" t="n">
-        <v>7.156525</v>
+        <v>7.156471</v>
       </c>
       <c r="R81" t="n">
-        <v>7.27175</v>
+        <v>7.271693</v>
       </c>
       <c r="S81" t="n">
-        <v>7.39754</v>
+        <v>7.39748</v>
       </c>
       <c r="T81" t="n">
-        <v>7.532548</v>
+        <v>7.532483</v>
       </c>
       <c r="U81" t="n">
-        <v>7.714249</v>
+        <v>7.714179</v>
       </c>
       <c r="V81" t="n">
-        <v>7.923533</v>
+        <v>7.923457</v>
       </c>
     </row>
     <row r="82">
@@ -6606,58 +6606,58 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>20.93378</v>
+        <v>20.933787</v>
       </c>
       <c r="F82" t="n">
-        <v>22.708628</v>
+        <v>22.708639</v>
       </c>
       <c r="G82" t="n">
-        <v>24.650687</v>
+        <v>24.650699</v>
       </c>
       <c r="H82" t="n">
-        <v>25.037791</v>
+        <v>25.037805</v>
       </c>
       <c r="I82" t="n">
-        <v>25.345649</v>
+        <v>25.345665</v>
       </c>
       <c r="J82" t="n">
-        <v>25.559125</v>
+        <v>25.559144</v>
       </c>
       <c r="K82" t="n">
-        <v>25.441963</v>
+        <v>25.441985</v>
       </c>
       <c r="L82" t="n">
-        <v>24.993074</v>
+        <v>24.993099</v>
       </c>
       <c r="M82" t="n">
-        <v>24.580368</v>
+        <v>24.580396</v>
       </c>
       <c r="N82" t="n">
-        <v>24.286975</v>
+        <v>24.287006</v>
       </c>
       <c r="O82" t="n">
-        <v>23.545013</v>
+        <v>23.545046</v>
       </c>
       <c r="P82" t="n">
-        <v>23.124702</v>
+        <v>23.124738</v>
       </c>
       <c r="Q82" t="n">
-        <v>22.358412</v>
+        <v>22.35845</v>
       </c>
       <c r="R82" t="n">
-        <v>21.125401</v>
+        <v>21.12544</v>
       </c>
       <c r="S82" t="n">
-        <v>19.930629</v>
+        <v>19.930668</v>
       </c>
       <c r="T82" t="n">
-        <v>18.796678</v>
+        <v>18.796718</v>
       </c>
       <c r="U82" t="n">
-        <v>17.820393</v>
+        <v>17.820434</v>
       </c>
       <c r="V82" t="n">
-        <v>16.936083</v>
+        <v>16.936125</v>
       </c>
     </row>
     <row r="83">
@@ -6682,58 +6682,58 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>34.260917</v>
+        <v>34.260909</v>
       </c>
       <c r="F83" t="n">
-        <v>49.450721</v>
+        <v>49.450717</v>
       </c>
       <c r="G83" t="n">
-        <v>71.13917499999999</v>
+        <v>71.139183</v>
       </c>
       <c r="H83" t="n">
-        <v>86.515401</v>
+        <v>86.515422</v>
       </c>
       <c r="I83" t="n">
-        <v>95.951302</v>
+        <v>95.951335</v>
       </c>
       <c r="J83" t="n">
-        <v>99.782307</v>
+        <v>99.78234999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>99.444524</v>
+        <v>99.444575</v>
       </c>
       <c r="L83" t="n">
-        <v>96.70450200000001</v>
+        <v>96.70455800000001</v>
       </c>
       <c r="M83" t="n">
-        <v>94.004295</v>
+        <v>94.004357</v>
       </c>
       <c r="N83" t="n">
-        <v>91.9684</v>
+        <v>91.968467</v>
       </c>
       <c r="O83" t="n">
-        <v>88.540978</v>
+        <v>88.541049</v>
       </c>
       <c r="P83" t="n">
-        <v>86.565971</v>
+        <v>86.56604799999999</v>
       </c>
       <c r="Q83" t="n">
-        <v>83.489593</v>
+        <v>83.48967500000001</v>
       </c>
       <c r="R83" t="n">
-        <v>78.79227400000001</v>
+        <v>78.79235799999999</v>
       </c>
       <c r="S83" t="n">
-        <v>74.300788</v>
+        <v>74.30087399999999</v>
       </c>
       <c r="T83" t="n">
-        <v>70.066627</v>
+        <v>70.066715</v>
       </c>
       <c r="U83" t="n">
-        <v>66.4572</v>
+        <v>66.457291</v>
       </c>
       <c r="V83" t="n">
-        <v>63.247911</v>
+        <v>63.248004</v>
       </c>
     </row>
     <row r="84">
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>13.604363</v>
+        <v>13.604364</v>
       </c>
       <c r="F86" t="n">
-        <v>14.551186</v>
+        <v>14.551187</v>
       </c>
       <c r="G86" t="n">
         <v>14.888334</v>
@@ -6922,46 +6922,46 @@
         <v>14.444201</v>
       </c>
       <c r="I86" t="n">
-        <v>13.872086</v>
+        <v>13.872085</v>
       </c>
       <c r="J86" t="n">
-        <v>13.086792</v>
+        <v>13.08679</v>
       </c>
       <c r="K86" t="n">
-        <v>12.246906</v>
+        <v>12.246903</v>
       </c>
       <c r="L86" t="n">
-        <v>11.332892</v>
+        <v>11.332887</v>
       </c>
       <c r="M86" t="n">
-        <v>10.622315</v>
+        <v>10.622309</v>
       </c>
       <c r="N86" t="n">
-        <v>10.109971</v>
+        <v>10.109964</v>
       </c>
       <c r="O86" t="n">
-        <v>9.648579</v>
+        <v>9.648569999999999</v>
       </c>
       <c r="P86" t="n">
-        <v>9.277521999999999</v>
+        <v>9.277512</v>
       </c>
       <c r="Q86" t="n">
-        <v>8.781734</v>
+        <v>8.781723</v>
       </c>
       <c r="R86" t="n">
-        <v>8.182544</v>
+        <v>8.182531000000001</v>
       </c>
       <c r="S86" t="n">
-        <v>7.606453</v>
+        <v>7.606439</v>
       </c>
       <c r="T86" t="n">
-        <v>7.061123</v>
+        <v>7.061108</v>
       </c>
       <c r="U86" t="n">
-        <v>6.551312</v>
+        <v>6.551296</v>
       </c>
       <c r="V86" t="n">
-        <v>6.064974</v>
+        <v>6.064957</v>
       </c>
     </row>
     <row r="87">
@@ -6986,16 +6986,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.870623</v>
+        <v>1.870622</v>
       </c>
       <c r="F87" t="n">
-        <v>2.250611</v>
+        <v>2.25061</v>
       </c>
       <c r="G87" t="n">
-        <v>2.646658</v>
+        <v>2.646657</v>
       </c>
       <c r="H87" t="n">
-        <v>2.886668</v>
+        <v>2.886667</v>
       </c>
       <c r="I87" t="n">
         <v>3.044577</v>
@@ -7013,31 +7013,31 @@
         <v>2.970346</v>
       </c>
       <c r="N87" t="n">
-        <v>2.946134</v>
+        <v>2.946133</v>
       </c>
       <c r="O87" t="n">
-        <v>2.914525</v>
+        <v>2.914524</v>
       </c>
       <c r="P87" t="n">
-        <v>2.892401</v>
+        <v>2.8924</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.815941</v>
+        <v>2.815939</v>
       </c>
       <c r="R87" t="n">
-        <v>2.690984</v>
+        <v>2.690982</v>
       </c>
       <c r="S87" t="n">
-        <v>2.559087</v>
+        <v>2.559085</v>
       </c>
       <c r="T87" t="n">
-        <v>2.425245</v>
+        <v>2.425243</v>
       </c>
       <c r="U87" t="n">
-        <v>2.296473</v>
+        <v>2.296471</v>
       </c>
       <c r="V87" t="n">
-        <v>2.172055</v>
+        <v>2.172052</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>29.548964</v>
+        <v>29.548973</v>
       </c>
       <c r="F88" t="n">
-        <v>28.798757</v>
+        <v>28.798768</v>
       </c>
       <c r="G88" t="n">
-        <v>27.78512</v>
+        <v>27.785129</v>
       </c>
       <c r="H88" t="n">
-        <v>26.739919</v>
+        <v>26.739926</v>
       </c>
       <c r="I88" t="n">
-        <v>26.305046</v>
+        <v>26.305053</v>
       </c>
       <c r="J88" t="n">
-        <v>25.901293</v>
+        <v>25.901301</v>
       </c>
       <c r="K88" t="n">
-        <v>25.520502</v>
+        <v>25.520512</v>
       </c>
       <c r="L88" t="n">
-        <v>24.915845</v>
+        <v>24.915856</v>
       </c>
       <c r="M88" t="n">
-        <v>24.590972</v>
+        <v>24.590986</v>
       </c>
       <c r="N88" t="n">
-        <v>24.573055</v>
+        <v>24.573072</v>
       </c>
       <c r="O88" t="n">
-        <v>24.53628</v>
+        <v>24.5363</v>
       </c>
       <c r="P88" t="n">
-        <v>24.609441</v>
+        <v>24.609464</v>
       </c>
       <c r="Q88" t="n">
-        <v>24.253066</v>
+        <v>24.253092</v>
       </c>
       <c r="R88" t="n">
-        <v>23.506981</v>
+        <v>23.507008</v>
       </c>
       <c r="S88" t="n">
-        <v>22.711282</v>
+        <v>22.711312</v>
       </c>
       <c r="T88" t="n">
-        <v>21.932057</v>
+        <v>21.932088</v>
       </c>
       <c r="U88" t="n">
-        <v>21.219509</v>
+        <v>21.219542</v>
       </c>
       <c r="V88" t="n">
-        <v>20.550758</v>
+        <v>20.550793</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5.455169</v>
+        <v>5.455171</v>
       </c>
       <c r="F89" t="n">
-        <v>5.644684</v>
+        <v>5.644689</v>
       </c>
       <c r="G89" t="n">
-        <v>5.863674</v>
+        <v>5.86368</v>
       </c>
       <c r="H89" t="n">
-        <v>5.809357</v>
+        <v>5.809366</v>
       </c>
       <c r="I89" t="n">
-        <v>5.705412</v>
+        <v>5.705422</v>
       </c>
       <c r="J89" t="n">
-        <v>5.507356</v>
+        <v>5.507368</v>
       </c>
       <c r="K89" t="n">
-        <v>5.281127</v>
+        <v>5.281139</v>
       </c>
       <c r="L89" t="n">
-        <v>5.013743</v>
+        <v>5.013757</v>
       </c>
       <c r="M89" t="n">
-        <v>4.823332</v>
+        <v>4.823346</v>
       </c>
       <c r="N89" t="n">
-        <v>4.718979</v>
+        <v>4.718995</v>
       </c>
       <c r="O89" t="n">
-        <v>4.642009</v>
+        <v>4.642026</v>
       </c>
       <c r="P89" t="n">
-        <v>4.618537</v>
+        <v>4.618555</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.540144</v>
+        <v>4.540162</v>
       </c>
       <c r="R89" t="n">
-        <v>4.403982</v>
+        <v>4.404001</v>
       </c>
       <c r="S89" t="n">
-        <v>4.268873</v>
+        <v>4.268893</v>
       </c>
       <c r="T89" t="n">
-        <v>4.140099</v>
+        <v>4.14012</v>
       </c>
       <c r="U89" t="n">
-        <v>4.024711</v>
+        <v>4.024733</v>
       </c>
       <c r="V89" t="n">
-        <v>3.920253</v>
+        <v>3.920276</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>12.971544</v>
+        <v>12.971539</v>
       </c>
       <c r="F90" t="n">
-        <v>13.582758</v>
+        <v>13.582748</v>
       </c>
       <c r="G90" t="n">
-        <v>14.399395</v>
+        <v>14.399381</v>
       </c>
       <c r="H90" t="n">
-        <v>14.673187</v>
+        <v>14.673171</v>
       </c>
       <c r="I90" t="n">
-        <v>14.754507</v>
+        <v>14.754489</v>
       </c>
       <c r="J90" t="n">
-        <v>14.458863</v>
+        <v>14.458843</v>
       </c>
       <c r="K90" t="n">
-        <v>13.964255</v>
+        <v>13.964235</v>
       </c>
       <c r="L90" t="n">
-        <v>13.299211</v>
+        <v>13.29919</v>
       </c>
       <c r="M90" t="n">
-        <v>12.819572</v>
+        <v>12.819551</v>
       </c>
       <c r="N90" t="n">
-        <v>12.519332</v>
+        <v>12.519309</v>
       </c>
       <c r="O90" t="n">
-        <v>12.216456</v>
+        <v>12.216434</v>
       </c>
       <c r="P90" t="n">
-        <v>11.974882</v>
+        <v>11.974859</v>
       </c>
       <c r="Q90" t="n">
-        <v>11.546986</v>
+        <v>11.546963</v>
       </c>
       <c r="R90" t="n">
-        <v>10.9739</v>
+        <v>10.973877</v>
       </c>
       <c r="S90" t="n">
-        <v>10.428103</v>
+        <v>10.42808</v>
       </c>
       <c r="T90" t="n">
-        <v>9.924061</v>
+        <v>9.924039</v>
       </c>
       <c r="U90" t="n">
-        <v>9.468223999999999</v>
+        <v>9.468202</v>
       </c>
       <c r="V90" t="n">
-        <v>9.043142</v>
+        <v>9.043120999999999</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3.72694</v>
+        <v>3.726938</v>
       </c>
       <c r="F91" t="n">
-        <v>3.989941</v>
+        <v>3.989938</v>
       </c>
       <c r="G91" t="n">
-        <v>4.131886</v>
+        <v>4.131881</v>
       </c>
       <c r="H91" t="n">
-        <v>3.991418</v>
+        <v>3.991411</v>
       </c>
       <c r="I91" t="n">
-        <v>3.761842</v>
+        <v>3.761833</v>
       </c>
       <c r="J91" t="n">
-        <v>3.454717</v>
+        <v>3.454707</v>
       </c>
       <c r="K91" t="n">
-        <v>3.143938</v>
+        <v>3.143927</v>
       </c>
       <c r="L91" t="n">
-        <v>2.83742</v>
+        <v>2.837408</v>
       </c>
       <c r="M91" t="n">
-        <v>2.598114</v>
+        <v>2.598101</v>
       </c>
       <c r="N91" t="n">
-        <v>2.417693</v>
+        <v>2.417679</v>
       </c>
       <c r="O91" t="n">
-        <v>2.259612</v>
+        <v>2.259598</v>
       </c>
       <c r="P91" t="n">
-        <v>2.131299</v>
+        <v>2.131284</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.982514</v>
+        <v>1.982498</v>
       </c>
       <c r="R91" t="n">
-        <v>1.826319</v>
+        <v>1.826303</v>
       </c>
       <c r="S91" t="n">
-        <v>1.69429</v>
+        <v>1.694273</v>
       </c>
       <c r="T91" t="n">
-        <v>1.586957</v>
+        <v>1.58694</v>
       </c>
       <c r="U91" t="n">
-        <v>1.502146</v>
+        <v>1.502129</v>
       </c>
       <c r="V91" t="n">
-        <v>1.433783</v>
+        <v>1.433767</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2.086503</v>
+        <v>2.086502</v>
       </c>
       <c r="F92" t="n">
-        <v>2.252926</v>
+        <v>2.252923</v>
       </c>
       <c r="G92" t="n">
-        <v>2.408693</v>
+        <v>2.408689</v>
       </c>
       <c r="H92" t="n">
-        <v>2.392102</v>
+        <v>2.392096</v>
       </c>
       <c r="I92" t="n">
-        <v>2.308816</v>
+        <v>2.30881</v>
       </c>
       <c r="J92" t="n">
-        <v>2.166853</v>
+        <v>2.166845</v>
       </c>
       <c r="K92" t="n">
-        <v>2.008521</v>
+        <v>2.008513</v>
       </c>
       <c r="L92" t="n">
-        <v>1.836014</v>
+        <v>1.836006</v>
       </c>
       <c r="M92" t="n">
-        <v>1.700138</v>
+        <v>1.700129</v>
       </c>
       <c r="N92" t="n">
-        <v>1.597044</v>
+        <v>1.597034</v>
       </c>
       <c r="O92" t="n">
-        <v>1.502915</v>
+        <v>1.502905</v>
       </c>
       <c r="P92" t="n">
-        <v>1.424298</v>
+        <v>1.424287</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.331175</v>
+        <v>1.331163</v>
       </c>
       <c r="R92" t="n">
-        <v>1.230275</v>
+        <v>1.230264</v>
       </c>
       <c r="S92" t="n">
-        <v>1.141767</v>
+        <v>1.141755</v>
       </c>
       <c r="T92" t="n">
-        <v>1.065728</v>
+        <v>1.065716</v>
       </c>
       <c r="U92" t="n">
-        <v>1.001053</v>
+        <v>1.001041</v>
       </c>
       <c r="V92" t="n">
-        <v>0.944655</v>
+        <v>0.944644</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.456287</v>
+        <v>0.456286</v>
       </c>
       <c r="F93" t="n">
         <v>0.517819</v>
       </c>
       <c r="G93" t="n">
-        <v>0.589506</v>
+        <v>0.5895049999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>0.640601</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="I93" t="n">
-        <v>0.679029</v>
+        <v>0.679028</v>
       </c>
       <c r="J93" t="n">
-        <v>0.690997</v>
+        <v>0.6909960000000001</v>
       </c>
       <c r="K93" t="n">
-        <v>0.682851</v>
+        <v>0.68285</v>
       </c>
       <c r="L93" t="n">
-        <v>0.656824</v>
+        <v>0.656823</v>
       </c>
       <c r="M93" t="n">
-        <v>0.631937</v>
+        <v>0.6319360000000001</v>
       </c>
       <c r="N93" t="n">
-        <v>0.611862</v>
+        <v>0.611861</v>
       </c>
       <c r="O93" t="n">
-        <v>0.591386</v>
+        <v>0.591385</v>
       </c>
       <c r="P93" t="n">
-        <v>0.57523</v>
+        <v>0.575228</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.5509540000000001</v>
+        <v>0.550953</v>
       </c>
       <c r="R93" t="n">
-        <v>0.519302</v>
+        <v>0.519301</v>
       </c>
       <c r="S93" t="n">
-        <v>0.487776</v>
+        <v>0.487775</v>
       </c>
       <c r="T93" t="n">
-        <v>0.457174</v>
+        <v>0.457172</v>
       </c>
       <c r="U93" t="n">
-        <v>0.428792</v>
+        <v>0.42879</v>
       </c>
       <c r="V93" t="n">
-        <v>0.402874</v>
+        <v>0.402872</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>83.433087</v>
+        <v>83.433099</v>
       </c>
       <c r="F94" t="n">
-        <v>95.901324</v>
+        <v>95.901355</v>
       </c>
       <c r="G94" t="n">
-        <v>103.919541</v>
+        <v>103.919591</v>
       </c>
       <c r="H94" t="n">
-        <v>104.988868</v>
+        <v>104.988935</v>
       </c>
       <c r="I94" t="n">
-        <v>103.442048</v>
+        <v>103.442128</v>
       </c>
       <c r="J94" t="n">
-        <v>99.36509100000001</v>
+        <v>99.36518100000001</v>
       </c>
       <c r="K94" t="n">
-        <v>94.49352</v>
+        <v>94.493619</v>
       </c>
       <c r="L94" t="n">
-        <v>88.836381</v>
+        <v>88.83648599999999</v>
       </c>
       <c r="M94" t="n">
-        <v>84.40818899999999</v>
+        <v>84.408299</v>
       </c>
       <c r="N94" t="n">
-        <v>81.175909</v>
+        <v>81.176025</v>
       </c>
       <c r="O94" t="n">
-        <v>78.081289</v>
+        <v>78.081408</v>
       </c>
       <c r="P94" t="n">
-        <v>75.57516099999999</v>
+        <v>75.575283</v>
       </c>
       <c r="Q94" t="n">
-        <v>72.005803</v>
+        <v>72.005926</v>
       </c>
       <c r="R94" t="n">
-        <v>67.544493</v>
+        <v>67.54461499999999</v>
       </c>
       <c r="S94" t="n">
-        <v>63.238348</v>
+        <v>63.238466</v>
       </c>
       <c r="T94" t="n">
-        <v>59.233459</v>
+        <v>59.233574</v>
       </c>
       <c r="U94" t="n">
-        <v>55.71863</v>
+        <v>55.718742</v>
       </c>
       <c r="V94" t="n">
-        <v>52.670552</v>
+        <v>52.670661</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>21.910295</v>
+        <v>21.91028</v>
       </c>
       <c r="F95" t="n">
-        <v>25.231112</v>
+        <v>25.231086</v>
       </c>
       <c r="G95" t="n">
-        <v>27.77946</v>
+        <v>27.779426</v>
       </c>
       <c r="H95" t="n">
-        <v>28.361314</v>
+        <v>28.361273</v>
       </c>
       <c r="I95" t="n">
-        <v>28.149659</v>
+        <v>28.149613</v>
       </c>
       <c r="J95" t="n">
-        <v>26.963795</v>
+        <v>26.963744</v>
       </c>
       <c r="K95" t="n">
-        <v>25.276895</v>
+        <v>25.276839</v>
       </c>
       <c r="L95" t="n">
-        <v>23.168047</v>
+        <v>23.167987</v>
       </c>
       <c r="M95" t="n">
-        <v>21.33293</v>
+        <v>21.332866</v>
       </c>
       <c r="N95" t="n">
-        <v>19.808076</v>
+        <v>19.808009</v>
       </c>
       <c r="O95" t="n">
-        <v>18.388417</v>
+        <v>18.388347</v>
       </c>
       <c r="P95" t="n">
-        <v>17.201126</v>
+        <v>17.201052</v>
       </c>
       <c r="Q95" t="n">
-        <v>15.868567</v>
+        <v>15.868492</v>
       </c>
       <c r="R95" t="n">
-        <v>14.482535</v>
+        <v>14.482461</v>
       </c>
       <c r="S95" t="n">
-        <v>13.279467</v>
+        <v>13.279394</v>
       </c>
       <c r="T95" t="n">
-        <v>12.261384</v>
+        <v>12.261312</v>
       </c>
       <c r="U95" t="n">
-        <v>11.401631</v>
+        <v>11.40156</v>
       </c>
       <c r="V95" t="n">
-        <v>10.659638</v>
+        <v>10.659567</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>9.417629</v>
+        <v>9.417628000000001</v>
       </c>
       <c r="F96" t="n">
-        <v>9.59418</v>
+        <v>9.594177</v>
       </c>
       <c r="G96" t="n">
-        <v>9.320385999999999</v>
+        <v>9.32038</v>
       </c>
       <c r="H96" t="n">
-        <v>8.895854999999999</v>
+        <v>8.895846000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>8.621878000000001</v>
+        <v>8.621866000000001</v>
       </c>
       <c r="J96" t="n">
-        <v>8.345007000000001</v>
+        <v>8.344993000000001</v>
       </c>
       <c r="K96" t="n">
-        <v>8.078327</v>
+        <v>8.078312</v>
       </c>
       <c r="L96" t="n">
-        <v>7.757379</v>
+        <v>7.757364</v>
       </c>
       <c r="M96" t="n">
-        <v>7.529851</v>
+        <v>7.529835</v>
       </c>
       <c r="N96" t="n">
-        <v>7.397271</v>
+        <v>7.397253</v>
       </c>
       <c r="O96" t="n">
-        <v>7.263323</v>
+        <v>7.263305</v>
       </c>
       <c r="P96" t="n">
-        <v>7.171659</v>
+        <v>7.171641</v>
       </c>
       <c r="Q96" t="n">
-        <v>6.969755</v>
+        <v>6.969737</v>
       </c>
       <c r="R96" t="n">
-        <v>6.672079</v>
+        <v>6.672062</v>
       </c>
       <c r="S96" t="n">
-        <v>6.376385</v>
+        <v>6.376367</v>
       </c>
       <c r="T96" t="n">
-        <v>6.093235</v>
+        <v>6.093218</v>
       </c>
       <c r="U96" t="n">
-        <v>5.836133</v>
+        <v>5.836116</v>
       </c>
       <c r="V96" t="n">
-        <v>5.602703</v>
+        <v>5.602686</v>
       </c>
     </row>
     <row r="97">
@@ -7749,55 +7749,55 @@
         <v>3.90198</v>
       </c>
       <c r="F97" t="n">
-        <v>3.679649</v>
+        <v>3.679648</v>
       </c>
       <c r="G97" t="n">
-        <v>3.472985</v>
+        <v>3.472983</v>
       </c>
       <c r="H97" t="n">
-        <v>3.299778</v>
+        <v>3.299774</v>
       </c>
       <c r="I97" t="n">
-        <v>3.229049</v>
+        <v>3.229044</v>
       </c>
       <c r="J97" t="n">
-        <v>3.169218</v>
+        <v>3.169212</v>
       </c>
       <c r="K97" t="n">
-        <v>3.111283</v>
+        <v>3.111277</v>
       </c>
       <c r="L97" t="n">
-        <v>3.027396</v>
+        <v>3.027389</v>
       </c>
       <c r="M97" t="n">
-        <v>2.978857</v>
+        <v>2.97885</v>
       </c>
       <c r="N97" t="n">
-        <v>2.971738</v>
+        <v>2.97173</v>
       </c>
       <c r="O97" t="n">
-        <v>2.970607</v>
+        <v>2.970599</v>
       </c>
       <c r="P97" t="n">
-        <v>2.993424</v>
+        <v>2.993416</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.972286</v>
+        <v>2.972278</v>
       </c>
       <c r="R97" t="n">
-        <v>2.906632</v>
+        <v>2.906624</v>
       </c>
       <c r="S97" t="n">
-        <v>2.834517</v>
+        <v>2.834509</v>
       </c>
       <c r="T97" t="n">
-        <v>2.758762</v>
+        <v>2.758754</v>
       </c>
       <c r="U97" t="n">
-        <v>2.684381</v>
+        <v>2.684373</v>
       </c>
       <c r="V97" t="n">
-        <v>2.610287</v>
+        <v>2.610278</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>19.248833</v>
+        <v>19.248831</v>
       </c>
       <c r="F98" t="n">
-        <v>18.892813</v>
+        <v>18.892811</v>
       </c>
       <c r="G98" t="n">
         <v>17.256789</v>
       </c>
       <c r="H98" t="n">
-        <v>15.536419</v>
+        <v>15.536423</v>
       </c>
       <c r="I98" t="n">
-        <v>14.245006</v>
+        <v>14.245012</v>
       </c>
       <c r="J98" t="n">
-        <v>13.131656</v>
+        <v>13.131664</v>
       </c>
       <c r="K98" t="n">
-        <v>12.253928</v>
+        <v>12.253938</v>
       </c>
       <c r="L98" t="n">
-        <v>11.380903</v>
+        <v>11.380913</v>
       </c>
       <c r="M98" t="n">
-        <v>10.823658</v>
+        <v>10.82367</v>
       </c>
       <c r="N98" t="n">
-        <v>10.527534</v>
+        <v>10.527547</v>
       </c>
       <c r="O98" t="n">
-        <v>10.295558</v>
+        <v>10.295573</v>
       </c>
       <c r="P98" t="n">
-        <v>10.190927</v>
+        <v>10.190943</v>
       </c>
       <c r="Q98" t="n">
-        <v>10.058446</v>
+        <v>10.058465</v>
       </c>
       <c r="R98" t="n">
-        <v>9.840011000000001</v>
+        <v>9.840031</v>
       </c>
       <c r="S98" t="n">
-        <v>9.591659999999999</v>
+        <v>9.591683</v>
       </c>
       <c r="T98" t="n">
-        <v>9.298931</v>
+        <v>9.298957</v>
       </c>
       <c r="U98" t="n">
-        <v>9.014462</v>
+        <v>9.014493</v>
       </c>
       <c r="V98" t="n">
-        <v>8.720020999999999</v>
+        <v>8.720058</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>29.251775</v>
+        <v>29.251771</v>
       </c>
       <c r="F99" t="n">
-        <v>33.227599</v>
+        <v>33.227588</v>
       </c>
       <c r="G99" t="n">
-        <v>35.540688</v>
+        <v>35.54067</v>
       </c>
       <c r="H99" t="n">
-        <v>36.085721</v>
+        <v>36.085697</v>
       </c>
       <c r="I99" t="n">
-        <v>35.938877</v>
+        <v>35.938847</v>
       </c>
       <c r="J99" t="n">
-        <v>34.907954</v>
+        <v>34.90792</v>
       </c>
       <c r="K99" t="n">
-        <v>33.600442</v>
+        <v>33.600405</v>
       </c>
       <c r="L99" t="n">
-        <v>31.757247</v>
+        <v>31.757207</v>
       </c>
       <c r="M99" t="n">
-        <v>30.526239</v>
+        <v>30.526196</v>
       </c>
       <c r="N99" t="n">
-        <v>29.939768</v>
+        <v>29.93972</v>
       </c>
       <c r="O99" t="n">
-        <v>29.528071</v>
+        <v>29.528019</v>
       </c>
       <c r="P99" t="n">
-        <v>29.490016</v>
+        <v>29.489957</v>
       </c>
       <c r="Q99" t="n">
-        <v>29.365524</v>
+        <v>29.365458</v>
       </c>
       <c r="R99" t="n">
-        <v>28.965484</v>
+        <v>28.965409</v>
       </c>
       <c r="S99" t="n">
-        <v>28.464943</v>
+        <v>28.464859</v>
       </c>
       <c r="T99" t="n">
-        <v>27.850389</v>
+        <v>27.850293</v>
       </c>
       <c r="U99" t="n">
-        <v>27.281752</v>
+        <v>27.281639</v>
       </c>
       <c r="V99" t="n">
-        <v>26.671625</v>
+        <v>26.671487</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>9.735694000000001</v>
+        <v>9.735695</v>
       </c>
       <c r="F100" t="n">
-        <v>9.486177</v>
+        <v>9.486179</v>
       </c>
       <c r="G100" t="n">
-        <v>8.774963</v>
+        <v>8.774967999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>8.007</v>
+        <v>8.007007</v>
       </c>
       <c r="I100" t="n">
-        <v>7.422561</v>
+        <v>7.42257</v>
       </c>
       <c r="J100" t="n">
-        <v>6.89249</v>
+        <v>6.892501</v>
       </c>
       <c r="K100" t="n">
-        <v>6.467974</v>
+        <v>6.467986</v>
       </c>
       <c r="L100" t="n">
-        <v>6.039034</v>
+        <v>6.039048</v>
       </c>
       <c r="M100" t="n">
-        <v>5.783587</v>
+        <v>5.783602</v>
       </c>
       <c r="N100" t="n">
-        <v>5.676388</v>
+        <v>5.676405</v>
       </c>
       <c r="O100" t="n">
-        <v>5.615615</v>
+        <v>5.615634</v>
       </c>
       <c r="P100" t="n">
-        <v>5.633947</v>
+        <v>5.633969</v>
       </c>
       <c r="Q100" t="n">
-        <v>5.642935</v>
+        <v>5.642959</v>
       </c>
       <c r="R100" t="n">
-        <v>5.606494</v>
+        <v>5.606522</v>
       </c>
       <c r="S100" t="n">
-        <v>5.556556</v>
+        <v>5.556588</v>
       </c>
       <c r="T100" t="n">
-        <v>5.487492</v>
+        <v>5.487528</v>
       </c>
       <c r="U100" t="n">
-        <v>5.425722</v>
+        <v>5.425766</v>
       </c>
       <c r="V100" t="n">
-        <v>5.359742</v>
+        <v>5.359797</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>13.134885</v>
+        <v>13.134884</v>
       </c>
       <c r="F101" t="n">
-        <v>13.717044</v>
+        <v>13.717042</v>
       </c>
       <c r="G101" t="n">
-        <v>13.491143</v>
+        <v>13.49114</v>
       </c>
       <c r="H101" t="n">
-        <v>12.840846</v>
+        <v>12.840843</v>
       </c>
       <c r="I101" t="n">
-        <v>12.19532</v>
+        <v>12.195318</v>
       </c>
       <c r="J101" t="n">
-        <v>11.459096</v>
+        <v>11.459094</v>
       </c>
       <c r="K101" t="n">
-        <v>10.795077</v>
+        <v>10.795076</v>
       </c>
       <c r="L101" t="n">
-        <v>10.075449</v>
+        <v>10.075448</v>
       </c>
       <c r="M101" t="n">
-        <v>9.626186000000001</v>
+        <v>9.626184</v>
       </c>
       <c r="N101" t="n">
-        <v>9.426672</v>
+        <v>9.426671000000001</v>
       </c>
       <c r="O101" t="n">
-        <v>9.315414000000001</v>
+        <v>9.315412999999999</v>
       </c>
       <c r="P101" t="n">
-        <v>9.345443</v>
+        <v>9.345442</v>
       </c>
       <c r="Q101" t="n">
-        <v>9.363733</v>
+        <v>9.363731</v>
       </c>
       <c r="R101" t="n">
-        <v>9.302008000000001</v>
+        <v>9.302006</v>
       </c>
       <c r="S101" t="n">
-        <v>9.206472</v>
+        <v>9.206469999999999</v>
       </c>
       <c r="T101" t="n">
-        <v>9.071612</v>
+        <v>9.07161</v>
       </c>
       <c r="U101" t="n">
-        <v>8.952339</v>
+        <v>8.952336000000001</v>
       </c>
       <c r="V101" t="n">
-        <v>8.825739</v>
+        <v>8.825735999999999</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>95.140216</v>
+        <v>95.14023299999999</v>
       </c>
       <c r="F102" t="n">
-        <v>105.07788</v>
+        <v>105.077909</v>
       </c>
       <c r="G102" t="n">
-        <v>110.46281</v>
+        <v>110.462844</v>
       </c>
       <c r="H102" t="n">
-        <v>111.776433</v>
+        <v>111.776469</v>
       </c>
       <c r="I102" t="n">
-        <v>111.957414</v>
+        <v>111.957451</v>
       </c>
       <c r="J102" t="n">
-        <v>109.785895</v>
+        <v>109.785933</v>
       </c>
       <c r="K102" t="n">
-        <v>106.778843</v>
+        <v>106.778883</v>
       </c>
       <c r="L102" t="n">
-        <v>101.940607</v>
+        <v>101.940649</v>
       </c>
       <c r="M102" t="n">
-        <v>98.90298799999999</v>
+        <v>98.90303299999999</v>
       </c>
       <c r="N102" t="n">
-        <v>97.844431</v>
+        <v>97.844481</v>
       </c>
       <c r="O102" t="n">
-        <v>97.366139</v>
+        <v>97.366195</v>
       </c>
       <c r="P102" t="n">
-        <v>98.21614700000001</v>
+        <v>98.216211</v>
       </c>
       <c r="Q102" t="n">
-        <v>98.90784600000001</v>
+        <v>98.90791900000001</v>
       </c>
       <c r="R102" t="n">
-        <v>98.788612</v>
+        <v>98.788695</v>
       </c>
       <c r="S102" t="n">
-        <v>98.44099900000001</v>
+        <v>98.44109400000001</v>
       </c>
       <c r="T102" t="n">
-        <v>97.673794</v>
+        <v>97.673902</v>
       </c>
       <c r="U102" t="n">
-        <v>96.991249</v>
+        <v>96.991377</v>
       </c>
       <c r="V102" t="n">
-        <v>96.24435699999999</v>
+        <v>96.24451500000001</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>224.401007</v>
+        <v>224.400974</v>
       </c>
       <c r="F103" t="n">
-        <v>212.261671</v>
+        <v>212.26163</v>
       </c>
       <c r="G103" t="n">
-        <v>188.535434</v>
+        <v>188.53541</v>
       </c>
       <c r="H103" t="n">
-        <v>166.195729</v>
+        <v>166.195728</v>
       </c>
       <c r="I103" t="n">
-        <v>150.101986</v>
+        <v>150.102007</v>
       </c>
       <c r="J103" t="n">
-        <v>136.712225</v>
+        <v>136.712261</v>
       </c>
       <c r="K103" t="n">
-        <v>126.354584</v>
+        <v>126.35463</v>
       </c>
       <c r="L103" t="n">
-        <v>116.370309</v>
+        <v>116.37036</v>
       </c>
       <c r="M103" t="n">
-        <v>109.868459</v>
+        <v>109.868513</v>
       </c>
       <c r="N103" t="n">
-        <v>106.199369</v>
+        <v>106.199427</v>
       </c>
       <c r="O103" t="n">
-        <v>103.411275</v>
+        <v>103.411336</v>
       </c>
       <c r="P103" t="n">
-        <v>102.158238</v>
+        <v>102.158303</v>
       </c>
       <c r="Q103" t="n">
-        <v>100.836453</v>
+        <v>100.836522</v>
       </c>
       <c r="R103" t="n">
-        <v>98.818577</v>
+        <v>98.81865000000001</v>
       </c>
       <c r="S103" t="n">
-        <v>96.558457</v>
+        <v>96.558533</v>
       </c>
       <c r="T103" t="n">
-        <v>93.915688</v>
+        <v>93.91576999999999</v>
       </c>
       <c r="U103" t="n">
-        <v>91.404971</v>
+        <v>91.405064</v>
       </c>
       <c r="V103" t="n">
-        <v>88.859893</v>
+        <v>88.86</v>
       </c>
     </row>
     <row r="104">
@@ -8278,22 +8278,22 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>19.842946</v>
+        <v>19.842948</v>
       </c>
       <c r="F104" t="n">
-        <v>21.062957</v>
+        <v>21.06296</v>
       </c>
       <c r="G104" t="n">
-        <v>21.11929</v>
+        <v>21.119293</v>
       </c>
       <c r="H104" t="n">
-        <v>20.738401</v>
+        <v>20.738403</v>
       </c>
       <c r="I104" t="n">
-        <v>20.38276</v>
+        <v>20.382762</v>
       </c>
       <c r="J104" t="n">
-        <v>19.725208</v>
+        <v>19.725209</v>
       </c>
       <c r="K104" t="n">
         <v>18.940071</v>
@@ -8302,22 +8302,22 @@
         <v>17.785157</v>
       </c>
       <c r="M104" t="n">
-        <v>16.915792</v>
+        <v>16.915791</v>
       </c>
       <c r="N104" t="n">
-        <v>16.370404</v>
+        <v>16.370403</v>
       </c>
       <c r="O104" t="n">
-        <v>15.906575</v>
+        <v>15.906574</v>
       </c>
       <c r="P104" t="n">
-        <v>15.636037</v>
+        <v>15.636036</v>
       </c>
       <c r="Q104" t="n">
-        <v>15.311306</v>
+        <v>15.311305</v>
       </c>
       <c r="R104" t="n">
-        <v>14.855159</v>
+        <v>14.855158</v>
       </c>
       <c r="S104" t="n">
         <v>14.382322</v>
@@ -8354,37 +8354,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>10.756006</v>
+        <v>10.756005</v>
       </c>
       <c r="F105" t="n">
-        <v>11.602962</v>
+        <v>11.60296</v>
       </c>
       <c r="G105" t="n">
-        <v>11.962712</v>
+        <v>11.96271</v>
       </c>
       <c r="H105" t="n">
-        <v>11.867686</v>
+        <v>11.867684</v>
       </c>
       <c r="I105" t="n">
-        <v>11.676512</v>
+        <v>11.67651</v>
       </c>
       <c r="J105" t="n">
-        <v>11.276241</v>
+        <v>11.276239</v>
       </c>
       <c r="K105" t="n">
-        <v>10.84914</v>
+        <v>10.849138</v>
       </c>
       <c r="L105" t="n">
-        <v>10.282106</v>
+        <v>10.282105</v>
       </c>
       <c r="M105" t="n">
-        <v>9.935126</v>
+        <v>9.935124999999999</v>
       </c>
       <c r="N105" t="n">
-        <v>9.805616000000001</v>
+        <v>9.805615</v>
       </c>
       <c r="O105" t="n">
-        <v>9.731344999999999</v>
+        <v>9.731344</v>
       </c>
       <c r="P105" t="n">
         <v>9.768539000000001</v>
@@ -8393,19 +8393,19 @@
         <v>9.763109</v>
       </c>
       <c r="R105" t="n">
-        <v>9.657842</v>
+        <v>9.657843</v>
       </c>
       <c r="S105" t="n">
-        <v>9.521829</v>
+        <v>9.521831000000001</v>
       </c>
       <c r="T105" t="n">
-        <v>9.361058999999999</v>
+        <v>9.361060999999999</v>
       </c>
       <c r="U105" t="n">
-        <v>9.234332999999999</v>
+        <v>9.234336000000001</v>
       </c>
       <c r="V105" t="n">
-        <v>9.112788999999999</v>
+        <v>9.112793</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>101.153019</v>
+        <v>101.15303</v>
       </c>
       <c r="F106" t="n">
-        <v>112.604682</v>
+        <v>112.604696</v>
       </c>
       <c r="G106" t="n">
-        <v>120.34513</v>
+        <v>120.345134</v>
       </c>
       <c r="H106" t="n">
-        <v>122.696863</v>
+        <v>122.696856</v>
       </c>
       <c r="I106" t="n">
-        <v>122.830594</v>
+        <v>122.830575</v>
       </c>
       <c r="J106" t="n">
-        <v>119.655301</v>
+        <v>119.655272</v>
       </c>
       <c r="K106" t="n">
-        <v>115.057831</v>
+        <v>115.057795</v>
       </c>
       <c r="L106" t="n">
-        <v>108.121649</v>
+        <v>108.121609</v>
       </c>
       <c r="M106" t="n">
-        <v>103.052642</v>
+        <v>103.052596</v>
       </c>
       <c r="N106" t="n">
-        <v>100.009092</v>
+        <v>100.009041</v>
       </c>
       <c r="O106" t="n">
-        <v>97.465957</v>
+        <v>97.4659</v>
       </c>
       <c r="P106" t="n">
-        <v>96.113207</v>
+        <v>96.11314299999999</v>
       </c>
       <c r="Q106" t="n">
-        <v>94.537064</v>
+        <v>94.536992</v>
       </c>
       <c r="R106" t="n">
-        <v>92.281612</v>
+        <v>92.281532</v>
       </c>
       <c r="S106" t="n">
-        <v>90.065781</v>
+        <v>90.065692</v>
       </c>
       <c r="T106" t="n">
-        <v>87.84590900000001</v>
+        <v>87.845806</v>
       </c>
       <c r="U106" t="n">
-        <v>85.965722</v>
+        <v>85.965597</v>
       </c>
       <c r="V106" t="n">
-        <v>84.096501</v>
+        <v>84.096345</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2.659806</v>
+        <v>2.659805</v>
       </c>
       <c r="F107" t="n">
-        <v>3.118875</v>
+        <v>3.118873</v>
       </c>
       <c r="G107" t="n">
-        <v>3.263598</v>
+        <v>3.263595</v>
       </c>
       <c r="H107" t="n">
-        <v>3.262703</v>
+        <v>3.262699</v>
       </c>
       <c r="I107" t="n">
-        <v>3.25664</v>
+        <v>3.256636</v>
       </c>
       <c r="J107" t="n">
-        <v>3.219308</v>
+        <v>3.219303</v>
       </c>
       <c r="K107" t="n">
-        <v>3.182105</v>
+        <v>3.182099</v>
       </c>
       <c r="L107" t="n">
-        <v>3.098511</v>
+        <v>3.098505</v>
       </c>
       <c r="M107" t="n">
-        <v>3.065556</v>
+        <v>3.06555</v>
       </c>
       <c r="N107" t="n">
-        <v>3.082974</v>
+        <v>3.082967</v>
       </c>
       <c r="O107" t="n">
-        <v>3.103415</v>
+        <v>3.103406</v>
       </c>
       <c r="P107" t="n">
-        <v>3.148908</v>
+        <v>3.148898</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.171979</v>
+        <v>3.171968</v>
       </c>
       <c r="R107" t="n">
-        <v>3.153482</v>
+        <v>3.15347</v>
       </c>
       <c r="S107" t="n">
-        <v>3.113431</v>
+        <v>3.113417</v>
       </c>
       <c r="T107" t="n">
-        <v>3.051681</v>
+        <v>3.051665</v>
       </c>
       <c r="U107" t="n">
-        <v>2.987737</v>
+        <v>2.987718</v>
       </c>
       <c r="V107" t="n">
-        <v>2.914206</v>
+        <v>2.914184</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>48.405893</v>
+        <v>48.405884</v>
       </c>
       <c r="F108" t="n">
-        <v>51.249773</v>
+        <v>51.249755</v>
       </c>
       <c r="G108" t="n">
-        <v>50.353544</v>
+        <v>50.353522</v>
       </c>
       <c r="H108" t="n">
-        <v>47.856198</v>
+        <v>47.856174</v>
       </c>
       <c r="I108" t="n">
-        <v>45.46385</v>
+        <v>45.463824</v>
       </c>
       <c r="J108" t="n">
-        <v>42.776701</v>
+        <v>42.776675</v>
       </c>
       <c r="K108" t="n">
-        <v>40.315001</v>
+        <v>40.314974</v>
       </c>
       <c r="L108" t="n">
-        <v>37.607285</v>
+        <v>37.607257</v>
       </c>
       <c r="M108" t="n">
-        <v>35.874713</v>
+        <v>35.874684</v>
       </c>
       <c r="N108" t="n">
-        <v>35.046999</v>
+        <v>35.046967</v>
       </c>
       <c r="O108" t="n">
-        <v>34.535964</v>
+        <v>34.535929</v>
       </c>
       <c r="P108" t="n">
-        <v>34.565811</v>
+        <v>34.565771</v>
       </c>
       <c r="Q108" t="n">
-        <v>34.594462</v>
+        <v>34.594417</v>
       </c>
       <c r="R108" t="n">
-        <v>34.395045</v>
+        <v>34.394994</v>
       </c>
       <c r="S108" t="n">
-        <v>34.15565</v>
+        <v>34.155591</v>
       </c>
       <c r="T108" t="n">
-        <v>33.815935</v>
+        <v>33.815866</v>
       </c>
       <c r="U108" t="n">
-        <v>33.525206</v>
+        <v>33.525123</v>
       </c>
       <c r="V108" t="n">
-        <v>33.173691</v>
+        <v>33.173589</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>14.822663</v>
+        <v>14.822667</v>
       </c>
       <c r="F109" t="n">
-        <v>15.741062</v>
+        <v>15.74107</v>
       </c>
       <c r="G109" t="n">
-        <v>16.523634</v>
+        <v>16.523644</v>
       </c>
       <c r="H109" t="n">
-        <v>17.207403</v>
+        <v>17.207412</v>
       </c>
       <c r="I109" t="n">
-        <v>17.999438</v>
+        <v>17.999445</v>
       </c>
       <c r="J109" t="n">
-        <v>18.344732</v>
+        <v>18.344737</v>
       </c>
       <c r="K109" t="n">
-        <v>18.331697</v>
+        <v>18.3317</v>
       </c>
       <c r="L109" t="n">
-        <v>17.757529</v>
+        <v>17.75753</v>
       </c>
       <c r="M109" t="n">
         <v>17.306372</v>
       </c>
       <c r="N109" t="n">
-        <v>17.080173</v>
+        <v>17.080172</v>
       </c>
       <c r="O109" t="n">
-        <v>16.867194</v>
+        <v>16.867192</v>
       </c>
       <c r="P109" t="n">
-        <v>16.809955</v>
+        <v>16.809953</v>
       </c>
       <c r="Q109" t="n">
-        <v>16.663923</v>
+        <v>16.66392</v>
       </c>
       <c r="R109" t="n">
-        <v>16.346994</v>
+        <v>16.346991</v>
       </c>
       <c r="S109" t="n">
-        <v>15.992002</v>
+        <v>15.991998</v>
       </c>
       <c r="T109" t="n">
-        <v>15.616731</v>
+        <v>15.616727</v>
       </c>
       <c r="U109" t="n">
-        <v>15.313472</v>
+        <v>15.313467</v>
       </c>
       <c r="V109" t="n">
-        <v>15.022535</v>
+        <v>15.022529</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>12.25735</v>
+        <v>12.257354</v>
       </c>
       <c r="F110" t="n">
-        <v>13.826186</v>
+        <v>13.826192</v>
       </c>
       <c r="G110" t="n">
-        <v>14.797938</v>
+        <v>14.797945</v>
       </c>
       <c r="H110" t="n">
-        <v>15.049998</v>
+        <v>15.050006</v>
       </c>
       <c r="I110" t="n">
-        <v>14.991692</v>
+        <v>14.991702</v>
       </c>
       <c r="J110" t="n">
-        <v>14.594788</v>
+        <v>14.594799</v>
       </c>
       <c r="K110" t="n">
-        <v>14.133592</v>
+        <v>14.133604</v>
       </c>
       <c r="L110" t="n">
-        <v>13.492205</v>
+        <v>13.492219</v>
       </c>
       <c r="M110" t="n">
-        <v>13.137256</v>
+        <v>13.137271</v>
       </c>
       <c r="N110" t="n">
-        <v>13.076181</v>
+        <v>13.076199</v>
       </c>
       <c r="O110" t="n">
-        <v>13.096706</v>
+        <v>13.096727</v>
       </c>
       <c r="P110" t="n">
-        <v>13.285549</v>
+        <v>13.285573</v>
       </c>
       <c r="Q110" t="n">
-        <v>13.435515</v>
+        <v>13.435542</v>
       </c>
       <c r="R110" t="n">
-        <v>13.450945</v>
+        <v>13.450976</v>
       </c>
       <c r="S110" t="n">
-        <v>13.401535</v>
+        <v>13.401572</v>
       </c>
       <c r="T110" t="n">
-        <v>13.275852</v>
+        <v>13.275894</v>
       </c>
       <c r="U110" t="n">
-        <v>13.147173</v>
+        <v>13.147225</v>
       </c>
       <c r="V110" t="n">
-        <v>12.99073</v>
+        <v>12.990794</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>78.597213</v>
+        <v>78.597222</v>
       </c>
       <c r="F111" t="n">
-        <v>85.870862</v>
+        <v>85.870876</v>
       </c>
       <c r="G111" t="n">
-        <v>87.790499</v>
+        <v>87.79051699999999</v>
       </c>
       <c r="H111" t="n">
-        <v>86.321275</v>
+        <v>86.32129399999999</v>
       </c>
       <c r="I111" t="n">
-        <v>84.69866</v>
+        <v>84.69868200000001</v>
       </c>
       <c r="J111" t="n">
-        <v>81.94399199999999</v>
+        <v>81.944016</v>
       </c>
       <c r="K111" t="n">
-        <v>78.805086</v>
+        <v>78.80511300000001</v>
       </c>
       <c r="L111" t="n">
-        <v>74.21327599999999</v>
+        <v>74.213306</v>
       </c>
       <c r="M111" t="n">
-        <v>70.951876</v>
+        <v>70.95191</v>
       </c>
       <c r="N111" t="n">
-        <v>69.13773399999999</v>
+        <v>69.137773</v>
       </c>
       <c r="O111" t="n">
-        <v>67.70203100000001</v>
+        <v>67.702074</v>
       </c>
       <c r="P111" t="n">
-        <v>67.048598</v>
+        <v>67.048648</v>
       </c>
       <c r="Q111" t="n">
-        <v>66.08787599999999</v>
+        <v>66.087935</v>
       </c>
       <c r="R111" t="n">
-        <v>64.433249</v>
+        <v>64.433318</v>
       </c>
       <c r="S111" t="n">
-        <v>62.611141</v>
+        <v>62.611225</v>
       </c>
       <c r="T111" t="n">
-        <v>60.762088</v>
+        <v>60.762189</v>
       </c>
       <c r="U111" t="n">
-        <v>59.276352</v>
+        <v>59.276475</v>
       </c>
       <c r="V111" t="n">
-        <v>57.922812</v>
+        <v>57.922965</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>118.820164</v>
+        <v>118.820167</v>
       </c>
       <c r="F112" t="n">
         <v>131.737756</v>
       </c>
       <c r="G112" t="n">
-        <v>139.329791</v>
+        <v>139.329782</v>
       </c>
       <c r="H112" t="n">
-        <v>141.291149</v>
+        <v>141.29113</v>
       </c>
       <c r="I112" t="n">
-        <v>141.427497</v>
+        <v>141.427469</v>
       </c>
       <c r="J112" t="n">
-        <v>138.443277</v>
+        <v>138.443242</v>
       </c>
       <c r="K112" t="n">
-        <v>134.485167</v>
+        <v>134.485126</v>
       </c>
       <c r="L112" t="n">
-        <v>128.230884</v>
+        <v>128.230839</v>
       </c>
       <c r="M112" t="n">
-        <v>124.19042</v>
+        <v>124.190372</v>
       </c>
       <c r="N112" t="n">
-        <v>122.593439</v>
+        <v>122.593387</v>
       </c>
       <c r="O112" t="n">
-        <v>121.707405</v>
+        <v>121.707348</v>
       </c>
       <c r="P112" t="n">
-        <v>122.498214</v>
+        <v>122.49815</v>
       </c>
       <c r="Q112" t="n">
-        <v>123.12735</v>
+        <v>123.127278</v>
       </c>
       <c r="R112" t="n">
-        <v>122.7688</v>
+        <v>122.768718</v>
       </c>
       <c r="S112" t="n">
-        <v>122.072716</v>
+        <v>122.072622</v>
       </c>
       <c r="T112" t="n">
-        <v>120.91175</v>
+        <v>120.911643</v>
       </c>
       <c r="U112" t="n">
-        <v>119.994916</v>
+        <v>119.99479</v>
       </c>
       <c r="V112" t="n">
-        <v>119.146389</v>
+        <v>119.146237</v>
       </c>
     </row>
     <row r="113">
@@ -8962,58 +8962,58 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>15.683272</v>
+        <v>15.683273</v>
       </c>
       <c r="F113" t="n">
-        <v>16.8823</v>
+        <v>16.882299</v>
       </c>
       <c r="G113" t="n">
-        <v>14.409388</v>
+        <v>14.409382</v>
       </c>
       <c r="H113" t="n">
-        <v>12.911704</v>
+        <v>12.911692</v>
       </c>
       <c r="I113" t="n">
-        <v>12.06905</v>
+        <v>12.069032</v>
       </c>
       <c r="J113" t="n">
-        <v>11.6673</v>
+        <v>11.667277</v>
       </c>
       <c r="K113" t="n">
-        <v>11.394041</v>
+        <v>11.394013</v>
       </c>
       <c r="L113" t="n">
-        <v>11.119838</v>
+        <v>11.119805</v>
       </c>
       <c r="M113" t="n">
-        <v>10.909464</v>
+        <v>10.909427</v>
       </c>
       <c r="N113" t="n">
-        <v>10.684344</v>
+        <v>10.684301</v>
       </c>
       <c r="O113" t="n">
-        <v>10.200932</v>
+        <v>10.200884</v>
       </c>
       <c r="P113" t="n">
-        <v>9.843902</v>
+        <v>9.843849000000001</v>
       </c>
       <c r="Q113" t="n">
-        <v>9.353001000000001</v>
+        <v>9.352942000000001</v>
       </c>
       <c r="R113" t="n">
-        <v>8.611855</v>
+        <v>8.611791</v>
       </c>
       <c r="S113" t="n">
-        <v>8.064589</v>
+        <v>8.064518</v>
       </c>
       <c r="T113" t="n">
-        <v>7.540597</v>
+        <v>7.540518</v>
       </c>
       <c r="U113" t="n">
-        <v>7.069194</v>
+        <v>7.069103</v>
       </c>
       <c r="V113" t="n">
-        <v>6.629572</v>
+        <v>6.629464</v>
       </c>
     </row>
     <row r="114">
@@ -9038,58 +9038,58 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2.199082</v>
+        <v>2.19908</v>
       </c>
       <c r="F114" t="n">
-        <v>3.344313</v>
+        <v>3.344311</v>
       </c>
       <c r="G114" t="n">
-        <v>4.258883</v>
+        <v>4.258881</v>
       </c>
       <c r="H114" t="n">
-        <v>4.991198</v>
+        <v>4.991197</v>
       </c>
       <c r="I114" t="n">
         <v>5.350946</v>
       </c>
       <c r="J114" t="n">
-        <v>5.390443</v>
+        <v>5.390444</v>
       </c>
       <c r="K114" t="n">
-        <v>5.19759</v>
+        <v>5.197592</v>
       </c>
       <c r="L114" t="n">
-        <v>4.876724</v>
+        <v>4.876725</v>
       </c>
       <c r="M114" t="n">
-        <v>4.561532</v>
+        <v>4.561534</v>
       </c>
       <c r="N114" t="n">
-        <v>4.250405</v>
+        <v>4.250407</v>
       </c>
       <c r="O114" t="n">
-        <v>3.873403</v>
+        <v>3.873405</v>
       </c>
       <c r="P114" t="n">
-        <v>3.582346</v>
+        <v>3.582348</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.270669</v>
+        <v>3.270671</v>
       </c>
       <c r="R114" t="n">
-        <v>2.89876</v>
+        <v>2.898762</v>
       </c>
       <c r="S114" t="n">
-        <v>2.619047</v>
+        <v>2.61905</v>
       </c>
       <c r="T114" t="n">
-        <v>2.371859</v>
+        <v>2.371861</v>
       </c>
       <c r="U114" t="n">
-        <v>2.164814</v>
+        <v>2.164817</v>
       </c>
       <c r="V114" t="n">
-        <v>1.988756</v>
+        <v>1.988759</v>
       </c>
     </row>
     <row r="115">
@@ -9114,58 +9114,58 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>59.915203</v>
+        <v>59.915204</v>
       </c>
       <c r="F115" t="n">
-        <v>74.144468</v>
+        <v>74.144471</v>
       </c>
       <c r="G115" t="n">
-        <v>79.192368</v>
+        <v>79.192376</v>
       </c>
       <c r="H115" t="n">
-        <v>83.943601</v>
+        <v>83.943614</v>
       </c>
       <c r="I115" t="n">
-        <v>86.93277999999999</v>
+        <v>86.93279800000001</v>
       </c>
       <c r="J115" t="n">
-        <v>88.474986</v>
+        <v>88.475008</v>
       </c>
       <c r="K115" t="n">
-        <v>88.394931</v>
+        <v>88.39495700000001</v>
       </c>
       <c r="L115" t="n">
-        <v>87.187164</v>
+        <v>87.187195</v>
       </c>
       <c r="M115" t="n">
-        <v>86.336451</v>
+        <v>86.33648599999999</v>
       </c>
       <c r="N115" t="n">
-        <v>85.601119</v>
+        <v>85.601159</v>
       </c>
       <c r="O115" t="n">
-        <v>82.945387</v>
+        <v>82.945432</v>
       </c>
       <c r="P115" t="n">
-        <v>81.35171200000001</v>
+        <v>81.35176300000001</v>
       </c>
       <c r="Q115" t="n">
-        <v>78.544476</v>
+        <v>78.544533</v>
       </c>
       <c r="R115" t="n">
-        <v>73.414924</v>
+        <v>73.414986</v>
       </c>
       <c r="S115" t="n">
-        <v>69.667698</v>
+        <v>69.667766</v>
       </c>
       <c r="T115" t="n">
-        <v>65.85598899999999</v>
+        <v>65.856065</v>
       </c>
       <c r="U115" t="n">
-        <v>62.231072</v>
+        <v>62.23116</v>
       </c>
       <c r="V115" t="n">
-        <v>58.620229</v>
+        <v>58.620334</v>
       </c>
     </row>
     <row r="116">
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1.512258</v>
+        <v>1.512257</v>
       </c>
       <c r="F116" t="n">
-        <v>1.708804</v>
+        <v>1.708801</v>
       </c>
       <c r="G116" t="n">
-        <v>1.770223</v>
+        <v>1.770218</v>
       </c>
       <c r="H116" t="n">
-        <v>1.792113</v>
+        <v>1.792108</v>
       </c>
       <c r="I116" t="n">
-        <v>1.780891</v>
+        <v>1.780884</v>
       </c>
       <c r="J116" t="n">
-        <v>1.737774</v>
+        <v>1.737766</v>
       </c>
       <c r="K116" t="n">
-        <v>1.676235</v>
+        <v>1.676226</v>
       </c>
       <c r="L116" t="n">
-        <v>1.594169</v>
+        <v>1.594159</v>
       </c>
       <c r="M116" t="n">
-        <v>1.530296</v>
+        <v>1.530286</v>
       </c>
       <c r="N116" t="n">
-        <v>1.485753</v>
+        <v>1.485741</v>
       </c>
       <c r="O116" t="n">
-        <v>1.441078</v>
+        <v>1.441066</v>
       </c>
       <c r="P116" t="n">
-        <v>1.400182</v>
+        <v>1.400169</v>
       </c>
       <c r="Q116" t="n">
-        <v>1.342925</v>
+        <v>1.342912</v>
       </c>
       <c r="R116" t="n">
-        <v>1.254791</v>
+        <v>1.254778</v>
       </c>
       <c r="S116" t="n">
-        <v>1.177039</v>
+        <v>1.177026</v>
       </c>
       <c r="T116" t="n">
-        <v>1.094323</v>
+        <v>1.09431</v>
       </c>
       <c r="U116" t="n">
-        <v>1.017082</v>
+        <v>1.017069</v>
       </c>
       <c r="V116" t="n">
-        <v>0.9461079999999999</v>
+        <v>0.946094</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6.475277</v>
+        <v>6.475278</v>
       </c>
       <c r="F117" t="n">
-        <v>9.036573000000001</v>
+        <v>9.036576999999999</v>
       </c>
       <c r="G117" t="n">
-        <v>10.322608</v>
+        <v>10.322615</v>
       </c>
       <c r="H117" t="n">
-        <v>10.984643</v>
+        <v>10.984654</v>
       </c>
       <c r="I117" t="n">
-        <v>11.162601</v>
+        <v>11.162615</v>
       </c>
       <c r="J117" t="n">
-        <v>10.958189</v>
+        <v>10.958206</v>
       </c>
       <c r="K117" t="n">
-        <v>10.536474</v>
+        <v>10.536492</v>
       </c>
       <c r="L117" t="n">
-        <v>9.940912000000001</v>
+        <v>9.940932</v>
       </c>
       <c r="M117" t="n">
-        <v>9.418513000000001</v>
+        <v>9.418533999999999</v>
       </c>
       <c r="N117" t="n">
-        <v>8.993929</v>
+        <v>8.993950999999999</v>
       </c>
       <c r="O117" t="n">
-        <v>8.591229999999999</v>
+        <v>8.591253999999999</v>
       </c>
       <c r="P117" t="n">
-        <v>8.25652</v>
+        <v>8.256544</v>
       </c>
       <c r="Q117" t="n">
-        <v>7.885266</v>
+        <v>7.885291</v>
       </c>
       <c r="R117" t="n">
-        <v>7.382135</v>
+        <v>7.382161</v>
       </c>
       <c r="S117" t="n">
-        <v>6.973632</v>
+        <v>6.973658</v>
       </c>
       <c r="T117" t="n">
-        <v>6.549272</v>
+        <v>6.549299</v>
       </c>
       <c r="U117" t="n">
-        <v>6.158768</v>
+        <v>6.158796</v>
       </c>
       <c r="V117" t="n">
-        <v>5.809225</v>
+        <v>5.809253</v>
       </c>
     </row>
     <row r="118">
@@ -9345,55 +9345,55 @@
         <v>5.603674</v>
       </c>
       <c r="F118" t="n">
-        <v>6.185124</v>
+        <v>6.185123</v>
       </c>
       <c r="G118" t="n">
         <v>6.220817</v>
       </c>
       <c r="H118" t="n">
-        <v>6.145803</v>
+        <v>6.145802</v>
       </c>
       <c r="I118" t="n">
-        <v>5.999155</v>
+        <v>5.999154</v>
       </c>
       <c r="J118" t="n">
-        <v>5.774181</v>
+        <v>5.77418</v>
       </c>
       <c r="K118" t="n">
-        <v>5.50969</v>
+        <v>5.509689</v>
       </c>
       <c r="L118" t="n">
-        <v>5.193317</v>
+        <v>5.193316</v>
       </c>
       <c r="M118" t="n">
-        <v>4.946945</v>
+        <v>4.946943</v>
       </c>
       <c r="N118" t="n">
-        <v>4.779954</v>
+        <v>4.779952</v>
       </c>
       <c r="O118" t="n">
-        <v>4.640483</v>
+        <v>4.640481</v>
       </c>
       <c r="P118" t="n">
-        <v>4.539438</v>
+        <v>4.539435</v>
       </c>
       <c r="Q118" t="n">
-        <v>4.414413</v>
+        <v>4.41441</v>
       </c>
       <c r="R118" t="n">
-        <v>4.20772</v>
+        <v>4.207718</v>
       </c>
       <c r="S118" t="n">
-        <v>4.045007</v>
+        <v>4.045005</v>
       </c>
       <c r="T118" t="n">
-        <v>3.860936</v>
+        <v>3.860934</v>
       </c>
       <c r="U118" t="n">
-        <v>3.682505</v>
+        <v>3.682503</v>
       </c>
       <c r="V118" t="n">
-        <v>3.511023</v>
+        <v>3.511022</v>
       </c>
     </row>
     <row r="119">
@@ -9421,55 +9421,55 @@
         <v>2.468055</v>
       </c>
       <c r="F119" t="n">
-        <v>3.288635</v>
+        <v>3.288636</v>
       </c>
       <c r="G119" t="n">
-        <v>3.932669</v>
+        <v>3.932671</v>
       </c>
       <c r="H119" t="n">
-        <v>4.442402</v>
+        <v>4.442404</v>
       </c>
       <c r="I119" t="n">
-        <v>4.771354</v>
+        <v>4.771358</v>
       </c>
       <c r="J119" t="n">
-        <v>4.918495</v>
+        <v>4.9185</v>
       </c>
       <c r="K119" t="n">
-        <v>4.937791</v>
+        <v>4.937796</v>
       </c>
       <c r="L119" t="n">
-        <v>4.848053</v>
+        <v>4.84806</v>
       </c>
       <c r="M119" t="n">
-        <v>4.780157</v>
+        <v>4.780164</v>
       </c>
       <c r="N119" t="n">
-        <v>4.756814</v>
+        <v>4.756822</v>
       </c>
       <c r="O119" t="n">
-        <v>4.728354</v>
+        <v>4.728362</v>
       </c>
       <c r="P119" t="n">
-        <v>4.707792</v>
+        <v>4.707801</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.634046</v>
+        <v>4.634055</v>
       </c>
       <c r="R119" t="n">
-        <v>4.453305</v>
+        <v>4.453315</v>
       </c>
       <c r="S119" t="n">
-        <v>4.304039</v>
+        <v>4.30405</v>
       </c>
       <c r="T119" t="n">
-        <v>4.120612</v>
+        <v>4.120624</v>
       </c>
       <c r="U119" t="n">
-        <v>3.932639</v>
+        <v>3.93265</v>
       </c>
       <c r="V119" t="n">
-        <v>3.742264</v>
+        <v>3.742276</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6e-06</v>
+        <v>5e-06</v>
       </c>
       <c r="F120" t="n">
-        <v>1.2e-05</v>
+        <v>1.1e-05</v>
       </c>
       <c r="G120" t="n">
-        <v>1.8e-05</v>
+        <v>1.6e-05</v>
       </c>
       <c r="H120" t="n">
-        <v>2.3e-05</v>
+        <v>2.1e-05</v>
       </c>
       <c r="I120" t="n">
-        <v>2.9e-05</v>
+        <v>2.6e-05</v>
       </c>
       <c r="J120" t="n">
-        <v>3.4e-05</v>
+        <v>3.1e-05</v>
       </c>
       <c r="K120" t="n">
+        <v>3.5e-05</v>
+      </c>
+      <c r="L120" t="n">
         <v>3.8e-05</v>
       </c>
-      <c r="L120" t="n">
+      <c r="M120" t="n">
         <v>4.2e-05</v>
       </c>
-      <c r="M120" t="n">
+      <c r="N120" t="n">
         <v>4.6e-05</v>
       </c>
-      <c r="N120" t="n">
+      <c r="O120" t="n">
         <v>5e-05</v>
       </c>
-      <c r="O120" t="n">
-        <v>5.4e-05</v>
-      </c>
       <c r="P120" t="n">
+        <v>5.3e-05</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>5.7e-05</v>
+      </c>
+      <c r="R120" t="n">
         <v>5.8e-05</v>
       </c>
-      <c r="Q120" t="n">
+      <c r="S120" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="T120" t="n">
+        <v>6.1e-05</v>
+      </c>
+      <c r="U120" t="n">
         <v>6.2e-05</v>
       </c>
-      <c r="R120" t="n">
-        <v>6.4e-05</v>
-      </c>
-      <c r="S120" t="n">
-        <v>6.600000000000001e-05</v>
-      </c>
-      <c r="T120" t="n">
-        <v>6.7e-05</v>
-      </c>
-      <c r="U120" t="n">
-        <v>6.8e-05</v>
-      </c>
       <c r="V120" t="n">
-        <v>6.8e-05</v>
+        <v>6.2e-05</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>8.7e-05</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="F121" t="n">
-        <v>0.000182</v>
+        <v>0.000167</v>
       </c>
       <c r="G121" t="n">
-        <v>0.000266</v>
+        <v>0.000243</v>
       </c>
       <c r="H121" t="n">
-        <v>0.000346</v>
+        <v>0.000317</v>
       </c>
       <c r="I121" t="n">
-        <v>0.000421</v>
+        <v>0.000386</v>
       </c>
       <c r="J121" t="n">
-        <v>0.000488</v>
+        <v>0.000447</v>
       </c>
       <c r="K121" t="n">
-        <v>0.000547</v>
+        <v>0.000501</v>
       </c>
       <c r="L121" t="n">
-        <v>0.000595</v>
+        <v>0.000545</v>
       </c>
       <c r="M121" t="n">
-        <v>0.000647</v>
+        <v>0.000592</v>
       </c>
       <c r="N121" t="n">
-        <v>0.000704</v>
+        <v>0.000645</v>
       </c>
       <c r="O121" t="n">
-        <v>0.000758</v>
+        <v>0.000694</v>
       </c>
       <c r="P121" t="n">
-        <v>0.000812</v>
+        <v>0.000744</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.000856</v>
+        <v>0.000784</v>
       </c>
       <c r="R121" t="n">
-        <v>0.000876</v>
+        <v>0.000802</v>
       </c>
       <c r="S121" t="n">
-        <v>0.000899</v>
+        <v>0.0008229999999999999</v>
       </c>
       <c r="T121" t="n">
-        <v>0.000911</v>
+        <v>0.000835</v>
       </c>
       <c r="U121" t="n">
-        <v>0.000919</v>
+        <v>0.000842</v>
       </c>
       <c r="V121" t="n">
-        <v>0.000922</v>
+        <v>0.000845</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>114.363119</v>
+        <v>114.363128</v>
       </c>
       <c r="F122" t="n">
-        <v>130.559891</v>
+        <v>130.559906</v>
       </c>
       <c r="G122" t="n">
-        <v>137.332253</v>
+        <v>137.332273</v>
       </c>
       <c r="H122" t="n">
-        <v>142.094683</v>
+        <v>142.094707</v>
       </c>
       <c r="I122" t="n">
-        <v>145.190607</v>
+        <v>145.190634</v>
       </c>
       <c r="J122" t="n">
-        <v>146.134683</v>
+        <v>146.134715</v>
       </c>
       <c r="K122" t="n">
-        <v>145.55467</v>
+        <v>145.554705</v>
       </c>
       <c r="L122" t="n">
-        <v>142.813195</v>
+        <v>142.813234</v>
       </c>
       <c r="M122" t="n">
-        <v>141.172163</v>
+        <v>141.172206</v>
       </c>
       <c r="N122" t="n">
-        <v>140.824857</v>
+        <v>140.824904</v>
       </c>
       <c r="O122" t="n">
-        <v>140.311068</v>
+        <v>140.311119</v>
       </c>
       <c r="P122" t="n">
-        <v>140.224679</v>
+        <v>140.224734</v>
       </c>
       <c r="Q122" t="n">
-        <v>138.637702</v>
+        <v>138.63776</v>
       </c>
       <c r="R122" t="n">
-        <v>133.878851</v>
+        <v>133.87891</v>
       </c>
       <c r="S122" t="n">
-        <v>130.107106</v>
+        <v>130.107165</v>
       </c>
       <c r="T122" t="n">
-        <v>125.516363</v>
+        <v>125.516422</v>
       </c>
       <c r="U122" t="n">
-        <v>121.141953</v>
+        <v>121.142011</v>
       </c>
       <c r="V122" t="n">
-        <v>116.987247</v>
+        <v>116.987305</v>
       </c>
     </row>
     <row r="123">
@@ -9725,16 +9725,16 @@
         <v>0.909592</v>
       </c>
       <c r="F123" t="n">
-        <v>1.007873</v>
+        <v>1.007872</v>
       </c>
       <c r="G123" t="n">
-        <v>1.068387</v>
+        <v>1.068384</v>
       </c>
       <c r="H123" t="n">
-        <v>1.070827</v>
+        <v>1.070821</v>
       </c>
       <c r="I123" t="n">
-        <v>1.048998</v>
+        <v>1.048985</v>
       </c>
       <c r="J123" t="n">
         <v>0.64041</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>12.016369</v>
+        <v>12.016364</v>
       </c>
       <c r="F124" t="n">
-        <v>13.362156</v>
+        <v>13.362143</v>
       </c>
       <c r="G124" t="n">
-        <v>14.006419</v>
+        <v>14.006392</v>
       </c>
       <c r="H124" t="n">
-        <v>13.94228</v>
+        <v>13.942228</v>
       </c>
       <c r="I124" t="n">
-        <v>13.52976</v>
+        <v>13.529641</v>
       </c>
       <c r="J124" t="n">
         <v>9.727302999999999</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>10.081752</v>
+        <v>10.081758</v>
       </c>
       <c r="F125" t="n">
-        <v>10.372546</v>
+        <v>10.372561</v>
       </c>
       <c r="G125" t="n">
-        <v>9.948047000000001</v>
+        <v>9.948077</v>
       </c>
       <c r="H125" t="n">
-        <v>9.268772999999999</v>
+        <v>9.268829999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>8.625309</v>
+        <v>8.625441</v>
       </c>
       <c r="J125" t="n">
         <v>12.532031</v>
@@ -10254,58 +10254,58 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>58.675205</v>
+        <v>58.67517</v>
       </c>
       <c r="F130" t="n">
-        <v>65.717868</v>
+        <v>65.717789</v>
       </c>
       <c r="G130" t="n">
-        <v>73.35108</v>
+        <v>73.350943</v>
       </c>
       <c r="H130" t="n">
-        <v>79.848985</v>
+        <v>79.848778</v>
       </c>
       <c r="I130" t="n">
-        <v>85.75115</v>
+        <v>85.750863</v>
       </c>
       <c r="J130" t="n">
-        <v>90.83150500000001</v>
+        <v>90.83113</v>
       </c>
       <c r="K130" t="n">
-        <v>93.857117</v>
+        <v>93.856652</v>
       </c>
       <c r="L130" t="n">
-        <v>94.82276899999999</v>
+        <v>94.822215</v>
       </c>
       <c r="M130" t="n">
-        <v>96.75300900000001</v>
+        <v>96.752347</v>
       </c>
       <c r="N130" t="n">
-        <v>99.149738</v>
+        <v>99.14894700000001</v>
       </c>
       <c r="O130" t="n">
-        <v>102.332406</v>
+        <v>102.331458</v>
       </c>
       <c r="P130" t="n">
-        <v>105.838678</v>
+        <v>105.837537</v>
       </c>
       <c r="Q130" t="n">
-        <v>107.31797</v>
+        <v>107.316614</v>
       </c>
       <c r="R130" t="n">
-        <v>106.789679</v>
+        <v>106.788082</v>
       </c>
       <c r="S130" t="n">
-        <v>104.701043</v>
+        <v>104.699172</v>
       </c>
       <c r="T130" t="n">
-        <v>101.501444</v>
+        <v>101.499245</v>
       </c>
       <c r="U130" t="n">
-        <v>97.049589</v>
+        <v>97.04698399999999</v>
       </c>
       <c r="V130" t="n">
-        <v>91.468234</v>
+        <v>91.465081</v>
       </c>
     </row>
     <row r="131">
@@ -10330,58 +10330,58 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>9.506285</v>
+        <v>9.506278999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>12.0767</v>
+        <v>12.076685</v>
       </c>
       <c r="G131" t="n">
-        <v>13.876678</v>
+        <v>13.876651</v>
       </c>
       <c r="H131" t="n">
-        <v>15.144003</v>
+        <v>15.143962</v>
       </c>
       <c r="I131" t="n">
-        <v>16.21405</v>
+        <v>16.213994</v>
       </c>
       <c r="J131" t="n">
-        <v>17.201282</v>
+        <v>17.20121</v>
       </c>
       <c r="K131" t="n">
-        <v>17.823612</v>
+        <v>17.823523</v>
       </c>
       <c r="L131" t="n">
-        <v>18.034325</v>
+        <v>18.03422</v>
       </c>
       <c r="M131" t="n">
-        <v>18.336992</v>
+        <v>18.336868</v>
       </c>
       <c r="N131" t="n">
-        <v>18.59558</v>
+        <v>18.595436</v>
       </c>
       <c r="O131" t="n">
-        <v>18.971731</v>
+        <v>18.971563</v>
       </c>
       <c r="P131" t="n">
-        <v>19.467888</v>
+        <v>19.467691</v>
       </c>
       <c r="Q131" t="n">
-        <v>19.686354</v>
+        <v>19.686123</v>
       </c>
       <c r="R131" t="n">
-        <v>19.595914</v>
+        <v>19.595646</v>
       </c>
       <c r="S131" t="n">
-        <v>19.222602</v>
+        <v>19.22229</v>
       </c>
       <c r="T131" t="n">
-        <v>18.621224</v>
+        <v>18.620863</v>
       </c>
       <c r="U131" t="n">
-        <v>17.777016</v>
+        <v>17.776595</v>
       </c>
       <c r="V131" t="n">
-        <v>16.731918</v>
+        <v>16.731415</v>
       </c>
     </row>
     <row r="132">
@@ -10406,58 +10406,58 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>178.72032</v>
+        <v>178.720334</v>
       </c>
       <c r="F132" t="n">
-        <v>183.900828</v>
+        <v>183.900853</v>
       </c>
       <c r="G132" t="n">
-        <v>183.798628</v>
+        <v>183.798675</v>
       </c>
       <c r="H132" t="n">
-        <v>178.844703</v>
+        <v>178.844784</v>
       </c>
       <c r="I132" t="n">
-        <v>174.105343</v>
+        <v>174.105467</v>
       </c>
       <c r="J132" t="n">
-        <v>171.024088</v>
+        <v>171.024255</v>
       </c>
       <c r="K132" t="n">
-        <v>168.255828</v>
+        <v>168.256022</v>
       </c>
       <c r="L132" t="n">
-        <v>164.44281</v>
+        <v>164.443013</v>
       </c>
       <c r="M132" t="n">
-        <v>163.019647</v>
+        <v>163.019854</v>
       </c>
       <c r="N132" t="n">
-        <v>162.70998</v>
+        <v>162.710178</v>
       </c>
       <c r="O132" t="n">
-        <v>164.794244</v>
+        <v>164.794416</v>
       </c>
       <c r="P132" t="n">
-        <v>167.754186</v>
+        <v>167.754318</v>
       </c>
       <c r="Q132" t="n">
-        <v>166.600172</v>
+        <v>166.600269</v>
       </c>
       <c r="R132" t="n">
-        <v>161.319271</v>
+        <v>161.31935</v>
       </c>
       <c r="S132" t="n">
-        <v>153.668629</v>
+        <v>153.668705</v>
       </c>
       <c r="T132" t="n">
-        <v>145.567667</v>
+        <v>145.567744</v>
       </c>
       <c r="U132" t="n">
-        <v>137.500974</v>
+        <v>137.501035</v>
       </c>
       <c r="V132" t="n">
-        <v>129.371485</v>
+        <v>129.371512</v>
       </c>
     </row>
     <row r="133">
@@ -10482,58 +10482,58 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>39.162777</v>
+        <v>39.162829</v>
       </c>
       <c r="F133" t="n">
-        <v>57.420503</v>
+        <v>57.420592</v>
       </c>
       <c r="G133" t="n">
-        <v>79.78067799999999</v>
+        <v>79.780783</v>
       </c>
       <c r="H133" t="n">
-        <v>99.24009</v>
+        <v>99.24020400000001</v>
       </c>
       <c r="I133" t="n">
-        <v>114.64759</v>
+        <v>114.647724</v>
       </c>
       <c r="J133" t="n">
-        <v>126.670003</v>
+        <v>126.670181</v>
       </c>
       <c r="K133" t="n">
-        <v>135.594478</v>
+        <v>135.594724</v>
       </c>
       <c r="L133" t="n">
-        <v>142.604518</v>
+        <v>142.604849</v>
       </c>
       <c r="M133" t="n">
-        <v>152.814811</v>
+        <v>152.815246</v>
       </c>
       <c r="N133" t="n">
-        <v>165.872828</v>
+        <v>165.873384</v>
       </c>
       <c r="O133" t="n">
-        <v>183.395724</v>
+        <v>183.396426</v>
       </c>
       <c r="P133" t="n">
-        <v>205.541812</v>
+        <v>205.542688</v>
       </c>
       <c r="Q133" t="n">
-        <v>228.141948</v>
+        <v>228.143014</v>
       </c>
       <c r="R133" t="n">
-        <v>250.281421</v>
+        <v>250.28269</v>
       </c>
       <c r="S133" t="n">
-        <v>271.349453</v>
+        <v>271.350955</v>
       </c>
       <c r="T133" t="n">
-        <v>291.255676</v>
+        <v>291.257467</v>
       </c>
       <c r="U133" t="n">
-        <v>308.948654</v>
+        <v>308.950826</v>
       </c>
       <c r="V133" t="n">
-        <v>324.627581</v>
+        <v>324.630279</v>
       </c>
     </row>
     <row r="134">
@@ -10558,58 +10558,58 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>19.331515</v>
+        <v>19.331516</v>
       </c>
       <c r="F134" t="n">
-        <v>18.818459</v>
+        <v>18.818464</v>
       </c>
       <c r="G134" t="n">
-        <v>18.611091</v>
+        <v>18.611104</v>
       </c>
       <c r="H134" t="n">
-        <v>18.56684</v>
+        <v>18.566862</v>
       </c>
       <c r="I134" t="n">
-        <v>18.879447</v>
+        <v>18.87948</v>
       </c>
       <c r="J134" t="n">
-        <v>19.452994</v>
+        <v>19.453038</v>
       </c>
       <c r="K134" t="n">
-        <v>19.88541</v>
+        <v>19.885466</v>
       </c>
       <c r="L134" t="n">
-        <v>20.109276</v>
+        <v>20.109343</v>
       </c>
       <c r="M134" t="n">
-        <v>20.657423</v>
+        <v>20.657503</v>
       </c>
       <c r="N134" t="n">
-        <v>21.394321</v>
+        <v>21.394417</v>
       </c>
       <c r="O134" t="n">
-        <v>22.539417</v>
+        <v>22.539534</v>
       </c>
       <c r="P134" t="n">
-        <v>24.129475</v>
+        <v>24.129616</v>
       </c>
       <c r="Q134" t="n">
-        <v>25.66968</v>
+        <v>25.669845</v>
       </c>
       <c r="R134" t="n">
-        <v>27.051238</v>
+        <v>27.051429</v>
       </c>
       <c r="S134" t="n">
-        <v>28.270422</v>
+        <v>28.270639</v>
       </c>
       <c r="T134" t="n">
-        <v>29.3553</v>
+        <v>29.355544</v>
       </c>
       <c r="U134" t="n">
-        <v>30.223481</v>
+        <v>30.223757</v>
       </c>
       <c r="V134" t="n">
-        <v>30.864844</v>
+        <v>30.865159</v>
       </c>
     </row>
     <row r="135">
@@ -10634,58 +10634,58 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>7.279331</v>
+        <v>7.279342</v>
       </c>
       <c r="F135" t="n">
-        <v>9.617635999999999</v>
+        <v>9.617656</v>
       </c>
       <c r="G135" t="n">
-        <v>12.441746</v>
+        <v>12.441774</v>
       </c>
       <c r="H135" t="n">
-        <v>14.901627</v>
+        <v>14.901665</v>
       </c>
       <c r="I135" t="n">
-        <v>17.063562</v>
+        <v>17.063609</v>
       </c>
       <c r="J135" t="n">
-        <v>19.095733</v>
+        <v>19.09579</v>
       </c>
       <c r="K135" t="n">
-        <v>20.869655</v>
+        <v>20.869725</v>
       </c>
       <c r="L135" t="n">
-        <v>22.439747</v>
+        <v>22.439829</v>
       </c>
       <c r="M135" t="n">
-        <v>24.511095</v>
+        <v>24.511192</v>
       </c>
       <c r="N135" t="n">
-        <v>26.915305</v>
+        <v>26.915418</v>
       </c>
       <c r="O135" t="n">
-        <v>29.844649</v>
+        <v>29.84478</v>
       </c>
       <c r="P135" t="n">
-        <v>33.267131</v>
+        <v>33.267283</v>
       </c>
       <c r="Q135" t="n">
-        <v>36.508671</v>
+        <v>36.508843</v>
       </c>
       <c r="R135" t="n">
-        <v>39.430839</v>
+        <v>39.431031</v>
       </c>
       <c r="S135" t="n">
-        <v>41.987298</v>
+        <v>41.987511</v>
       </c>
       <c r="T135" t="n">
-        <v>44.152084</v>
+        <v>44.152321</v>
       </c>
       <c r="U135" t="n">
-        <v>45.749649</v>
+        <v>45.749914</v>
       </c>
       <c r="V135" t="n">
-        <v>46.75525</v>
+        <v>46.755556</v>
       </c>
     </row>
     <row r="136">
@@ -10710,58 +10710,58 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>26.888564</v>
+        <v>26.888545</v>
       </c>
       <c r="F136" t="n">
-        <v>26.20867</v>
+        <v>26.208635</v>
       </c>
       <c r="G136" t="n">
-        <v>24.154341</v>
+        <v>24.154296</v>
       </c>
       <c r="H136" t="n">
-        <v>21.774324</v>
+        <v>21.774275</v>
       </c>
       <c r="I136" t="n">
-        <v>20.317616</v>
+        <v>20.317564</v>
       </c>
       <c r="J136" t="n">
-        <v>20.428952</v>
+        <v>20.428891</v>
       </c>
       <c r="K136" t="n">
-        <v>20.900559</v>
+        <v>20.900485</v>
       </c>
       <c r="L136" t="n">
-        <v>21.359281</v>
+        <v>21.359191</v>
       </c>
       <c r="M136" t="n">
-        <v>22.387135</v>
+        <v>22.387022</v>
       </c>
       <c r="N136" t="n">
-        <v>23.458053</v>
+        <v>23.457911</v>
       </c>
       <c r="O136" t="n">
-        <v>24.64056</v>
+        <v>24.640385</v>
       </c>
       <c r="P136" t="n">
-        <v>25.922171</v>
+        <v>25.921955</v>
       </c>
       <c r="Q136" t="n">
-        <v>26.769632</v>
+        <v>26.769367</v>
       </c>
       <c r="R136" t="n">
-        <v>27.169503</v>
+        <v>27.169181</v>
       </c>
       <c r="S136" t="n">
-        <v>27.172152</v>
+        <v>27.171762</v>
       </c>
       <c r="T136" t="n">
-        <v>26.814846</v>
+        <v>26.814375</v>
       </c>
       <c r="U136" t="n">
-        <v>26.024073</v>
+        <v>26.023503</v>
       </c>
       <c r="V136" t="n">
-        <v>24.844771</v>
+        <v>24.844067</v>
       </c>
     </row>
     <row r="137">
@@ -10786,58 +10786,58 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>7.640061</v>
+        <v>7.640064</v>
       </c>
       <c r="F137" t="n">
-        <v>8.155849</v>
+        <v>8.155854</v>
       </c>
       <c r="G137" t="n">
-        <v>8.136146</v>
+        <v>8.136153999999999</v>
       </c>
       <c r="H137" t="n">
-        <v>7.86735</v>
+        <v>7.867361</v>
       </c>
       <c r="I137" t="n">
-        <v>7.717297</v>
+        <v>7.717311</v>
       </c>
       <c r="J137" t="n">
-        <v>7.69717</v>
+        <v>7.697187</v>
       </c>
       <c r="K137" t="n">
-        <v>7.630118</v>
+        <v>7.630136</v>
       </c>
       <c r="L137" t="n">
-        <v>7.452744</v>
+        <v>7.452764</v>
       </c>
       <c r="M137" t="n">
-        <v>7.347498</v>
+        <v>7.347519</v>
       </c>
       <c r="N137" t="n">
-        <v>7.234743</v>
+        <v>7.234766</v>
       </c>
       <c r="O137" t="n">
-        <v>7.170129</v>
+        <v>7.170156</v>
       </c>
       <c r="P137" t="n">
-        <v>7.15341</v>
+        <v>7.15344</v>
       </c>
       <c r="Q137" t="n">
-        <v>7.045955</v>
+        <v>7.045989</v>
       </c>
       <c r="R137" t="n">
-        <v>6.847401</v>
+        <v>6.847438</v>
       </c>
       <c r="S137" t="n">
-        <v>6.571556</v>
+        <v>6.571596</v>
       </c>
       <c r="T137" t="n">
-        <v>6.239535</v>
+        <v>6.239579</v>
       </c>
       <c r="U137" t="n">
-        <v>5.862946</v>
+        <v>5.862996</v>
       </c>
       <c r="V137" t="n">
-        <v>5.47676</v>
+        <v>5.476817</v>
       </c>
     </row>
     <row r="138">
@@ -10862,58 +10862,58 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>22.52618</v>
+        <v>22.526166</v>
       </c>
       <c r="F138" t="n">
-        <v>23.375774</v>
+        <v>23.375744</v>
       </c>
       <c r="G138" t="n">
-        <v>23.503922</v>
+        <v>23.503876</v>
       </c>
       <c r="H138" t="n">
-        <v>22.707365</v>
+        <v>22.707307</v>
       </c>
       <c r="I138" t="n">
-        <v>21.693943</v>
+        <v>21.693876</v>
       </c>
       <c r="J138" t="n">
-        <v>20.844342</v>
+        <v>20.844267</v>
       </c>
       <c r="K138" t="n">
-        <v>20.003285</v>
+        <v>20.003202</v>
       </c>
       <c r="L138" t="n">
-        <v>19.173748</v>
+        <v>19.173658</v>
       </c>
       <c r="M138" t="n">
-        <v>18.815493</v>
+        <v>18.815391</v>
       </c>
       <c r="N138" t="n">
-        <v>18.731038</v>
+        <v>18.730922</v>
       </c>
       <c r="O138" t="n">
-        <v>18.953895</v>
+        <v>18.95376</v>
       </c>
       <c r="P138" t="n">
-        <v>19.333374</v>
+        <v>19.333216</v>
       </c>
       <c r="Q138" t="n">
-        <v>19.409643</v>
+        <v>19.409459</v>
       </c>
       <c r="R138" t="n">
-        <v>19.232384</v>
+        <v>19.23217</v>
       </c>
       <c r="S138" t="n">
-        <v>18.835478</v>
+        <v>18.83523</v>
       </c>
       <c r="T138" t="n">
-        <v>18.272773</v>
+        <v>18.272485</v>
       </c>
       <c r="U138" t="n">
-        <v>17.53748</v>
+        <v>17.53714</v>
       </c>
       <c r="V138" t="n">
-        <v>16.674714</v>
+        <v>16.674305</v>
       </c>
     </row>
     <row r="139">
@@ -10938,58 +10938,58 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>32.396879</v>
+        <v>32.396853</v>
       </c>
       <c r="F139" t="n">
-        <v>35.529682</v>
+        <v>35.529625</v>
       </c>
       <c r="G139" t="n">
-        <v>39.173369</v>
+        <v>39.173272</v>
       </c>
       <c r="H139" t="n">
-        <v>42.356578</v>
+        <v>42.356434</v>
       </c>
       <c r="I139" t="n">
-        <v>45.293158</v>
+        <v>45.292962</v>
       </c>
       <c r="J139" t="n">
-        <v>47.745699</v>
+        <v>47.745445</v>
       </c>
       <c r="K139" t="n">
-        <v>49.057892</v>
+        <v>49.05758</v>
       </c>
       <c r="L139" t="n">
-        <v>49.252591</v>
+        <v>49.252222</v>
       </c>
       <c r="M139" t="n">
-        <v>49.933028</v>
+        <v>49.932591</v>
       </c>
       <c r="N139" t="n">
-        <v>50.846693</v>
+        <v>50.846176</v>
       </c>
       <c r="O139" t="n">
-        <v>52.231135</v>
+        <v>52.230519</v>
       </c>
       <c r="P139" t="n">
-        <v>53.795155</v>
+        <v>53.79442</v>
       </c>
       <c r="Q139" t="n">
-        <v>54.323928</v>
+        <v>54.32306</v>
       </c>
       <c r="R139" t="n">
-        <v>53.836218</v>
+        <v>53.835205</v>
       </c>
       <c r="S139" t="n">
-        <v>52.603445</v>
+        <v>52.602265</v>
       </c>
       <c r="T139" t="n">
-        <v>50.89278</v>
+        <v>50.891401</v>
       </c>
       <c r="U139" t="n">
-        <v>48.652507</v>
+        <v>48.650879</v>
       </c>
       <c r="V139" t="n">
-        <v>45.93033</v>
+        <v>45.928362</v>
       </c>
     </row>
     <row r="140">
@@ -11014,58 +11014,58 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>173.635205</v>
+        <v>173.63511</v>
       </c>
       <c r="F140" t="n">
-        <v>173.729865</v>
+        <v>173.72969</v>
       </c>
       <c r="G140" t="n">
-        <v>177.521797</v>
+        <v>177.521545</v>
       </c>
       <c r="H140" t="n">
-        <v>184.824679</v>
+        <v>184.824337</v>
       </c>
       <c r="I140" t="n">
-        <v>198.177033</v>
+        <v>198.176569</v>
       </c>
       <c r="J140" t="n">
-        <v>217.019198</v>
+        <v>217.018562</v>
       </c>
       <c r="K140" t="n">
-        <v>236.020862</v>
+        <v>236.020014</v>
       </c>
       <c r="L140" t="n">
-        <v>252.763388</v>
+        <v>252.762292</v>
       </c>
       <c r="M140" t="n">
-        <v>273.341546</v>
+        <v>273.340136</v>
       </c>
       <c r="N140" t="n">
-        <v>295.463763</v>
+        <v>295.461977</v>
       </c>
       <c r="O140" t="n">
-        <v>321.386941</v>
+        <v>321.384683</v>
       </c>
       <c r="P140" t="n">
-        <v>351.712223</v>
+        <v>351.709352</v>
       </c>
       <c r="Q140" t="n">
-        <v>380.307744</v>
+        <v>380.304105</v>
       </c>
       <c r="R140" t="n">
-        <v>406.317403</v>
+        <v>406.31279</v>
       </c>
       <c r="S140" t="n">
-        <v>429.964726</v>
+        <v>429.958856</v>
       </c>
       <c r="T140" t="n">
-        <v>451.285018</v>
+        <v>451.277489</v>
       </c>
       <c r="U140" t="n">
-        <v>468.517656</v>
+        <v>468.50788</v>
       </c>
       <c r="V140" t="n">
-        <v>481.165107</v>
+        <v>481.152079</v>
       </c>
     </row>
     <row r="141">
@@ -11090,58 +11090,58 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>7.273436</v>
+        <v>7.273484</v>
       </c>
       <c r="F141" t="n">
-        <v>8.185667</v>
+        <v>8.18577</v>
       </c>
       <c r="G141" t="n">
-        <v>9.185917999999999</v>
+        <v>9.186088</v>
       </c>
       <c r="H141" t="n">
-        <v>10.012163</v>
+        <v>10.012408</v>
       </c>
       <c r="I141" t="n">
-        <v>10.777992</v>
+        <v>10.778323</v>
       </c>
       <c r="J141" t="n">
-        <v>11.504779</v>
+        <v>11.505207</v>
       </c>
       <c r="K141" t="n">
-        <v>12.030254</v>
+        <v>12.030786</v>
       </c>
       <c r="L141" t="n">
-        <v>12.384233</v>
+        <v>12.384879</v>
       </c>
       <c r="M141" t="n">
-        <v>12.978072</v>
+        <v>12.978863</v>
       </c>
       <c r="N141" t="n">
-        <v>13.788299</v>
+        <v>13.789268</v>
       </c>
       <c r="O141" t="n">
-        <v>14.974853</v>
+        <v>14.976048</v>
       </c>
       <c r="P141" t="n">
-        <v>16.559531</v>
+        <v>16.561017</v>
       </c>
       <c r="Q141" t="n">
-        <v>18.219555</v>
+        <v>18.221389</v>
       </c>
       <c r="R141" t="n">
-        <v>19.875816</v>
+        <v>19.87807</v>
       </c>
       <c r="S141" t="n">
-        <v>21.434553</v>
+        <v>21.437328</v>
       </c>
       <c r="T141" t="n">
-        <v>22.867975</v>
+        <v>22.871421</v>
       </c>
       <c r="U141" t="n">
-        <v>24.110521</v>
+        <v>24.114859</v>
       </c>
       <c r="V141" t="n">
-        <v>25.211516</v>
+        <v>25.217134</v>
       </c>
     </row>
     <row r="142">
@@ -11166,58 +11166,58 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4.048052</v>
+        <v>4.048119</v>
       </c>
       <c r="F142" t="n">
-        <v>7.196821</v>
+        <v>7.196965</v>
       </c>
       <c r="G142" t="n">
-        <v>13.030432</v>
+        <v>13.030664</v>
       </c>
       <c r="H142" t="n">
-        <v>19.855418</v>
+        <v>19.855746</v>
       </c>
       <c r="I142" t="n">
-        <v>26.170367</v>
+        <v>26.170807</v>
       </c>
       <c r="J142" t="n">
-        <v>31.223971</v>
+        <v>31.224552</v>
       </c>
       <c r="K142" t="n">
-        <v>34.761495</v>
+        <v>34.762249</v>
       </c>
       <c r="L142" t="n">
-        <v>37.283378</v>
+        <v>37.284334</v>
       </c>
       <c r="M142" t="n">
-        <v>40.344044</v>
+        <v>40.345261</v>
       </c>
       <c r="N142" t="n">
-        <v>44.037118</v>
+        <v>44.038658</v>
       </c>
       <c r="O142" t="n">
-        <v>48.814247</v>
+        <v>48.816203</v>
       </c>
       <c r="P142" t="n">
-        <v>54.644933</v>
+        <v>54.647436</v>
       </c>
       <c r="Q142" t="n">
-        <v>60.323487</v>
+        <v>60.326663</v>
       </c>
       <c r="R142" t="n">
-        <v>65.569671</v>
+        <v>65.573677</v>
       </c>
       <c r="S142" t="n">
-        <v>70.296756</v>
+        <v>70.301802</v>
       </c>
       <c r="T142" t="n">
-        <v>74.51162100000001</v>
+        <v>74.51801</v>
       </c>
       <c r="U142" t="n">
-        <v>77.95139899999999</v>
+        <v>77.959575</v>
       </c>
       <c r="V142" t="n">
-        <v>80.66221400000001</v>
+        <v>80.67295900000001</v>
       </c>
     </row>
     <row r="143">
@@ -11470,58 +11470,58 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.561783</v>
+        <v>0.561782</v>
       </c>
       <c r="F146" t="n">
-        <v>0.604783</v>
+        <v>0.604782</v>
       </c>
       <c r="G146" t="n">
-        <v>0.607254</v>
+        <v>0.607251</v>
       </c>
       <c r="H146" t="n">
-        <v>0.585711</v>
+        <v>0.585707</v>
       </c>
       <c r="I146" t="n">
-        <v>0.591431</v>
+        <v>0.591426</v>
       </c>
       <c r="J146" t="n">
-        <v>0.589589</v>
+        <v>0.589584</v>
       </c>
       <c r="K146" t="n">
-        <v>0.587867</v>
+        <v>0.587862</v>
       </c>
       <c r="L146" t="n">
-        <v>0.581365</v>
+        <v>0.58136</v>
       </c>
       <c r="M146" t="n">
-        <v>0.572515</v>
+        <v>0.572509</v>
       </c>
       <c r="N146" t="n">
-        <v>0.577583</v>
+        <v>0.577577</v>
       </c>
       <c r="O146" t="n">
-        <v>0.59157</v>
+        <v>0.591564</v>
       </c>
       <c r="P146" t="n">
-        <v>0.615991</v>
+        <v>0.615984</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.642483</v>
+        <v>0.642476</v>
       </c>
       <c r="R146" t="n">
-        <v>0.6654600000000001</v>
+        <v>0.665451</v>
       </c>
       <c r="S146" t="n">
-        <v>0.681168</v>
+        <v>0.681159</v>
       </c>
       <c r="T146" t="n">
-        <v>0.689705</v>
+        <v>0.689696</v>
       </c>
       <c r="U146" t="n">
-        <v>0.695485</v>
+        <v>0.695476</v>
       </c>
       <c r="V146" t="n">
-        <v>0.6987100000000001</v>
+        <v>0.6987</v>
       </c>
     </row>
     <row r="147">
@@ -11552,52 +11552,52 @@
         <v>0.918995</v>
       </c>
       <c r="G147" t="n">
-        <v>1.042094</v>
+        <v>1.042093</v>
       </c>
       <c r="H147" t="n">
-        <v>1.062694</v>
+        <v>1.062693</v>
       </c>
       <c r="I147" t="n">
-        <v>1.086134</v>
+        <v>1.086132</v>
       </c>
       <c r="J147" t="n">
-        <v>1.072375</v>
+        <v>1.072373</v>
       </c>
       <c r="K147" t="n">
-        <v>1.059518</v>
+        <v>1.059516</v>
       </c>
       <c r="L147" t="n">
-        <v>1.032488</v>
+        <v>1.032486</v>
       </c>
       <c r="M147" t="n">
-        <v>0.997821</v>
+        <v>0.997819</v>
       </c>
       <c r="N147" t="n">
-        <v>0.986255</v>
+        <v>0.986252</v>
       </c>
       <c r="O147" t="n">
-        <v>0.985441</v>
+        <v>0.985438</v>
       </c>
       <c r="P147" t="n">
-        <v>0.994696</v>
+        <v>0.994693</v>
       </c>
       <c r="Q147" t="n">
-        <v>1.000898</v>
+        <v>1.000894</v>
       </c>
       <c r="R147" t="n">
-        <v>0.997929</v>
+        <v>0.997924</v>
       </c>
       <c r="S147" t="n">
-        <v>0.98246</v>
+        <v>0.982454</v>
       </c>
       <c r="T147" t="n">
-        <v>0.956619</v>
+        <v>0.956612</v>
       </c>
       <c r="U147" t="n">
-        <v>0.928682</v>
+        <v>0.928674</v>
       </c>
       <c r="V147" t="n">
-        <v>0.89859</v>
+        <v>0.898579</v>
       </c>
     </row>
     <row r="148">
@@ -11622,58 +11622,58 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>47.639778</v>
+        <v>47.639779</v>
       </c>
       <c r="F148" t="n">
-        <v>61.30145</v>
+        <v>61.301451</v>
       </c>
       <c r="G148" t="n">
-        <v>73.87052199999999</v>
+        <v>73.870525</v>
       </c>
       <c r="H148" t="n">
-        <v>79.37278999999999</v>
+        <v>79.372795</v>
       </c>
       <c r="I148" t="n">
-        <v>83.574663</v>
+        <v>83.574668</v>
       </c>
       <c r="J148" t="n">
-        <v>83.57549899999999</v>
+        <v>83.575506</v>
       </c>
       <c r="K148" t="n">
-        <v>82.47389099999999</v>
+        <v>82.47389800000001</v>
       </c>
       <c r="L148" t="n">
-        <v>79.91842699999999</v>
+        <v>79.918434</v>
       </c>
       <c r="M148" t="n">
-        <v>76.751282</v>
+        <v>76.75129</v>
       </c>
       <c r="N148" t="n">
-        <v>75.618197</v>
+        <v>75.618206</v>
       </c>
       <c r="O148" t="n">
-        <v>75.69541099999999</v>
+        <v>75.695421</v>
       </c>
       <c r="P148" t="n">
-        <v>76.768874</v>
+        <v>76.768885</v>
       </c>
       <c r="Q148" t="n">
-        <v>77.518248</v>
+        <v>77.51826</v>
       </c>
       <c r="R148" t="n">
-        <v>77.413501</v>
+        <v>77.41351400000001</v>
       </c>
       <c r="S148" t="n">
-        <v>76.218147</v>
+        <v>76.21816200000001</v>
       </c>
       <c r="T148" t="n">
-        <v>74.23380400000001</v>
+        <v>74.23381999999999</v>
       </c>
       <c r="U148" t="n">
-        <v>72.092631</v>
+        <v>72.09264899999999</v>
       </c>
       <c r="V148" t="n">
-        <v>69.72333</v>
+        <v>69.72335200000001</v>
       </c>
     </row>
     <row r="149">
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5.760313</v>
+        <v>5.760312</v>
       </c>
       <c r="F149" t="n">
         <v>6.461022</v>
@@ -11713,19 +11713,19 @@
         <v>9.048519000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>10.031733</v>
+        <v>10.031732</v>
       </c>
       <c r="K149" t="n">
-        <v>11.016338</v>
+        <v>11.016337</v>
       </c>
       <c r="L149" t="n">
-        <v>12.025098</v>
+        <v>12.025097</v>
       </c>
       <c r="M149" t="n">
-        <v>13.369587</v>
+        <v>13.369586</v>
       </c>
       <c r="N149" t="n">
-        <v>15.065647</v>
+        <v>15.065646</v>
       </c>
       <c r="O149" t="n">
         <v>16.937464</v>
@@ -11737,19 +11737,19 @@
         <v>21.271102</v>
       </c>
       <c r="R149" t="n">
-        <v>23.334872</v>
+        <v>23.334873</v>
       </c>
       <c r="S149" t="n">
-        <v>25.154488</v>
+        <v>25.154489</v>
       </c>
       <c r="T149" t="n">
-        <v>26.996218</v>
+        <v>26.99622</v>
       </c>
       <c r="U149" t="n">
-        <v>28.88857</v>
+        <v>28.888573</v>
       </c>
       <c r="V149" t="n">
-        <v>30.842617</v>
+        <v>30.84262</v>
       </c>
     </row>
     <row r="150">
@@ -11774,58 +11774,58 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>24.373245</v>
+        <v>24.373246</v>
       </c>
       <c r="F150" t="n">
-        <v>26.992326</v>
+        <v>26.992327</v>
       </c>
       <c r="G150" t="n">
-        <v>29.246057</v>
+        <v>29.246059</v>
       </c>
       <c r="H150" t="n">
-        <v>31.031756</v>
+        <v>31.031759</v>
       </c>
       <c r="I150" t="n">
-        <v>32.330825</v>
+        <v>32.330829</v>
       </c>
       <c r="J150" t="n">
-        <v>33.100882</v>
+        <v>33.100886</v>
       </c>
       <c r="K150" t="n">
-        <v>33.349784</v>
+        <v>33.34979</v>
       </c>
       <c r="L150" t="n">
-        <v>33.135819</v>
+        <v>33.135825</v>
       </c>
       <c r="M150" t="n">
-        <v>33.278341</v>
+        <v>33.278348</v>
       </c>
       <c r="N150" t="n">
-        <v>33.68465</v>
+        <v>33.684658</v>
       </c>
       <c r="O150" t="n">
-        <v>33.833469</v>
+        <v>33.833478</v>
       </c>
       <c r="P150" t="n">
-        <v>33.931085</v>
+        <v>33.931095</v>
       </c>
       <c r="Q150" t="n">
-        <v>33.67965</v>
+        <v>33.67966</v>
       </c>
       <c r="R150" t="n">
-        <v>32.830122</v>
+        <v>32.830133</v>
       </c>
       <c r="S150" t="n">
-        <v>31.405126</v>
+        <v>31.405137</v>
       </c>
       <c r="T150" t="n">
-        <v>29.803555</v>
+        <v>29.803566</v>
       </c>
       <c r="U150" t="n">
-        <v>28.07854</v>
+        <v>28.078551</v>
       </c>
       <c r="V150" t="n">
-        <v>26.263572</v>
+        <v>26.263583</v>
       </c>
     </row>
     <row r="151">
@@ -11856,52 +11856,52 @@
         <v>14.071342</v>
       </c>
       <c r="G151" t="n">
-        <v>15.88925</v>
+        <v>15.889251</v>
       </c>
       <c r="H151" t="n">
-        <v>17.522964</v>
+        <v>17.522965</v>
       </c>
       <c r="I151" t="n">
-        <v>18.578514</v>
+        <v>18.578515</v>
       </c>
       <c r="J151" t="n">
-        <v>19.072205</v>
+        <v>19.072206</v>
       </c>
       <c r="K151" t="n">
-        <v>19.213213</v>
+        <v>19.213214</v>
       </c>
       <c r="L151" t="n">
-        <v>19.129128</v>
+        <v>19.129129</v>
       </c>
       <c r="M151" t="n">
-        <v>19.376497</v>
+        <v>19.376499</v>
       </c>
       <c r="N151" t="n">
-        <v>19.947391</v>
+        <v>19.947393</v>
       </c>
       <c r="O151" t="n">
-        <v>20.503959</v>
+        <v>20.503961</v>
       </c>
       <c r="P151" t="n">
-        <v>21.094596</v>
+        <v>21.094598</v>
       </c>
       <c r="Q151" t="n">
-        <v>21.500672</v>
+        <v>21.500674</v>
       </c>
       <c r="R151" t="n">
-        <v>21.557578</v>
+        <v>21.55758</v>
       </c>
       <c r="S151" t="n">
-        <v>21.238451</v>
+        <v>21.238454</v>
       </c>
       <c r="T151" t="n">
-        <v>20.812565</v>
+        <v>20.812567</v>
       </c>
       <c r="U151" t="n">
-        <v>20.326236</v>
+        <v>20.326239</v>
       </c>
       <c r="V151" t="n">
-        <v>19.771331</v>
+        <v>19.771334</v>
       </c>
     </row>
     <row r="152">
@@ -11929,55 +11929,55 @@
         <v>15.8616</v>
       </c>
       <c r="F152" t="n">
-        <v>19.149359</v>
+        <v>19.149358</v>
       </c>
       <c r="G152" t="n">
-        <v>21.234988</v>
+        <v>21.234986</v>
       </c>
       <c r="H152" t="n">
-        <v>22.414437</v>
+        <v>22.414435</v>
       </c>
       <c r="I152" t="n">
-        <v>22.649302</v>
+        <v>22.6493</v>
       </c>
       <c r="J152" t="n">
-        <v>22.361661</v>
+        <v>22.361658</v>
       </c>
       <c r="K152" t="n">
-        <v>21.99016</v>
+        <v>21.990156</v>
       </c>
       <c r="L152" t="n">
-        <v>21.686894</v>
+        <v>21.68689</v>
       </c>
       <c r="M152" t="n">
-        <v>21.849121</v>
+        <v>21.849117</v>
       </c>
       <c r="N152" t="n">
-        <v>22.264883</v>
+        <v>22.264878</v>
       </c>
       <c r="O152" t="n">
-        <v>22.545418</v>
+        <v>22.545412</v>
       </c>
       <c r="P152" t="n">
-        <v>22.816424</v>
+        <v>22.816418</v>
       </c>
       <c r="Q152" t="n">
-        <v>22.879993</v>
+        <v>22.879986</v>
       </c>
       <c r="R152" t="n">
-        <v>22.571083</v>
+        <v>22.571076</v>
       </c>
       <c r="S152" t="n">
-        <v>21.899316</v>
+        <v>21.899308</v>
       </c>
       <c r="T152" t="n">
-        <v>21.149278</v>
+        <v>21.14927</v>
       </c>
       <c r="U152" t="n">
-        <v>20.35214</v>
+        <v>20.352132</v>
       </c>
       <c r="V152" t="n">
-        <v>19.513554</v>
+        <v>19.513545</v>
       </c>
     </row>
     <row r="153">
@@ -12008,52 +12008,52 @@
         <v>2.165278</v>
       </c>
       <c r="G153" t="n">
-        <v>2.476841</v>
+        <v>2.47684</v>
       </c>
       <c r="H153" t="n">
-        <v>2.864519</v>
+        <v>2.864518</v>
       </c>
       <c r="I153" t="n">
-        <v>3.24753</v>
+        <v>3.247529</v>
       </c>
       <c r="J153" t="n">
-        <v>3.602474</v>
+        <v>3.602472</v>
       </c>
       <c r="K153" t="n">
-        <v>3.927586</v>
+        <v>3.927584</v>
       </c>
       <c r="L153" t="n">
-        <v>4.240677</v>
+        <v>4.240675</v>
       </c>
       <c r="M153" t="n">
-        <v>4.6571</v>
+        <v>4.657097</v>
       </c>
       <c r="N153" t="n">
-        <v>5.196554</v>
+        <v>5.196551</v>
       </c>
       <c r="O153" t="n">
-        <v>5.7915</v>
+        <v>5.791496</v>
       </c>
       <c r="P153" t="n">
-        <v>6.465014</v>
+        <v>6.46501</v>
       </c>
       <c r="Q153" t="n">
-        <v>7.152705</v>
+        <v>7.1527</v>
       </c>
       <c r="R153" t="n">
-        <v>7.782199</v>
+        <v>7.782194</v>
       </c>
       <c r="S153" t="n">
-        <v>8.324559000000001</v>
+        <v>8.324553</v>
       </c>
       <c r="T153" t="n">
-        <v>8.867156</v>
+        <v>8.867149</v>
       </c>
       <c r="U153" t="n">
-        <v>9.420487</v>
+        <v>9.42048</v>
       </c>
       <c r="V153" t="n">
-        <v>9.984377</v>
+        <v>9.98437</v>
       </c>
     </row>
     <row r="154">
@@ -12096,7 +12096,7 @@
         <v>2.729853</v>
       </c>
       <c r="K154" t="n">
-        <v>2.61577</v>
+        <v>2.615769</v>
       </c>
       <c r="L154" t="n">
         <v>2.499112</v>
@@ -12105,31 +12105,31 @@
         <v>2.434216</v>
       </c>
       <c r="N154" t="n">
-        <v>2.399668</v>
+        <v>2.399667</v>
       </c>
       <c r="O154" t="n">
-        <v>2.351807</v>
+        <v>2.351806</v>
       </c>
       <c r="P154" t="n">
         <v>2.305617</v>
       </c>
       <c r="Q154" t="n">
-        <v>2.242474</v>
+        <v>2.242473</v>
       </c>
       <c r="R154" t="n">
-        <v>2.151532</v>
+        <v>2.151531</v>
       </c>
       <c r="S154" t="n">
-        <v>2.035041</v>
+        <v>2.03504</v>
       </c>
       <c r="T154" t="n">
-        <v>1.919522</v>
+        <v>1.919521</v>
       </c>
       <c r="U154" t="n">
-        <v>1.806543</v>
+        <v>1.806542</v>
       </c>
       <c r="V154" t="n">
-        <v>1.694326</v>
+        <v>1.694325</v>
       </c>
     </row>
     <row r="155">
@@ -12157,55 +12157,55 @@
         <v>2.460983</v>
       </c>
       <c r="F155" t="n">
-        <v>3.391742</v>
+        <v>3.391741</v>
       </c>
       <c r="G155" t="n">
-        <v>4.154243</v>
+        <v>4.154242</v>
       </c>
       <c r="H155" t="n">
-        <v>5.066155</v>
+        <v>5.066154</v>
       </c>
       <c r="I155" t="n">
-        <v>5.969692</v>
+        <v>5.96969</v>
       </c>
       <c r="J155" t="n">
-        <v>6.915319</v>
+        <v>6.915318</v>
       </c>
       <c r="K155" t="n">
-        <v>7.901791</v>
+        <v>7.901789</v>
       </c>
       <c r="L155" t="n">
-        <v>8.963872</v>
+        <v>8.963869000000001</v>
       </c>
       <c r="M155" t="n">
-        <v>10.301777</v>
+        <v>10.301773</v>
       </c>
       <c r="N155" t="n">
-        <v>11.783005</v>
+        <v>11.783001</v>
       </c>
       <c r="O155" t="n">
-        <v>13.160892</v>
+        <v>13.160888</v>
       </c>
       <c r="P155" t="n">
-        <v>14.63497</v>
+        <v>14.634964</v>
       </c>
       <c r="Q155" t="n">
-        <v>16.258596</v>
+        <v>16.258589</v>
       </c>
       <c r="R155" t="n">
-        <v>17.750824</v>
+        <v>17.750817</v>
       </c>
       <c r="S155" t="n">
-        <v>19.430728</v>
+        <v>19.43072</v>
       </c>
       <c r="T155" t="n">
-        <v>21.319986</v>
+        <v>21.319977</v>
       </c>
       <c r="U155" t="n">
-        <v>23.520168</v>
+        <v>23.520158</v>
       </c>
       <c r="V155" t="n">
-        <v>26.284481</v>
+        <v>26.28447</v>
       </c>
     </row>
     <row r="156">
@@ -12239,49 +12239,49 @@
         <v>36.415923</v>
       </c>
       <c r="H156" t="n">
-        <v>40.132762</v>
+        <v>40.132763</v>
       </c>
       <c r="I156" t="n">
-        <v>42.592127</v>
+        <v>42.592128</v>
       </c>
       <c r="J156" t="n">
-        <v>44.41713</v>
+        <v>44.417132</v>
       </c>
       <c r="K156" t="n">
-        <v>45.544036</v>
+        <v>45.544039</v>
       </c>
       <c r="L156" t="n">
-        <v>46.287126</v>
+        <v>46.28713</v>
       </c>
       <c r="M156" t="n">
-        <v>47.73689</v>
+        <v>47.736895</v>
       </c>
       <c r="N156" t="n">
-        <v>49.064457</v>
+        <v>49.064462</v>
       </c>
       <c r="O156" t="n">
-        <v>49.244471</v>
+        <v>49.244478</v>
       </c>
       <c r="P156" t="n">
-        <v>49.176162</v>
+        <v>49.17617</v>
       </c>
       <c r="Q156" t="n">
-        <v>49.0323</v>
+        <v>49.032309</v>
       </c>
       <c r="R156" t="n">
-        <v>48.061328</v>
+        <v>48.061338</v>
       </c>
       <c r="S156" t="n">
-        <v>47.252762</v>
+        <v>47.252774</v>
       </c>
       <c r="T156" t="n">
-        <v>46.643723</v>
+        <v>46.643736</v>
       </c>
       <c r="U156" t="n">
-        <v>46.422745</v>
+        <v>46.422759</v>
       </c>
       <c r="V156" t="n">
-        <v>46.984789</v>
+        <v>46.984805</v>
       </c>
     </row>
     <row r="157">
@@ -12324,10 +12324,10 @@
         <v>1.226295</v>
       </c>
       <c r="K157" t="n">
-        <v>1.252933</v>
+        <v>1.252934</v>
       </c>
       <c r="L157" t="n">
-        <v>1.28038</v>
+        <v>1.280381</v>
       </c>
       <c r="M157" t="n">
         <v>1.341276</v>
@@ -12339,25 +12339,25 @@
         <v>1.426907</v>
       </c>
       <c r="P157" t="n">
-        <v>1.436389</v>
+        <v>1.43639</v>
       </c>
       <c r="Q157" t="n">
-        <v>1.43222</v>
+        <v>1.432221</v>
       </c>
       <c r="R157" t="n">
-        <v>1.394206</v>
+        <v>1.394207</v>
       </c>
       <c r="S157" t="n">
-        <v>1.355024</v>
+        <v>1.355025</v>
       </c>
       <c r="T157" t="n">
         <v>1.31848</v>
       </c>
       <c r="U157" t="n">
-        <v>1.289202</v>
+        <v>1.289203</v>
       </c>
       <c r="V157" t="n">
-        <v>1.277861</v>
+        <v>1.277862</v>
       </c>
     </row>
     <row r="158">
@@ -12388,7 +12388,7 @@
         <v>6.614289</v>
       </c>
       <c r="G158" t="n">
-        <v>6.541802</v>
+        <v>6.541803</v>
       </c>
       <c r="H158" t="n">
         <v>6.569126</v>
@@ -12397,7 +12397,7 @@
         <v>6.584618</v>
       </c>
       <c r="J158" t="n">
-        <v>6.639697</v>
+        <v>6.639698</v>
       </c>
       <c r="K158" t="n">
         <v>6.696625</v>
@@ -12406,34 +12406,34 @@
         <v>6.749322</v>
       </c>
       <c r="M158" t="n">
-        <v>6.904632</v>
+        <v>6.904633</v>
       </c>
       <c r="N158" t="n">
-        <v>7.027069</v>
+        <v>7.02707</v>
       </c>
       <c r="O158" t="n">
-        <v>6.986026</v>
+        <v>6.986027</v>
       </c>
       <c r="P158" t="n">
-        <v>6.902369</v>
+        <v>6.90237</v>
       </c>
       <c r="Q158" t="n">
-        <v>6.786101</v>
+        <v>6.786102</v>
       </c>
       <c r="R158" t="n">
-        <v>6.578547</v>
+        <v>6.578548</v>
       </c>
       <c r="S158" t="n">
-        <v>6.439835</v>
+        <v>6.439836</v>
       </c>
       <c r="T158" t="n">
-        <v>6.369622</v>
+        <v>6.369623</v>
       </c>
       <c r="U158" t="n">
-        <v>6.36355</v>
+        <v>6.363552</v>
       </c>
       <c r="V158" t="n">
-        <v>6.451696</v>
+        <v>6.451697</v>
       </c>
     </row>
     <row r="159">
@@ -12473,7 +12473,7 @@
         <v>0.729483</v>
       </c>
       <c r="J159" t="n">
-        <v>0.758235</v>
+        <v>0.758236</v>
       </c>
       <c r="K159" t="n">
         <v>0.788411</v>
@@ -12485,22 +12485,22 @@
         <v>0.85349</v>
       </c>
       <c r="N159" t="n">
-        <v>0.879979</v>
+        <v>0.87998</v>
       </c>
       <c r="O159" t="n">
-        <v>0.884664</v>
+        <v>0.884665</v>
       </c>
       <c r="P159" t="n">
-        <v>0.88525</v>
+        <v>0.885251</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.879395</v>
+        <v>0.879396</v>
       </c>
       <c r="R159" t="n">
-        <v>0.848804</v>
+        <v>0.848805</v>
       </c>
       <c r="S159" t="n">
-        <v>0.811795</v>
+        <v>0.811796</v>
       </c>
       <c r="T159" t="n">
         <v>0.771983</v>
@@ -12509,7 +12509,7 @@
         <v>0.736604</v>
       </c>
       <c r="V159" t="n">
-        <v>0.715121</v>
+        <v>0.715122</v>
       </c>
     </row>
     <row r="160">
@@ -12540,52 +12540,52 @@
         <v>2.884267</v>
       </c>
       <c r="G160" t="n">
-        <v>3.513144</v>
+        <v>3.513143</v>
       </c>
       <c r="H160" t="n">
-        <v>4.26302</v>
+        <v>4.263019</v>
       </c>
       <c r="I160" t="n">
-        <v>4.978515</v>
+        <v>4.978514</v>
       </c>
       <c r="J160" t="n">
-        <v>5.629733</v>
+        <v>5.629731</v>
       </c>
       <c r="K160" t="n">
-        <v>6.22182</v>
+        <v>6.221818</v>
       </c>
       <c r="L160" t="n">
-        <v>6.768406</v>
+        <v>6.768404</v>
       </c>
       <c r="M160" t="n">
-        <v>7.484737</v>
+        <v>7.484735</v>
       </c>
       <c r="N160" t="n">
-        <v>8.306957000000001</v>
+        <v>8.306953999999999</v>
       </c>
       <c r="O160" t="n">
-        <v>9.087387</v>
+        <v>9.087383000000001</v>
       </c>
       <c r="P160" t="n">
-        <v>9.965889000000001</v>
+        <v>9.965884000000001</v>
       </c>
       <c r="Q160" t="n">
-        <v>10.968981</v>
+        <v>10.968976</v>
       </c>
       <c r="R160" t="n">
-        <v>11.887939</v>
+        <v>11.887933</v>
       </c>
       <c r="S160" t="n">
-        <v>12.928071</v>
+        <v>12.928065</v>
       </c>
       <c r="T160" t="n">
-        <v>14.128257</v>
+        <v>14.12825</v>
       </c>
       <c r="U160" t="n">
-        <v>15.579341</v>
+        <v>15.579334</v>
       </c>
       <c r="V160" t="n">
-        <v>17.489635</v>
+        <v>17.489627</v>
       </c>
     </row>
     <row r="161">
@@ -12692,10 +12692,10 @@
         <v>1.848936</v>
       </c>
       <c r="G162" t="n">
-        <v>1.373537</v>
+        <v>1.373538</v>
       </c>
       <c r="H162" t="n">
-        <v>1.129573</v>
+        <v>1.129574</v>
       </c>
       <c r="I162" t="n">
         <v>1.009001</v>
@@ -12704,10 +12704,10 @@
         <v>0.960282</v>
       </c>
       <c r="K162" t="n">
-        <v>0.947944</v>
+        <v>0.947945</v>
       </c>
       <c r="L162" t="n">
-        <v>0.95455</v>
+        <v>0.954551</v>
       </c>
       <c r="M162" t="n">
         <v>0.993955</v>
@@ -12716,7 +12716,7 @@
         <v>1.05258</v>
       </c>
       <c r="O162" t="n">
-        <v>1.101858</v>
+        <v>1.101859</v>
       </c>
       <c r="P162" t="n">
         <v>1.140313</v>
@@ -12725,10 +12725,10 @@
         <v>1.149417</v>
       </c>
       <c r="R162" t="n">
-        <v>1.111743</v>
+        <v>1.111744</v>
       </c>
       <c r="S162" t="n">
-        <v>1.075032</v>
+        <v>1.075033</v>
       </c>
       <c r="T162" t="n">
         <v>1.033587</v>
@@ -12737,7 +12737,7 @@
         <v>0.990596</v>
       </c>
       <c r="V162" t="n">
-        <v>0.944289</v>
+        <v>0.94429</v>
       </c>
     </row>
     <row r="163">
@@ -12838,58 +12838,58 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2.801818</v>
+        <v>2.801817</v>
       </c>
       <c r="F164" t="n">
-        <v>3.802227</v>
+        <v>3.802226</v>
       </c>
       <c r="G164" t="n">
-        <v>4.82204</v>
+        <v>4.822037</v>
       </c>
       <c r="H164" t="n">
-        <v>5.763501</v>
+        <v>5.763497</v>
       </c>
       <c r="I164" t="n">
-        <v>6.469603</v>
+        <v>6.469598</v>
       </c>
       <c r="J164" t="n">
-        <v>6.925819</v>
+        <v>6.925814</v>
       </c>
       <c r="K164" t="n">
-        <v>7.13801</v>
+        <v>7.138004</v>
       </c>
       <c r="L164" t="n">
-        <v>7.084003</v>
+        <v>7.083996</v>
       </c>
       <c r="M164" t="n">
-        <v>7.066397</v>
+        <v>7.06639</v>
       </c>
       <c r="N164" t="n">
-        <v>7.084324</v>
+        <v>7.084316</v>
       </c>
       <c r="O164" t="n">
-        <v>7.087113</v>
+        <v>7.087104</v>
       </c>
       <c r="P164" t="n">
-        <v>7.136238</v>
+        <v>7.136228</v>
       </c>
       <c r="Q164" t="n">
-        <v>7.125561</v>
+        <v>7.12555</v>
       </c>
       <c r="R164" t="n">
-        <v>6.906711</v>
+        <v>6.9067</v>
       </c>
       <c r="S164" t="n">
-        <v>6.739691</v>
+        <v>6.73968</v>
       </c>
       <c r="T164" t="n">
-        <v>6.572231</v>
+        <v>6.572219</v>
       </c>
       <c r="U164" t="n">
-        <v>6.4224</v>
+        <v>6.422388</v>
       </c>
       <c r="V164" t="n">
-        <v>6.273871</v>
+        <v>6.273859</v>
       </c>
     </row>
     <row r="165">
@@ -12920,52 +12920,52 @@
         <v>3.548846</v>
       </c>
       <c r="G165" t="n">
-        <v>3.62455</v>
+        <v>3.624549</v>
       </c>
       <c r="H165" t="n">
-        <v>3.674864</v>
+        <v>3.674862</v>
       </c>
       <c r="I165" t="n">
-        <v>3.721812</v>
+        <v>3.72181</v>
       </c>
       <c r="J165" t="n">
-        <v>3.78391</v>
+        <v>3.783908</v>
       </c>
       <c r="K165" t="n">
-        <v>3.838604</v>
+        <v>3.838601</v>
       </c>
       <c r="L165" t="n">
-        <v>3.901971</v>
+        <v>3.901967</v>
       </c>
       <c r="M165" t="n">
-        <v>4.07537</v>
+        <v>4.075366</v>
       </c>
       <c r="N165" t="n">
-        <v>4.33594</v>
+        <v>4.335935</v>
       </c>
       <c r="O165" t="n">
-        <v>4.622737</v>
+        <v>4.622732</v>
       </c>
       <c r="P165" t="n">
-        <v>4.974599</v>
+        <v>4.974593</v>
       </c>
       <c r="Q165" t="n">
-        <v>5.322546</v>
+        <v>5.322539</v>
       </c>
       <c r="R165" t="n">
-        <v>5.537223</v>
+        <v>5.537215</v>
       </c>
       <c r="S165" t="n">
-        <v>5.802951</v>
+        <v>5.802943</v>
       </c>
       <c r="T165" t="n">
-        <v>6.076152</v>
+        <v>6.076142</v>
       </c>
       <c r="U165" t="n">
-        <v>6.363362</v>
+        <v>6.363352</v>
       </c>
       <c r="V165" t="n">
-        <v>6.654376</v>
+        <v>6.654365</v>
       </c>
     </row>
     <row r="166">
@@ -12990,58 +12990,58 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6.494538</v>
+        <v>6.494535</v>
       </c>
       <c r="F166" t="n">
-        <v>7.312643</v>
+        <v>7.312637</v>
       </c>
       <c r="G166" t="n">
-        <v>7.663889</v>
+        <v>7.66388</v>
       </c>
       <c r="H166" t="n">
-        <v>7.897122</v>
+        <v>7.89711</v>
       </c>
       <c r="I166" t="n">
-        <v>7.911355</v>
+        <v>7.91134</v>
       </c>
       <c r="J166" t="n">
-        <v>7.814765</v>
+        <v>7.814748</v>
       </c>
       <c r="K166" t="n">
-        <v>7.588486</v>
+        <v>7.588467</v>
       </c>
       <c r="L166" t="n">
-        <v>7.288369</v>
+        <v>7.288348</v>
       </c>
       <c r="M166" t="n">
-        <v>7.100598</v>
+        <v>7.100575</v>
       </c>
       <c r="N166" t="n">
-        <v>6.977895</v>
+        <v>6.97787</v>
       </c>
       <c r="O166" t="n">
-        <v>6.825151</v>
+        <v>6.825124</v>
       </c>
       <c r="P166" t="n">
-        <v>6.697897</v>
+        <v>6.697868</v>
       </c>
       <c r="Q166" t="n">
-        <v>6.501602</v>
+        <v>6.501571</v>
       </c>
       <c r="R166" t="n">
-        <v>6.120012</v>
+        <v>6.119981</v>
       </c>
       <c r="S166" t="n">
-        <v>5.805603</v>
+        <v>5.80557</v>
       </c>
       <c r="T166" t="n">
-        <v>5.505627</v>
+        <v>5.505594</v>
       </c>
       <c r="U166" t="n">
-        <v>5.231185</v>
+        <v>5.231151</v>
       </c>
       <c r="V166" t="n">
-        <v>4.972275</v>
+        <v>4.97224</v>
       </c>
     </row>
     <row r="167">
@@ -13066,58 +13066,58 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>83.23418599999999</v>
+        <v>83.234193</v>
       </c>
       <c r="F167" t="n">
-        <v>89.804704</v>
+        <v>89.804717</v>
       </c>
       <c r="G167" t="n">
-        <v>92.343835</v>
+        <v>92.343852</v>
       </c>
       <c r="H167" t="n">
-        <v>96.821324</v>
+        <v>96.82134600000001</v>
       </c>
       <c r="I167" t="n">
-        <v>101.58977</v>
+        <v>101.589798</v>
       </c>
       <c r="J167" t="n">
-        <v>106.068466</v>
+        <v>106.068501</v>
       </c>
       <c r="K167" t="n">
-        <v>109.190752</v>
+        <v>109.190793</v>
       </c>
       <c r="L167" t="n">
-        <v>110.919558</v>
+        <v>110.919606</v>
       </c>
       <c r="M167" t="n">
-        <v>114.131189</v>
+        <v>114.131245</v>
       </c>
       <c r="N167" t="n">
-        <v>118.339526</v>
+        <v>118.33959</v>
       </c>
       <c r="O167" t="n">
-        <v>121.775163</v>
+        <v>121.775236</v>
       </c>
       <c r="P167" t="n">
-        <v>125.438815</v>
+        <v>125.438898</v>
       </c>
       <c r="Q167" t="n">
-        <v>127.477669</v>
+        <v>127.477762</v>
       </c>
       <c r="R167" t="n">
-        <v>125.172023</v>
+        <v>125.172124</v>
       </c>
       <c r="S167" t="n">
-        <v>123.121957</v>
+        <v>123.122066</v>
       </c>
       <c r="T167" t="n">
-        <v>120.20153</v>
+        <v>120.201648</v>
       </c>
       <c r="U167" t="n">
-        <v>116.594641</v>
+        <v>116.594766</v>
       </c>
       <c r="V167" t="n">
-        <v>112.262828</v>
+        <v>112.26296</v>
       </c>
     </row>
     <row r="168">
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1.480811</v>
+        <v>1.480812</v>
       </c>
       <c r="F168" t="n">
         <v>1.749764</v>
@@ -13151,49 +13151,49 @@
         <v>1.9257</v>
       </c>
       <c r="H168" t="n">
-        <v>2.082473</v>
+        <v>2.082474</v>
       </c>
       <c r="I168" t="n">
-        <v>2.197441</v>
+        <v>2.197442</v>
       </c>
       <c r="J168" t="n">
-        <v>2.289079</v>
+        <v>2.28908</v>
       </c>
       <c r="K168" t="n">
-        <v>2.351254</v>
+        <v>2.351255</v>
       </c>
       <c r="L168" t="n">
-        <v>2.389583</v>
+        <v>2.389585</v>
       </c>
       <c r="M168" t="n">
-        <v>2.464816</v>
+        <v>2.464818</v>
       </c>
       <c r="N168" t="n">
-        <v>2.564388</v>
+        <v>2.56439</v>
       </c>
       <c r="O168" t="n">
-        <v>2.645647</v>
+        <v>2.645649</v>
       </c>
       <c r="P168" t="n">
-        <v>2.72568</v>
+        <v>2.725683</v>
       </c>
       <c r="Q168" t="n">
-        <v>2.763342</v>
+        <v>2.763345</v>
       </c>
       <c r="R168" t="n">
-        <v>2.7028</v>
+        <v>2.702803</v>
       </c>
       <c r="S168" t="n">
-        <v>2.647485</v>
+        <v>2.647489</v>
       </c>
       <c r="T168" t="n">
-        <v>2.57659</v>
+        <v>2.576594</v>
       </c>
       <c r="U168" t="n">
-        <v>2.496058</v>
+        <v>2.496062</v>
       </c>
       <c r="V168" t="n">
-        <v>2.40368</v>
+        <v>2.403684</v>
       </c>
     </row>
     <row r="169">
@@ -13218,58 +13218,58 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>37.239639</v>
+        <v>37.239634</v>
       </c>
       <c r="F169" t="n">
-        <v>43.103514</v>
+        <v>43.103503</v>
       </c>
       <c r="G169" t="n">
-        <v>46.620322</v>
+        <v>46.620305</v>
       </c>
       <c r="H169" t="n">
-        <v>51.508172</v>
+        <v>51.508146</v>
       </c>
       <c r="I169" t="n">
-        <v>57.252028</v>
+        <v>57.251994</v>
       </c>
       <c r="J169" t="n">
-        <v>63.741834</v>
+        <v>63.741792</v>
       </c>
       <c r="K169" t="n">
-        <v>70.37503700000001</v>
+        <v>70.37498600000001</v>
       </c>
       <c r="L169" t="n">
-        <v>76.56704499999999</v>
+        <v>76.56698400000001</v>
       </c>
       <c r="M169" t="n">
-        <v>84.50764100000001</v>
+        <v>84.507569</v>
       </c>
       <c r="N169" t="n">
-        <v>94.547259</v>
+        <v>94.547173</v>
       </c>
       <c r="O169" t="n">
-        <v>105.757333</v>
+        <v>105.757233</v>
       </c>
       <c r="P169" t="n">
-        <v>118.863181</v>
+        <v>118.863067</v>
       </c>
       <c r="Q169" t="n">
-        <v>132.102887</v>
+        <v>132.102758</v>
       </c>
       <c r="R169" t="n">
-        <v>142.019729</v>
+        <v>142.019589</v>
       </c>
       <c r="S169" t="n">
-        <v>153.128136</v>
+        <v>153.127984</v>
       </c>
       <c r="T169" t="n">
-        <v>164.156458</v>
+        <v>164.156295</v>
       </c>
       <c r="U169" t="n">
-        <v>175.197842</v>
+        <v>175.197669</v>
       </c>
       <c r="V169" t="n">
-        <v>185.960843</v>
+        <v>185.960661</v>
       </c>
     </row>
     <row r="170">
@@ -13297,55 +13297,55 @@
         <v>1.965592</v>
       </c>
       <c r="F170" t="n">
-        <v>2.858782</v>
+        <v>2.858781</v>
       </c>
       <c r="G170" t="n">
-        <v>3.68285</v>
+        <v>3.682848</v>
       </c>
       <c r="H170" t="n">
-        <v>4.390594</v>
+        <v>4.390592</v>
       </c>
       <c r="I170" t="n">
-        <v>4.90957</v>
+        <v>4.909567</v>
       </c>
       <c r="J170" t="n">
-        <v>5.290072</v>
+        <v>5.290068</v>
       </c>
       <c r="K170" t="n">
-        <v>5.597158</v>
+        <v>5.597153</v>
       </c>
       <c r="L170" t="n">
-        <v>5.891236</v>
+        <v>5.89123</v>
       </c>
       <c r="M170" t="n">
-        <v>6.338367</v>
+        <v>6.33836</v>
       </c>
       <c r="N170" t="n">
-        <v>6.910158</v>
+        <v>6.91015</v>
       </c>
       <c r="O170" t="n">
-        <v>7.486534</v>
+        <v>7.486524</v>
       </c>
       <c r="P170" t="n">
-        <v>8.114722</v>
+        <v>8.114711</v>
       </c>
       <c r="Q170" t="n">
-        <v>8.678881000000001</v>
+        <v>8.678869000000001</v>
       </c>
       <c r="R170" t="n">
-        <v>8.999431</v>
+        <v>8.999416999999999</v>
       </c>
       <c r="S170" t="n">
-        <v>9.392147</v>
+        <v>9.392132</v>
       </c>
       <c r="T170" t="n">
-        <v>9.774919000000001</v>
+        <v>9.774902000000001</v>
       </c>
       <c r="U170" t="n">
-        <v>10.153282</v>
+        <v>10.153264</v>
       </c>
       <c r="V170" t="n">
-        <v>10.515933</v>
+        <v>10.515913</v>
       </c>
     </row>
     <row r="171">
@@ -13370,58 +13370,58 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>10.773938</v>
+        <v>10.773937</v>
       </c>
       <c r="F171" t="n">
-        <v>12.100726</v>
+        <v>12.100724</v>
       </c>
       <c r="G171" t="n">
-        <v>12.689806</v>
+        <v>12.689802</v>
       </c>
       <c r="H171" t="n">
-        <v>13.077625</v>
+        <v>13.077619</v>
       </c>
       <c r="I171" t="n">
-        <v>13.133388</v>
+        <v>13.133381</v>
       </c>
       <c r="J171" t="n">
-        <v>13.00444</v>
+        <v>13.004432</v>
       </c>
       <c r="K171" t="n">
-        <v>12.686369</v>
+        <v>12.686361</v>
       </c>
       <c r="L171" t="n">
-        <v>12.238266</v>
+        <v>12.238256</v>
       </c>
       <c r="M171" t="n">
-        <v>11.97393</v>
+        <v>11.97392</v>
       </c>
       <c r="N171" t="n">
-        <v>11.816185</v>
+        <v>11.816173</v>
       </c>
       <c r="O171" t="n">
-        <v>11.593524</v>
+        <v>11.593512</v>
       </c>
       <c r="P171" t="n">
-        <v>11.390924</v>
+        <v>11.39091</v>
       </c>
       <c r="Q171" t="n">
-        <v>11.032573</v>
+        <v>11.032559</v>
       </c>
       <c r="R171" t="n">
-        <v>10.314782</v>
+        <v>10.314768</v>
       </c>
       <c r="S171" t="n">
-        <v>9.661132</v>
+        <v>9.661118</v>
       </c>
       <c r="T171" t="n">
-        <v>8.996566</v>
+        <v>8.996551999999999</v>
       </c>
       <c r="U171" t="n">
-        <v>8.353994999999999</v>
+        <v>8.353980999999999</v>
       </c>
       <c r="V171" t="n">
-        <v>7.733549</v>
+        <v>7.733535</v>
       </c>
     </row>
     <row r="172">
@@ -13446,58 +13446,58 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>18.161266</v>
+        <v>18.161267</v>
       </c>
       <c r="F172" t="n">
-        <v>19.602225</v>
+        <v>19.602227</v>
       </c>
       <c r="G172" t="n">
-        <v>19.240385</v>
+        <v>19.240388</v>
       </c>
       <c r="H172" t="n">
-        <v>18.832349</v>
+        <v>18.832352</v>
       </c>
       <c r="I172" t="n">
-        <v>18.531765</v>
+        <v>18.53177</v>
       </c>
       <c r="J172" t="n">
-        <v>18.327911</v>
+        <v>18.327916</v>
       </c>
       <c r="K172" t="n">
-        <v>18.071353</v>
+        <v>18.071359</v>
       </c>
       <c r="L172" t="n">
-        <v>17.722099</v>
+        <v>17.722104</v>
       </c>
       <c r="M172" t="n">
-        <v>17.701194</v>
+        <v>17.701201</v>
       </c>
       <c r="N172" t="n">
-        <v>17.882693</v>
+        <v>17.882701</v>
       </c>
       <c r="O172" t="n">
-        <v>17.952349</v>
+        <v>17.952357</v>
       </c>
       <c r="P172" t="n">
-        <v>18.047465</v>
+        <v>18.047474</v>
       </c>
       <c r="Q172" t="n">
-        <v>17.900946</v>
+        <v>17.900956</v>
       </c>
       <c r="R172" t="n">
-        <v>17.171106</v>
+        <v>17.171116</v>
       </c>
       <c r="S172" t="n">
-        <v>16.506704</v>
+        <v>16.506715</v>
       </c>
       <c r="T172" t="n">
-        <v>15.749451</v>
+        <v>15.749462</v>
       </c>
       <c r="U172" t="n">
-        <v>14.933805</v>
+        <v>14.933817</v>
       </c>
       <c r="V172" t="n">
-        <v>14.047501</v>
+        <v>14.047513</v>
       </c>
     </row>
     <row r="173">
@@ -13534,10 +13534,10 @@
         <v>0.221293</v>
       </c>
       <c r="I173" t="n">
-        <v>0.248044</v>
+        <v>0.248043</v>
       </c>
       <c r="J173" t="n">
-        <v>0.270849</v>
+        <v>0.270848</v>
       </c>
       <c r="K173" t="n">
         <v>0.292592</v>
@@ -13549,31 +13549,31 @@
         <v>0.349398</v>
       </c>
       <c r="N173" t="n">
-        <v>0.392131</v>
+        <v>0.39213</v>
       </c>
       <c r="O173" t="n">
-        <v>0.437914</v>
+        <v>0.437913</v>
       </c>
       <c r="P173" t="n">
-        <v>0.489449</v>
+        <v>0.489448</v>
       </c>
       <c r="Q173" t="n">
-        <v>0.539548</v>
+        <v>0.539547</v>
       </c>
       <c r="R173" t="n">
-        <v>0.576086</v>
+        <v>0.576084</v>
       </c>
       <c r="S173" t="n">
-        <v>0.618159</v>
+        <v>0.618157</v>
       </c>
       <c r="T173" t="n">
-        <v>0.661029</v>
+        <v>0.661027</v>
       </c>
       <c r="U173" t="n">
-        <v>0.705134</v>
+        <v>0.705132</v>
       </c>
       <c r="V173" t="n">
-        <v>0.75012</v>
+        <v>0.750118</v>
       </c>
     </row>
     <row r="174">
@@ -13598,58 +13598,58 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>92.056631</v>
+        <v>92.056635</v>
       </c>
       <c r="F174" t="n">
-        <v>98.70314500000001</v>
+        <v>98.70315100000001</v>
       </c>
       <c r="G174" t="n">
-        <v>99.550225</v>
+        <v>99.55023199999999</v>
       </c>
       <c r="H174" t="n">
-        <v>101.349546</v>
+        <v>101.349554</v>
       </c>
       <c r="I174" t="n">
-        <v>102.906685</v>
+        <v>102.906695</v>
       </c>
       <c r="J174" t="n">
-        <v>105.684391</v>
+        <v>105.684405</v>
       </c>
       <c r="K174" t="n">
-        <v>108.201413</v>
+        <v>108.201431</v>
       </c>
       <c r="L174" t="n">
-        <v>109.099415</v>
+        <v>109.099437</v>
       </c>
       <c r="M174" t="n">
-        <v>110.060261</v>
+        <v>110.060288</v>
       </c>
       <c r="N174" t="n">
-        <v>110.6393</v>
+        <v>110.63933</v>
       </c>
       <c r="O174" t="n">
-        <v>109.519915</v>
+        <v>109.519949</v>
       </c>
       <c r="P174" t="n">
-        <v>108.055861</v>
+        <v>108.055898</v>
       </c>
       <c r="Q174" t="n">
-        <v>105.149349</v>
+        <v>105.149388</v>
       </c>
       <c r="R174" t="n">
-        <v>99.18470499999999</v>
+        <v>99.184747</v>
       </c>
       <c r="S174" t="n">
-        <v>94.048436</v>
+        <v>94.04848</v>
       </c>
       <c r="T174" t="n">
-        <v>88.76878600000001</v>
+        <v>88.768833</v>
       </c>
       <c r="U174" t="n">
-        <v>83.510963</v>
+        <v>83.51101199999999</v>
       </c>
       <c r="V174" t="n">
-        <v>78.18622999999999</v>
+        <v>78.18628</v>
       </c>
     </row>
     <row r="175">
@@ -13689,43 +13689,43 @@
         <v>0.933704</v>
       </c>
       <c r="J175" t="n">
-        <v>1.127927</v>
+        <v>1.127926</v>
       </c>
       <c r="K175" t="n">
-        <v>1.317095</v>
+        <v>1.317094</v>
       </c>
       <c r="L175" t="n">
         <v>1.50095</v>
       </c>
       <c r="M175" t="n">
-        <v>1.727629</v>
+        <v>1.727628</v>
       </c>
       <c r="N175" t="n">
-        <v>1.992881</v>
+        <v>1.99288</v>
       </c>
       <c r="O175" t="n">
-        <v>2.273941</v>
+        <v>2.27394</v>
       </c>
       <c r="P175" t="n">
-        <v>2.59738</v>
+        <v>2.597379</v>
       </c>
       <c r="Q175" t="n">
-        <v>2.931122</v>
+        <v>2.931121</v>
       </c>
       <c r="R175" t="n">
-        <v>3.204793</v>
+        <v>3.204792</v>
       </c>
       <c r="S175" t="n">
-        <v>3.525233</v>
+        <v>3.525231</v>
       </c>
       <c r="T175" t="n">
-        <v>3.8677</v>
+        <v>3.867698</v>
       </c>
       <c r="U175" t="n">
-        <v>4.232518</v>
+        <v>4.232517</v>
       </c>
       <c r="V175" t="n">
-        <v>4.610553</v>
+        <v>4.610551</v>
       </c>
     </row>
     <row r="176">
@@ -13826,58 +13826,58 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>66.04856599999999</v>
+        <v>66.048565</v>
       </c>
       <c r="F177" t="n">
-        <v>97.263947</v>
+        <v>97.263949</v>
       </c>
       <c r="G177" t="n">
-        <v>125.280807</v>
+        <v>125.280815</v>
       </c>
       <c r="H177" t="n">
-        <v>145.251868</v>
+        <v>145.251884</v>
       </c>
       <c r="I177" t="n">
-        <v>154.18634</v>
+        <v>154.186361</v>
       </c>
       <c r="J177" t="n">
-        <v>155.673558</v>
+        <v>155.673583</v>
       </c>
       <c r="K177" t="n">
-        <v>152.49179</v>
+        <v>152.491818</v>
       </c>
       <c r="L177" t="n">
-        <v>149.039328</v>
+        <v>149.039358</v>
       </c>
       <c r="M177" t="n">
-        <v>149.463559</v>
+        <v>149.463595</v>
       </c>
       <c r="N177" t="n">
-        <v>151.962015</v>
+        <v>151.962057</v>
       </c>
       <c r="O177" t="n">
-        <v>153.751175</v>
+        <v>153.751224</v>
       </c>
       <c r="P177" t="n">
-        <v>155.162967</v>
+        <v>155.163023</v>
       </c>
       <c r="Q177" t="n">
-        <v>153.261634</v>
+        <v>153.261696</v>
       </c>
       <c r="R177" t="n">
-        <v>145.31773</v>
+        <v>145.317796</v>
       </c>
       <c r="S177" t="n">
-        <v>137.792895</v>
+        <v>137.792965</v>
       </c>
       <c r="T177" t="n">
-        <v>130.167355</v>
+        <v>130.167428</v>
       </c>
       <c r="U177" t="n">
-        <v>123.010972</v>
+        <v>123.011049</v>
       </c>
       <c r="V177" t="n">
-        <v>115.974842</v>
+        <v>115.974923</v>
       </c>
     </row>
     <row r="178">
@@ -13914,46 +13914,46 @@
         <v>0.086119</v>
       </c>
       <c r="I178" t="n">
-        <v>0.094788</v>
+        <v>0.094787</v>
       </c>
       <c r="J178" t="n">
-        <v>0.102827</v>
+        <v>0.102826</v>
       </c>
       <c r="K178" t="n">
-        <v>0.11007</v>
+        <v>0.110069</v>
       </c>
       <c r="L178" t="n">
-        <v>0.116949</v>
+        <v>0.116948</v>
       </c>
       <c r="M178" t="n">
-        <v>0.126465</v>
+        <v>0.126464</v>
       </c>
       <c r="N178" t="n">
-        <v>0.138303</v>
+        <v>0.138302</v>
       </c>
       <c r="O178" t="n">
-        <v>0.150238</v>
+        <v>0.150237</v>
       </c>
       <c r="P178" t="n">
-        <v>0.163311</v>
+        <v>0.16331</v>
       </c>
       <c r="Q178" t="n">
         <v>0.175098</v>
       </c>
       <c r="R178" t="n">
-        <v>0.181743</v>
+        <v>0.181742</v>
       </c>
       <c r="S178" t="n">
-        <v>0.189436</v>
+        <v>0.189435</v>
       </c>
       <c r="T178" t="n">
-        <v>0.196575</v>
+        <v>0.196574</v>
       </c>
       <c r="U178" t="n">
-        <v>0.203325</v>
+        <v>0.203324</v>
       </c>
       <c r="V178" t="n">
-        <v>0.209517</v>
+        <v>0.209516</v>
       </c>
     </row>
     <row r="179">
@@ -14020,7 +14020,7 @@
         <v>0.202467</v>
       </c>
       <c r="S179" t="n">
-        <v>0.213228</v>
+        <v>0.213227</v>
       </c>
       <c r="T179" t="n">
         <v>0.224665</v>
@@ -14130,58 +14130,58 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>-2e-06</v>
+        <v>-7e-06</v>
       </c>
       <c r="F181" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="G181" t="n">
-        <v>-5e-06</v>
+        <v>3e-06</v>
       </c>
       <c r="H181" t="n">
-        <v>-4e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="I181" t="n">
-        <v>-3e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="J181" t="n">
-        <v>-1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="K181" t="n">
         <v>-1e-06</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>-1e-06</v>
       </c>
       <c r="M181" t="n">
-        <v>4e-06</v>
+        <v>-2e-06</v>
       </c>
       <c r="N181" t="n">
+        <v>-3e-06</v>
+      </c>
+      <c r="O181" t="n">
+        <v>-2e-06</v>
+      </c>
+      <c r="P181" t="n">
         <v>-8e-06</v>
-      </c>
-      <c r="O181" t="n">
-        <v>6e-06</v>
-      </c>
-      <c r="P181" t="n">
-        <v>-1e-06</v>
       </c>
       <c r="Q181" t="n">
         <v>4e-06</v>
       </c>
       <c r="R181" t="n">
-        <v>-1e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="S181" t="n">
-        <v>-5e-06</v>
+        <v>-7e-06</v>
       </c>
       <c r="T181" t="n">
+        <v>-4e-06</v>
+      </c>
+      <c r="U181" t="n">
         <v>-7e-06</v>
       </c>
-      <c r="U181" t="n">
-        <v>-5e-06</v>
-      </c>
       <c r="V181" t="n">
-        <v>-6e-06</v>
+        <v>-8e-06</v>
       </c>
     </row>
   </sheetData>
